--- a/詳細設計書.xlsx
+++ b/詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AA716B-860D-4753-9014-242147BB35CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5622ABB9-D65E-4A8E-8D4B-A6B3020B71CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="758" firstSheet="16" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="758" firstSheet="16" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="項目説明（原本）" sheetId="33" r:id="rId1"/>
@@ -32,8 +32,9 @@
     <sheet name="イベント一覧（アカウント登録）" sheetId="28" r:id="rId17"/>
     <sheet name="イベント一覧（アカウント検索・一覧）" sheetId="47" r:id="rId18"/>
     <sheet name="イベント一覧（アカウン更新）" sheetId="48" r:id="rId19"/>
-    <sheet name="更新仕様書" sheetId="26" r:id="rId20"/>
-    <sheet name="補足説明" sheetId="27" r:id="rId21"/>
+    <sheet name="イベント一覧（アカウン削除）" sheetId="49" r:id="rId20"/>
+    <sheet name="更新仕様書" sheetId="26" r:id="rId21"/>
+    <sheet name="補足説明" sheetId="27" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'IO関連図（アカウント検索・一覧）'!$A$1:$AG$38</definedName>
@@ -42,19 +43,20 @@
     <definedName name="_xlnm.Print_Area" localSheetId="17">'イベント一覧（アカウント検索・一覧）'!$A$1:$AG$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'イベント一覧（アカウント登録）'!$A$1:$AG$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'イベント一覧（アカウン更新）'!$A$1:$AG$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'イベント一覧（アカウン削除）'!$A$1:$AG$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'イベント一覧（原本）'!$A$1:$AG$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'画面レイアウト（アカウント検索・一覧）'!$A$1:$AK$81</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'画面レイアウト（アカウント更新）'!$A$1:$W$114</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'画面レイアウト（アカウント削除）'!$A$1:$W$114</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'画面レイアウト（アカウント登録）'!$A$1:$W$114</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="19">更新仕様書!$A$1:$AG$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">更新仕様書!$A$1:$AG$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'更新仕様書（原本）'!$A$1:$AG$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'項目説明（アカウント検索・一覧）'!$A$1:$AG$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'項目説明（アカウント更新・削除）'!$A$1:$AG$64</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'項目説明（アカウント登録）'!$A$1:$AG$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'項目説明（原本）'!$A$1:$AG$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">表紙!$A$1:$AF$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="20">補足説明!$A$1:$AG$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">補足説明!$A$1:$AG$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'補足説明（原本）'!$A$1:$AG$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">目次・概要!$A$1:$AG$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'IO関連図（アカウント検索・一覧）'!$1:$3</definedName>
@@ -63,27 +65,29 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="17">'イベント一覧（アカウント検索・一覧）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="16">'イベント一覧（アカウント登録）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="18">'イベント一覧（アカウン更新）'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'イベント一覧（アカウン削除）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'イベント一覧（原本）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'画面レイアウト（アカウント検索・一覧）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'画面レイアウト（アカウント更新）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'画面レイアウト（アカウント削除）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'画面レイアウト（アカウント登録）'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">更新仕様書!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">更新仕様書!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'更新仕様書（原本）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'項目説明（アカウント検索・一覧）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="14">'項目説明（アカウント更新・削除）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'項目説明（アカウント登録）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'項目説明（原本）'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">補足説明!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">補足説明!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'補足説明（原本）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">目次・概要!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="395">
   <si>
     <t>システム名</t>
     <rPh sb="4" eb="5">
@@ -3416,6 +3420,13 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
+    <t>データ元：DB、引数名：family_name、データ型：varchar、桁数：10、必須、チェック：ひらがな・漢字、文字数</t>
+    <rPh sb="59" eb="62">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
     <t>アカウント更新画面・更新確認画面・更新完了画面</t>
     <rPh sb="5" eb="7">
       <t>コウシン</t>
@@ -3438,6 +3449,67 @@
     <rPh sb="21" eb="23">
       <t>ガメン</t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データ元：DB、引数名：last_name、データ型：varchar、桁数：10、必須、チェック：ひらがな・漢字、文字数</t>
+    <rPh sb="57" eb="60">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データ元：DB、引数名：family_name_kana、データ型：varchar、桁数：10、必須、チェック：カタカナ、文字数</t>
+    <rPh sb="61" eb="64">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データ元：DB、引数名：last_name_kana、データ型：varchar、桁数：10、必須、チェック：カタカナ、文字数</t>
+    <rPh sb="59" eb="62">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データ元：DB、引数名：mail、データ型：varchar、桁数：100、必須、チェック：半角英数字・半角記号（ハイフン、＠）、文字数</t>
+    <rPh sb="64" eb="67">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データ元：DB、引数名：gender、データ型：int、必須</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データ元：DB、引数名：postal_code、データ型：int、桁数：7、必須、チェック：半角数字、文字数</t>
+    <rPh sb="51" eb="54">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データ元：DB、引数名：prefecture、データ型：varchar、桁数：100、必須</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データ元：DB、引数名：address_1、データ型：varchar、桁数：10、必須、チェック：ひらがな・漢字・数字・カタカナ・記号（ハイフンとスペース）、文字数</t>
+    <rPh sb="79" eb="82">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データ元：DB、引数名：address_2、データ型：varchar、桁数：100、必須、チェック：ひらがな・漢字・数字・カタカナ・記号（ハイフンとスペース）、文字数</t>
+    <rPh sb="80" eb="83">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データ元：DB、引数名：authority、データ型：int、必須</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -3500,7 +3572,7 @@
   </si>
   <si>
     <t>データ元：入力、引数名：password、データ型：varchar、桁数：10、必須、チェック：半角英数字、文字数</t>
-    <rPh sb="57" eb="60">
+    <rPh sb="0" eb="57">
       <t>モジスウ</t>
     </rPh>
     <phoneticPr fontId="4"/>
@@ -3650,6 +3722,158 @@
       <t>カンリョウ</t>
     </rPh>
     <rPh sb="43" eb="45">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント削除画面・削除確認画面・削除完了画面</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント削除画面</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>・「アカウント削除確認画面」へ遷移</t>
+    <rPh sb="7" eb="13">
+      <t>サクジョカクニンガメン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント削除確認画面</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>・前画面「アカウント削除画面」へ内容を保持した状態で戻る</t>
+    <rPh sb="1" eb="4">
+      <t>ゼンガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ホジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>■削除処理を実行</t>
+    <rPh sb="1" eb="3">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>・データベース内「delete_flag」に”1”を格納→アカウント削除完了画面へ遷移し、「削除完了しました」と表示</t>
+    <rPh sb="7" eb="8">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="36" eb="40">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>・データベース内「delete_flag」に”1”を格納時にエラーあり→アカウント削除完了画面へ遷移し、「エラーが発生したため削除できません」と表示</t>
+    <rPh sb="7" eb="8">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="43" eb="47">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="4"/>
@@ -4505,6 +4729,15 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4513,15 +4746,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4660,8 +4884,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4669,125 +4893,14 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -4837,6 +4950,21 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4855,23 +4983,128 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
@@ -4899,15 +5132,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
@@ -17892,48 +18116,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:181" ht="12.75" customHeight="1">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="259"/>
-      <c r="C1" s="259"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="259"/>
-      <c r="F1" s="259"/>
-      <c r="G1" s="259"/>
-      <c r="H1" s="259"/>
-      <c r="I1" s="259"/>
-      <c r="J1" s="259"/>
-      <c r="K1" s="259"/>
-      <c r="L1" s="259"/>
-      <c r="M1" s="259"/>
-      <c r="N1" s="259"/>
-      <c r="O1" s="259"/>
-      <c r="P1" s="259"/>
-      <c r="Q1" s="259"/>
-      <c r="R1" s="259"/>
-      <c r="S1" s="259"/>
-      <c r="T1" s="259"/>
-      <c r="U1" s="259"/>
-      <c r="V1" s="259"/>
-      <c r="W1" s="259"/>
-      <c r="X1" s="259"/>
-      <c r="Y1" s="259"/>
-      <c r="Z1" s="259"/>
-      <c r="AA1" s="259"/>
-      <c r="AB1" s="259"/>
-      <c r="AC1" s="259"/>
-      <c r="AD1" s="259"/>
-      <c r="AE1" s="259"/>
-      <c r="AF1" s="259"/>
-      <c r="AG1" s="259"/>
-      <c r="AH1" s="259"/>
-      <c r="AI1" s="259"/>
-      <c r="AJ1" s="259"/>
-      <c r="AK1" s="260"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="215"/>
+      <c r="N1" s="215"/>
+      <c r="O1" s="215"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="215"/>
+      <c r="Y1" s="215"/>
+      <c r="Z1" s="215"/>
+      <c r="AA1" s="215"/>
+      <c r="AB1" s="215"/>
+      <c r="AC1" s="215"/>
+      <c r="AD1" s="215"/>
+      <c r="AE1" s="215"/>
+      <c r="AF1" s="215"/>
+      <c r="AG1" s="215"/>
+      <c r="AH1" s="215"/>
+      <c r="AI1" s="215"/>
+      <c r="AJ1" s="215"/>
+      <c r="AK1" s="216"/>
     </row>
     <row r="2" spans="1:181" ht="13" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="217" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="142"/>
@@ -17977,10 +18201,10 @@
       <c r="AJ2" s="141" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="257"/>
+      <c r="AK2" s="197"/>
     </row>
     <row r="3" spans="1:181" s="21" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="261" t="s">
+      <c r="A3" s="217" t="s">
         <v>154</v>
       </c>
       <c r="B3" s="142"/>
@@ -18020,7 +18244,7 @@
       <c r="AH3" s="61"/>
       <c r="AI3" s="61"/>
       <c r="AJ3" s="141"/>
-      <c r="AK3" s="257"/>
+      <c r="AK3" s="197"/>
       <c r="AL3" s="19"/>
       <c r="AM3" s="20"/>
       <c r="AN3" s="20"/>
@@ -18331,34 +18555,34 @@
       <c r="D8" s="50"/>
       <c r="E8" s="50"/>
       <c r="F8" s="50"/>
-      <c r="G8" s="235" t="s">
+      <c r="G8" s="198" t="s">
         <v>156</v>
       </c>
-      <c r="H8" s="236"/>
-      <c r="I8" s="236"/>
-      <c r="J8" s="239"/>
-      <c r="K8" s="240"/>
-      <c r="L8" s="240"/>
-      <c r="M8" s="240"/>
-      <c r="N8" s="240"/>
-      <c r="O8" s="240"/>
-      <c r="P8" s="240"/>
-      <c r="Q8" s="240"/>
-      <c r="R8" s="241"/>
-      <c r="S8" s="245" t="s">
+      <c r="H8" s="199"/>
+      <c r="I8" s="199"/>
+      <c r="J8" s="202"/>
+      <c r="K8" s="203"/>
+      <c r="L8" s="203"/>
+      <c r="M8" s="203"/>
+      <c r="N8" s="203"/>
+      <c r="O8" s="203"/>
+      <c r="P8" s="203"/>
+      <c r="Q8" s="203"/>
+      <c r="R8" s="204"/>
+      <c r="S8" s="208" t="s">
         <v>157</v>
       </c>
-      <c r="T8" s="246"/>
-      <c r="U8" s="247"/>
-      <c r="V8" s="239"/>
-      <c r="W8" s="240"/>
-      <c r="X8" s="240"/>
-      <c r="Y8" s="240"/>
-      <c r="Z8" s="240"/>
-      <c r="AA8" s="240"/>
-      <c r="AB8" s="240"/>
-      <c r="AC8" s="240"/>
-      <c r="AD8" s="241"/>
+      <c r="T8" s="209"/>
+      <c r="U8" s="210"/>
+      <c r="V8" s="202"/>
+      <c r="W8" s="203"/>
+      <c r="X8" s="203"/>
+      <c r="Y8" s="203"/>
+      <c r="Z8" s="203"/>
+      <c r="AA8" s="203"/>
+      <c r="AB8" s="203"/>
+      <c r="AC8" s="203"/>
+      <c r="AD8" s="204"/>
       <c r="AE8" s="50"/>
       <c r="AF8" s="50"/>
       <c r="AG8" s="50"/>
@@ -18374,30 +18598,30 @@
       <c r="D9" s="50"/>
       <c r="E9" s="50"/>
       <c r="F9" s="50"/>
-      <c r="G9" s="237"/>
-      <c r="H9" s="238"/>
-      <c r="I9" s="238"/>
-      <c r="J9" s="242"/>
-      <c r="K9" s="243"/>
-      <c r="L9" s="243"/>
-      <c r="M9" s="243"/>
-      <c r="N9" s="243"/>
-      <c r="O9" s="243"/>
-      <c r="P9" s="243"/>
-      <c r="Q9" s="243"/>
-      <c r="R9" s="244"/>
-      <c r="S9" s="248"/>
-      <c r="T9" s="249"/>
-      <c r="U9" s="250"/>
-      <c r="V9" s="242"/>
-      <c r="W9" s="243"/>
-      <c r="X9" s="243"/>
-      <c r="Y9" s="243"/>
-      <c r="Z9" s="243"/>
-      <c r="AA9" s="243"/>
-      <c r="AB9" s="243"/>
-      <c r="AC9" s="243"/>
-      <c r="AD9" s="244"/>
+      <c r="G9" s="200"/>
+      <c r="H9" s="201"/>
+      <c r="I9" s="201"/>
+      <c r="J9" s="205"/>
+      <c r="K9" s="206"/>
+      <c r="L9" s="206"/>
+      <c r="M9" s="206"/>
+      <c r="N9" s="206"/>
+      <c r="O9" s="206"/>
+      <c r="P9" s="206"/>
+      <c r="Q9" s="206"/>
+      <c r="R9" s="207"/>
+      <c r="S9" s="211"/>
+      <c r="T9" s="212"/>
+      <c r="U9" s="213"/>
+      <c r="V9" s="205"/>
+      <c r="W9" s="206"/>
+      <c r="X9" s="206"/>
+      <c r="Y9" s="206"/>
+      <c r="Z9" s="206"/>
+      <c r="AA9" s="206"/>
+      <c r="AB9" s="206"/>
+      <c r="AC9" s="206"/>
+      <c r="AD9" s="207"/>
       <c r="AE9" s="50"/>
       <c r="AF9" s="50"/>
       <c r="AG9" s="50"/>
@@ -18413,34 +18637,34 @@
       <c r="D10" s="50"/>
       <c r="E10" s="50"/>
       <c r="F10" s="50"/>
-      <c r="G10" s="235" t="s">
+      <c r="G10" s="198" t="s">
         <v>230</v>
       </c>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="239"/>
-      <c r="K10" s="240"/>
-      <c r="L10" s="240"/>
-      <c r="M10" s="240"/>
-      <c r="N10" s="240"/>
-      <c r="O10" s="240"/>
-      <c r="P10" s="240"/>
-      <c r="Q10" s="240"/>
-      <c r="R10" s="241"/>
-      <c r="S10" s="245" t="s">
+      <c r="H10" s="199"/>
+      <c r="I10" s="199"/>
+      <c r="J10" s="202"/>
+      <c r="K10" s="203"/>
+      <c r="L10" s="203"/>
+      <c r="M10" s="203"/>
+      <c r="N10" s="203"/>
+      <c r="O10" s="203"/>
+      <c r="P10" s="203"/>
+      <c r="Q10" s="203"/>
+      <c r="R10" s="204"/>
+      <c r="S10" s="208" t="s">
         <v>231</v>
       </c>
-      <c r="T10" s="246"/>
-      <c r="U10" s="247"/>
-      <c r="V10" s="239"/>
-      <c r="W10" s="240"/>
-      <c r="X10" s="240"/>
-      <c r="Y10" s="240"/>
-      <c r="Z10" s="240"/>
-      <c r="AA10" s="240"/>
-      <c r="AB10" s="240"/>
-      <c r="AC10" s="240"/>
-      <c r="AD10" s="241"/>
+      <c r="T10" s="209"/>
+      <c r="U10" s="210"/>
+      <c r="V10" s="202"/>
+      <c r="W10" s="203"/>
+      <c r="X10" s="203"/>
+      <c r="Y10" s="203"/>
+      <c r="Z10" s="203"/>
+      <c r="AA10" s="203"/>
+      <c r="AB10" s="203"/>
+      <c r="AC10" s="203"/>
+      <c r="AD10" s="204"/>
       <c r="AE10" s="50"/>
       <c r="AF10" s="50"/>
       <c r="AG10" s="50"/>
@@ -18456,30 +18680,30 @@
       <c r="D11" s="50"/>
       <c r="E11" s="50"/>
       <c r="F11" s="50"/>
-      <c r="G11" s="237"/>
-      <c r="H11" s="238"/>
-      <c r="I11" s="238"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="243"/>
-      <c r="L11" s="243"/>
-      <c r="M11" s="243"/>
-      <c r="N11" s="243"/>
-      <c r="O11" s="243"/>
-      <c r="P11" s="243"/>
-      <c r="Q11" s="243"/>
-      <c r="R11" s="244"/>
-      <c r="S11" s="248"/>
-      <c r="T11" s="249"/>
-      <c r="U11" s="250"/>
-      <c r="V11" s="242"/>
-      <c r="W11" s="243"/>
-      <c r="X11" s="243"/>
-      <c r="Y11" s="243"/>
-      <c r="Z11" s="243"/>
-      <c r="AA11" s="243"/>
-      <c r="AB11" s="243"/>
-      <c r="AC11" s="243"/>
-      <c r="AD11" s="244"/>
+      <c r="G11" s="200"/>
+      <c r="H11" s="201"/>
+      <c r="I11" s="201"/>
+      <c r="J11" s="205"/>
+      <c r="K11" s="206"/>
+      <c r="L11" s="206"/>
+      <c r="M11" s="206"/>
+      <c r="N11" s="206"/>
+      <c r="O11" s="206"/>
+      <c r="P11" s="206"/>
+      <c r="Q11" s="206"/>
+      <c r="R11" s="207"/>
+      <c r="S11" s="211"/>
+      <c r="T11" s="212"/>
+      <c r="U11" s="213"/>
+      <c r="V11" s="205"/>
+      <c r="W11" s="206"/>
+      <c r="X11" s="206"/>
+      <c r="Y11" s="206"/>
+      <c r="Z11" s="206"/>
+      <c r="AA11" s="206"/>
+      <c r="AB11" s="206"/>
+      <c r="AC11" s="206"/>
+      <c r="AD11" s="207"/>
       <c r="AE11" s="50"/>
       <c r="AF11" s="50"/>
       <c r="AG11" s="50"/>
@@ -18495,36 +18719,36 @@
       <c r="D12" s="50"/>
       <c r="E12" s="50"/>
       <c r="F12" s="50"/>
-      <c r="G12" s="235" t="s">
+      <c r="G12" s="198" t="s">
         <v>160</v>
       </c>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="239"/>
-      <c r="K12" s="240"/>
-      <c r="L12" s="240"/>
-      <c r="M12" s="240"/>
-      <c r="N12" s="240"/>
-      <c r="O12" s="240"/>
-      <c r="P12" s="240"/>
-      <c r="Q12" s="240"/>
-      <c r="R12" s="241"/>
-      <c r="S12" s="245" t="s">
+      <c r="H12" s="199"/>
+      <c r="I12" s="199"/>
+      <c r="J12" s="202"/>
+      <c r="K12" s="203"/>
+      <c r="L12" s="203"/>
+      <c r="M12" s="203"/>
+      <c r="N12" s="203"/>
+      <c r="O12" s="203"/>
+      <c r="P12" s="203"/>
+      <c r="Q12" s="203"/>
+      <c r="R12" s="204"/>
+      <c r="S12" s="208" t="s">
         <v>162</v>
       </c>
-      <c r="T12" s="246"/>
-      <c r="U12" s="247"/>
-      <c r="V12" s="251" t="s">
+      <c r="T12" s="209"/>
+      <c r="U12" s="210"/>
+      <c r="V12" s="219" t="s">
         <v>232</v>
       </c>
-      <c r="W12" s="252"/>
-      <c r="X12" s="252"/>
-      <c r="Y12" s="252"/>
-      <c r="Z12" s="252"/>
-      <c r="AA12" s="252"/>
-      <c r="AB12" s="252"/>
-      <c r="AC12" s="252"/>
-      <c r="AD12" s="253"/>
+      <c r="W12" s="220"/>
+      <c r="X12" s="220"/>
+      <c r="Y12" s="220"/>
+      <c r="Z12" s="220"/>
+      <c r="AA12" s="220"/>
+      <c r="AB12" s="220"/>
+      <c r="AC12" s="220"/>
+      <c r="AD12" s="221"/>
       <c r="AE12" s="62"/>
       <c r="AF12" s="62"/>
       <c r="AG12" s="62"/>
@@ -18540,30 +18764,30 @@
       <c r="D13" s="91"/>
       <c r="E13" s="91"/>
       <c r="F13" s="50"/>
-      <c r="G13" s="237"/>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="242"/>
-      <c r="K13" s="243"/>
-      <c r="L13" s="243"/>
-      <c r="M13" s="243"/>
-      <c r="N13" s="243"/>
-      <c r="O13" s="243"/>
-      <c r="P13" s="243"/>
-      <c r="Q13" s="243"/>
-      <c r="R13" s="244"/>
-      <c r="S13" s="248"/>
-      <c r="T13" s="249"/>
-      <c r="U13" s="250"/>
-      <c r="V13" s="254"/>
-      <c r="W13" s="255"/>
-      <c r="X13" s="255"/>
-      <c r="Y13" s="255"/>
-      <c r="Z13" s="255"/>
-      <c r="AA13" s="255"/>
-      <c r="AB13" s="255"/>
-      <c r="AC13" s="255"/>
-      <c r="AD13" s="256"/>
+      <c r="G13" s="200"/>
+      <c r="H13" s="201"/>
+      <c r="I13" s="201"/>
+      <c r="J13" s="205"/>
+      <c r="K13" s="206"/>
+      <c r="L13" s="206"/>
+      <c r="M13" s="206"/>
+      <c r="N13" s="206"/>
+      <c r="O13" s="206"/>
+      <c r="P13" s="206"/>
+      <c r="Q13" s="206"/>
+      <c r="R13" s="207"/>
+      <c r="S13" s="211"/>
+      <c r="T13" s="212"/>
+      <c r="U13" s="213"/>
+      <c r="V13" s="222"/>
+      <c r="W13" s="223"/>
+      <c r="X13" s="223"/>
+      <c r="Y13" s="223"/>
+      <c r="Z13" s="223"/>
+      <c r="AA13" s="223"/>
+      <c r="AB13" s="223"/>
+      <c r="AC13" s="223"/>
+      <c r="AD13" s="224"/>
       <c r="AE13" s="50"/>
       <c r="AF13" s="50"/>
       <c r="AG13" s="50"/>
@@ -18579,32 +18803,32 @@
       <c r="D14" s="50"/>
       <c r="E14" s="50"/>
       <c r="F14" s="50"/>
-      <c r="G14" s="235" t="s">
+      <c r="G14" s="198" t="s">
         <v>167</v>
       </c>
-      <c r="H14" s="236"/>
-      <c r="I14" s="236"/>
-      <c r="J14" s="239"/>
-      <c r="K14" s="240"/>
-      <c r="L14" s="240"/>
-      <c r="M14" s="240"/>
-      <c r="N14" s="240"/>
-      <c r="O14" s="240"/>
-      <c r="P14" s="240"/>
-      <c r="Q14" s="240"/>
-      <c r="R14" s="241"/>
-      <c r="S14" s="239"/>
-      <c r="T14" s="240"/>
-      <c r="U14" s="241"/>
-      <c r="V14" s="239"/>
-      <c r="W14" s="240"/>
-      <c r="X14" s="240"/>
-      <c r="Y14" s="240"/>
-      <c r="Z14" s="240"/>
-      <c r="AA14" s="240"/>
-      <c r="AB14" s="240"/>
-      <c r="AC14" s="240"/>
-      <c r="AD14" s="241"/>
+      <c r="H14" s="199"/>
+      <c r="I14" s="199"/>
+      <c r="J14" s="202"/>
+      <c r="K14" s="203"/>
+      <c r="L14" s="203"/>
+      <c r="M14" s="203"/>
+      <c r="N14" s="203"/>
+      <c r="O14" s="203"/>
+      <c r="P14" s="203"/>
+      <c r="Q14" s="203"/>
+      <c r="R14" s="204"/>
+      <c r="S14" s="202"/>
+      <c r="T14" s="203"/>
+      <c r="U14" s="204"/>
+      <c r="V14" s="202"/>
+      <c r="W14" s="203"/>
+      <c r="X14" s="203"/>
+      <c r="Y14" s="203"/>
+      <c r="Z14" s="203"/>
+      <c r="AA14" s="203"/>
+      <c r="AB14" s="203"/>
+      <c r="AC14" s="203"/>
+      <c r="AD14" s="204"/>
       <c r="AE14" s="50"/>
       <c r="AF14" s="50"/>
       <c r="AG14" s="50"/>
@@ -18620,30 +18844,30 @@
       <c r="D15" s="50"/>
       <c r="E15" s="50"/>
       <c r="F15" s="50"/>
-      <c r="G15" s="237"/>
-      <c r="H15" s="238"/>
-      <c r="I15" s="238"/>
-      <c r="J15" s="242"/>
-      <c r="K15" s="243"/>
-      <c r="L15" s="243"/>
-      <c r="M15" s="243"/>
-      <c r="N15" s="243"/>
-      <c r="O15" s="243"/>
-      <c r="P15" s="243"/>
-      <c r="Q15" s="243"/>
-      <c r="R15" s="244"/>
-      <c r="S15" s="242"/>
-      <c r="T15" s="243"/>
-      <c r="U15" s="244"/>
-      <c r="V15" s="242"/>
-      <c r="W15" s="243"/>
-      <c r="X15" s="243"/>
-      <c r="Y15" s="243"/>
-      <c r="Z15" s="243"/>
-      <c r="AA15" s="243"/>
-      <c r="AB15" s="243"/>
-      <c r="AC15" s="243"/>
-      <c r="AD15" s="244"/>
+      <c r="G15" s="200"/>
+      <c r="H15" s="201"/>
+      <c r="I15" s="201"/>
+      <c r="J15" s="205"/>
+      <c r="K15" s="206"/>
+      <c r="L15" s="206"/>
+      <c r="M15" s="206"/>
+      <c r="N15" s="206"/>
+      <c r="O15" s="206"/>
+      <c r="P15" s="206"/>
+      <c r="Q15" s="206"/>
+      <c r="R15" s="207"/>
+      <c r="S15" s="205"/>
+      <c r="T15" s="206"/>
+      <c r="U15" s="207"/>
+      <c r="V15" s="205"/>
+      <c r="W15" s="206"/>
+      <c r="X15" s="206"/>
+      <c r="Y15" s="206"/>
+      <c r="Z15" s="206"/>
+      <c r="AA15" s="206"/>
+      <c r="AB15" s="206"/>
+      <c r="AC15" s="206"/>
+      <c r="AD15" s="207"/>
       <c r="AE15" s="50"/>
       <c r="AF15" s="50"/>
       <c r="AG15" s="50"/>
@@ -18659,9 +18883,9 @@
       <c r="D16" s="50"/>
       <c r="E16" s="50"/>
       <c r="F16" s="50"/>
-      <c r="G16" s="232"/>
-      <c r="H16" s="232"/>
-      <c r="I16" s="232"/>
+      <c r="G16" s="218"/>
+      <c r="H16" s="218"/>
+      <c r="I16" s="218"/>
       <c r="J16" s="52"/>
       <c r="K16" s="50"/>
       <c r="L16" s="50"/>
@@ -18671,18 +18895,18 @@
       <c r="P16" s="50"/>
       <c r="Q16" s="50"/>
       <c r="R16" s="50"/>
-      <c r="S16" s="232"/>
-      <c r="T16" s="232"/>
-      <c r="U16" s="232"/>
-      <c r="V16" s="232"/>
-      <c r="W16" s="232"/>
-      <c r="X16" s="232"/>
-      <c r="Y16" s="232"/>
-      <c r="Z16" s="232"/>
-      <c r="AA16" s="232"/>
-      <c r="AB16" s="232"/>
-      <c r="AC16" s="232"/>
-      <c r="AD16" s="232"/>
+      <c r="S16" s="218"/>
+      <c r="T16" s="218"/>
+      <c r="U16" s="218"/>
+      <c r="V16" s="218"/>
+      <c r="W16" s="218"/>
+      <c r="X16" s="218"/>
+      <c r="Y16" s="218"/>
+      <c r="Z16" s="218"/>
+      <c r="AA16" s="218"/>
+      <c r="AB16" s="218"/>
+      <c r="AC16" s="218"/>
+      <c r="AD16" s="218"/>
       <c r="AE16" s="50"/>
       <c r="AF16" s="50"/>
       <c r="AG16" s="50"/>
@@ -18698,9 +18922,9 @@
       <c r="D17" s="50"/>
       <c r="E17" s="50"/>
       <c r="F17" s="50"/>
-      <c r="G17" s="232"/>
-      <c r="H17" s="232"/>
-      <c r="I17" s="232"/>
+      <c r="G17" s="218"/>
+      <c r="H17" s="218"/>
+      <c r="I17" s="218"/>
       <c r="J17" s="52"/>
       <c r="K17" s="50"/>
       <c r="L17" s="50"/>
@@ -18710,18 +18934,18 @@
       <c r="P17" s="50"/>
       <c r="Q17" s="50"/>
       <c r="R17" s="50"/>
-      <c r="S17" s="232"/>
-      <c r="T17" s="232"/>
-      <c r="U17" s="232"/>
-      <c r="V17" s="232"/>
-      <c r="W17" s="232"/>
-      <c r="X17" s="232"/>
-      <c r="Y17" s="232"/>
-      <c r="Z17" s="232"/>
-      <c r="AA17" s="232"/>
-      <c r="AB17" s="232"/>
-      <c r="AC17" s="232"/>
-      <c r="AD17" s="232"/>
+      <c r="S17" s="218"/>
+      <c r="T17" s="218"/>
+      <c r="U17" s="218"/>
+      <c r="V17" s="218"/>
+      <c r="W17" s="218"/>
+      <c r="X17" s="218"/>
+      <c r="Y17" s="218"/>
+      <c r="Z17" s="218"/>
+      <c r="AA17" s="218"/>
+      <c r="AB17" s="218"/>
+      <c r="AC17" s="218"/>
+      <c r="AD17" s="218"/>
       <c r="AE17" s="50"/>
       <c r="AF17" s="50"/>
       <c r="AG17" s="50"/>
@@ -19870,34 +20094,34 @@
       <c r="D47" s="50"/>
       <c r="E47" s="50"/>
       <c r="F47" s="50"/>
-      <c r="G47" s="235" t="s">
+      <c r="G47" s="198" t="s">
         <v>156</v>
       </c>
-      <c r="H47" s="236"/>
-      <c r="I47" s="236"/>
-      <c r="J47" s="239"/>
-      <c r="K47" s="240"/>
-      <c r="L47" s="240"/>
-      <c r="M47" s="240"/>
-      <c r="N47" s="240"/>
-      <c r="O47" s="240"/>
-      <c r="P47" s="240"/>
-      <c r="Q47" s="240"/>
-      <c r="R47" s="241"/>
-      <c r="S47" s="245" t="s">
+      <c r="H47" s="199"/>
+      <c r="I47" s="199"/>
+      <c r="J47" s="202"/>
+      <c r="K47" s="203"/>
+      <c r="L47" s="203"/>
+      <c r="M47" s="203"/>
+      <c r="N47" s="203"/>
+      <c r="O47" s="203"/>
+      <c r="P47" s="203"/>
+      <c r="Q47" s="203"/>
+      <c r="R47" s="204"/>
+      <c r="S47" s="208" t="s">
         <v>157</v>
       </c>
-      <c r="T47" s="246"/>
-      <c r="U47" s="247"/>
-      <c r="V47" s="239"/>
-      <c r="W47" s="240"/>
-      <c r="X47" s="240"/>
-      <c r="Y47" s="240"/>
-      <c r="Z47" s="240"/>
-      <c r="AA47" s="240"/>
-      <c r="AB47" s="240"/>
-      <c r="AC47" s="240"/>
-      <c r="AD47" s="241"/>
+      <c r="T47" s="209"/>
+      <c r="U47" s="210"/>
+      <c r="V47" s="202"/>
+      <c r="W47" s="203"/>
+      <c r="X47" s="203"/>
+      <c r="Y47" s="203"/>
+      <c r="Z47" s="203"/>
+      <c r="AA47" s="203"/>
+      <c r="AB47" s="203"/>
+      <c r="AC47" s="203"/>
+      <c r="AD47" s="204"/>
       <c r="AE47" s="50"/>
       <c r="AF47" s="50"/>
       <c r="AG47" s="50"/>
@@ -19913,30 +20137,30 @@
       <c r="D48" s="50"/>
       <c r="E48" s="50"/>
       <c r="F48" s="50"/>
-      <c r="G48" s="237"/>
-      <c r="H48" s="238"/>
-      <c r="I48" s="238"/>
-      <c r="J48" s="242"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="243"/>
-      <c r="O48" s="243"/>
-      <c r="P48" s="243"/>
-      <c r="Q48" s="243"/>
-      <c r="R48" s="244"/>
-      <c r="S48" s="248"/>
-      <c r="T48" s="249"/>
-      <c r="U48" s="250"/>
-      <c r="V48" s="242"/>
-      <c r="W48" s="243"/>
-      <c r="X48" s="243"/>
-      <c r="Y48" s="243"/>
-      <c r="Z48" s="243"/>
-      <c r="AA48" s="243"/>
-      <c r="AB48" s="243"/>
-      <c r="AC48" s="243"/>
-      <c r="AD48" s="244"/>
+      <c r="G48" s="200"/>
+      <c r="H48" s="201"/>
+      <c r="I48" s="201"/>
+      <c r="J48" s="205"/>
+      <c r="K48" s="206"/>
+      <c r="L48" s="206"/>
+      <c r="M48" s="206"/>
+      <c r="N48" s="206"/>
+      <c r="O48" s="206"/>
+      <c r="P48" s="206"/>
+      <c r="Q48" s="206"/>
+      <c r="R48" s="207"/>
+      <c r="S48" s="211"/>
+      <c r="T48" s="212"/>
+      <c r="U48" s="213"/>
+      <c r="V48" s="205"/>
+      <c r="W48" s="206"/>
+      <c r="X48" s="206"/>
+      <c r="Y48" s="206"/>
+      <c r="Z48" s="206"/>
+      <c r="AA48" s="206"/>
+      <c r="AB48" s="206"/>
+      <c r="AC48" s="206"/>
+      <c r="AD48" s="207"/>
       <c r="AE48" s="50"/>
       <c r="AF48" s="50"/>
       <c r="AG48" s="50"/>
@@ -19952,34 +20176,34 @@
       <c r="D49" s="50"/>
       <c r="E49" s="50"/>
       <c r="F49" s="50"/>
-      <c r="G49" s="235" t="s">
+      <c r="G49" s="198" t="s">
         <v>230</v>
       </c>
-      <c r="H49" s="236"/>
-      <c r="I49" s="236"/>
-      <c r="J49" s="239"/>
-      <c r="K49" s="240"/>
-      <c r="L49" s="240"/>
-      <c r="M49" s="240"/>
-      <c r="N49" s="240"/>
-      <c r="O49" s="240"/>
-      <c r="P49" s="240"/>
-      <c r="Q49" s="240"/>
-      <c r="R49" s="241"/>
-      <c r="S49" s="245" t="s">
+      <c r="H49" s="199"/>
+      <c r="I49" s="199"/>
+      <c r="J49" s="202"/>
+      <c r="K49" s="203"/>
+      <c r="L49" s="203"/>
+      <c r="M49" s="203"/>
+      <c r="N49" s="203"/>
+      <c r="O49" s="203"/>
+      <c r="P49" s="203"/>
+      <c r="Q49" s="203"/>
+      <c r="R49" s="204"/>
+      <c r="S49" s="208" t="s">
         <v>231</v>
       </c>
-      <c r="T49" s="246"/>
-      <c r="U49" s="247"/>
-      <c r="V49" s="239"/>
-      <c r="W49" s="240"/>
-      <c r="X49" s="240"/>
-      <c r="Y49" s="240"/>
-      <c r="Z49" s="240"/>
-      <c r="AA49" s="240"/>
-      <c r="AB49" s="240"/>
-      <c r="AC49" s="240"/>
-      <c r="AD49" s="241"/>
+      <c r="T49" s="209"/>
+      <c r="U49" s="210"/>
+      <c r="V49" s="202"/>
+      <c r="W49" s="203"/>
+      <c r="X49" s="203"/>
+      <c r="Y49" s="203"/>
+      <c r="Z49" s="203"/>
+      <c r="AA49" s="203"/>
+      <c r="AB49" s="203"/>
+      <c r="AC49" s="203"/>
+      <c r="AD49" s="204"/>
       <c r="AE49" s="50"/>
       <c r="AF49" s="50"/>
       <c r="AG49" s="50"/>
@@ -19995,30 +20219,30 @@
       <c r="D50" s="50"/>
       <c r="E50" s="50"/>
       <c r="F50" s="50"/>
-      <c r="G50" s="237"/>
-      <c r="H50" s="238"/>
-      <c r="I50" s="238"/>
-      <c r="J50" s="242"/>
-      <c r="K50" s="243"/>
-      <c r="L50" s="243"/>
-      <c r="M50" s="243"/>
-      <c r="N50" s="243"/>
-      <c r="O50" s="243"/>
-      <c r="P50" s="243"/>
-      <c r="Q50" s="243"/>
-      <c r="R50" s="244"/>
-      <c r="S50" s="248"/>
-      <c r="T50" s="249"/>
-      <c r="U50" s="250"/>
-      <c r="V50" s="242"/>
-      <c r="W50" s="243"/>
-      <c r="X50" s="243"/>
-      <c r="Y50" s="243"/>
-      <c r="Z50" s="243"/>
-      <c r="AA50" s="243"/>
-      <c r="AB50" s="243"/>
-      <c r="AC50" s="243"/>
-      <c r="AD50" s="244"/>
+      <c r="G50" s="200"/>
+      <c r="H50" s="201"/>
+      <c r="I50" s="201"/>
+      <c r="J50" s="205"/>
+      <c r="K50" s="206"/>
+      <c r="L50" s="206"/>
+      <c r="M50" s="206"/>
+      <c r="N50" s="206"/>
+      <c r="O50" s="206"/>
+      <c r="P50" s="206"/>
+      <c r="Q50" s="206"/>
+      <c r="R50" s="207"/>
+      <c r="S50" s="211"/>
+      <c r="T50" s="212"/>
+      <c r="U50" s="213"/>
+      <c r="V50" s="205"/>
+      <c r="W50" s="206"/>
+      <c r="X50" s="206"/>
+      <c r="Y50" s="206"/>
+      <c r="Z50" s="206"/>
+      <c r="AA50" s="206"/>
+      <c r="AB50" s="206"/>
+      <c r="AC50" s="206"/>
+      <c r="AD50" s="207"/>
       <c r="AE50" s="50"/>
       <c r="AF50" s="50"/>
       <c r="AG50" s="50"/>
@@ -20034,36 +20258,36 @@
       <c r="D51" s="50"/>
       <c r="E51" s="50"/>
       <c r="F51" s="50"/>
-      <c r="G51" s="235" t="s">
+      <c r="G51" s="198" t="s">
         <v>160</v>
       </c>
-      <c r="H51" s="236"/>
-      <c r="I51" s="236"/>
-      <c r="J51" s="239"/>
-      <c r="K51" s="240"/>
-      <c r="L51" s="240"/>
-      <c r="M51" s="240"/>
-      <c r="N51" s="240"/>
-      <c r="O51" s="240"/>
-      <c r="P51" s="240"/>
-      <c r="Q51" s="240"/>
-      <c r="R51" s="241"/>
-      <c r="S51" s="245" t="s">
+      <c r="H51" s="199"/>
+      <c r="I51" s="199"/>
+      <c r="J51" s="202"/>
+      <c r="K51" s="203"/>
+      <c r="L51" s="203"/>
+      <c r="M51" s="203"/>
+      <c r="N51" s="203"/>
+      <c r="O51" s="203"/>
+      <c r="P51" s="203"/>
+      <c r="Q51" s="203"/>
+      <c r="R51" s="204"/>
+      <c r="S51" s="208" t="s">
         <v>162</v>
       </c>
-      <c r="T51" s="246"/>
-      <c r="U51" s="247"/>
-      <c r="V51" s="251" t="s">
+      <c r="T51" s="209"/>
+      <c r="U51" s="210"/>
+      <c r="V51" s="219" t="s">
         <v>232</v>
       </c>
-      <c r="W51" s="252"/>
-      <c r="X51" s="252"/>
-      <c r="Y51" s="252"/>
-      <c r="Z51" s="252"/>
-      <c r="AA51" s="252"/>
-      <c r="AB51" s="252"/>
-      <c r="AC51" s="252"/>
-      <c r="AD51" s="253"/>
+      <c r="W51" s="220"/>
+      <c r="X51" s="220"/>
+      <c r="Y51" s="220"/>
+      <c r="Z51" s="220"/>
+      <c r="AA51" s="220"/>
+      <c r="AB51" s="220"/>
+      <c r="AC51" s="220"/>
+      <c r="AD51" s="221"/>
       <c r="AE51" s="62"/>
       <c r="AF51" s="62"/>
       <c r="AG51" s="62"/>
@@ -20079,30 +20303,30 @@
       <c r="D52" s="91"/>
       <c r="E52" s="91"/>
       <c r="F52" s="50"/>
-      <c r="G52" s="237"/>
-      <c r="H52" s="238"/>
-      <c r="I52" s="238"/>
-      <c r="J52" s="242"/>
-      <c r="K52" s="243"/>
-      <c r="L52" s="243"/>
-      <c r="M52" s="243"/>
-      <c r="N52" s="243"/>
-      <c r="O52" s="243"/>
-      <c r="P52" s="243"/>
-      <c r="Q52" s="243"/>
-      <c r="R52" s="244"/>
-      <c r="S52" s="248"/>
-      <c r="T52" s="249"/>
-      <c r="U52" s="250"/>
-      <c r="V52" s="254"/>
-      <c r="W52" s="255"/>
-      <c r="X52" s="255"/>
-      <c r="Y52" s="255"/>
-      <c r="Z52" s="255"/>
-      <c r="AA52" s="255"/>
-      <c r="AB52" s="255"/>
-      <c r="AC52" s="255"/>
-      <c r="AD52" s="256"/>
+      <c r="G52" s="200"/>
+      <c r="H52" s="201"/>
+      <c r="I52" s="201"/>
+      <c r="J52" s="205"/>
+      <c r="K52" s="206"/>
+      <c r="L52" s="206"/>
+      <c r="M52" s="206"/>
+      <c r="N52" s="206"/>
+      <c r="O52" s="206"/>
+      <c r="P52" s="206"/>
+      <c r="Q52" s="206"/>
+      <c r="R52" s="207"/>
+      <c r="S52" s="211"/>
+      <c r="T52" s="212"/>
+      <c r="U52" s="213"/>
+      <c r="V52" s="222"/>
+      <c r="W52" s="223"/>
+      <c r="X52" s="223"/>
+      <c r="Y52" s="223"/>
+      <c r="Z52" s="223"/>
+      <c r="AA52" s="223"/>
+      <c r="AB52" s="223"/>
+      <c r="AC52" s="223"/>
+      <c r="AD52" s="224"/>
       <c r="AE52" s="50"/>
       <c r="AF52" s="50"/>
       <c r="AG52" s="50"/>
@@ -20118,32 +20342,32 @@
       <c r="D53" s="50"/>
       <c r="E53" s="50"/>
       <c r="F53" s="50"/>
-      <c r="G53" s="235" t="s">
+      <c r="G53" s="198" t="s">
         <v>167</v>
       </c>
-      <c r="H53" s="236"/>
-      <c r="I53" s="236"/>
-      <c r="J53" s="239"/>
-      <c r="K53" s="240"/>
-      <c r="L53" s="240"/>
-      <c r="M53" s="240"/>
-      <c r="N53" s="240"/>
-      <c r="O53" s="240"/>
-      <c r="P53" s="240"/>
-      <c r="Q53" s="240"/>
-      <c r="R53" s="241"/>
-      <c r="S53" s="239"/>
-      <c r="T53" s="240"/>
-      <c r="U53" s="241"/>
-      <c r="V53" s="239"/>
-      <c r="W53" s="240"/>
-      <c r="X53" s="240"/>
-      <c r="Y53" s="240"/>
-      <c r="Z53" s="240"/>
-      <c r="AA53" s="240"/>
-      <c r="AB53" s="240"/>
-      <c r="AC53" s="240"/>
-      <c r="AD53" s="241"/>
+      <c r="H53" s="199"/>
+      <c r="I53" s="199"/>
+      <c r="J53" s="202"/>
+      <c r="K53" s="203"/>
+      <c r="L53" s="203"/>
+      <c r="M53" s="203"/>
+      <c r="N53" s="203"/>
+      <c r="O53" s="203"/>
+      <c r="P53" s="203"/>
+      <c r="Q53" s="203"/>
+      <c r="R53" s="204"/>
+      <c r="S53" s="202"/>
+      <c r="T53" s="203"/>
+      <c r="U53" s="204"/>
+      <c r="V53" s="202"/>
+      <c r="W53" s="203"/>
+      <c r="X53" s="203"/>
+      <c r="Y53" s="203"/>
+      <c r="Z53" s="203"/>
+      <c r="AA53" s="203"/>
+      <c r="AB53" s="203"/>
+      <c r="AC53" s="203"/>
+      <c r="AD53" s="204"/>
       <c r="AE53" s="50"/>
       <c r="AF53" s="50"/>
       <c r="AG53" s="50"/>
@@ -20159,30 +20383,30 @@
       <c r="D54" s="50"/>
       <c r="E54" s="50"/>
       <c r="F54" s="50"/>
-      <c r="G54" s="237"/>
-      <c r="H54" s="238"/>
-      <c r="I54" s="238"/>
-      <c r="J54" s="242"/>
-      <c r="K54" s="243"/>
-      <c r="L54" s="243"/>
-      <c r="M54" s="243"/>
-      <c r="N54" s="243"/>
-      <c r="O54" s="243"/>
-      <c r="P54" s="243"/>
-      <c r="Q54" s="243"/>
-      <c r="R54" s="244"/>
-      <c r="S54" s="242"/>
-      <c r="T54" s="243"/>
-      <c r="U54" s="244"/>
-      <c r="V54" s="242"/>
-      <c r="W54" s="243"/>
-      <c r="X54" s="243"/>
-      <c r="Y54" s="243"/>
-      <c r="Z54" s="243"/>
-      <c r="AA54" s="243"/>
-      <c r="AB54" s="243"/>
-      <c r="AC54" s="243"/>
-      <c r="AD54" s="244"/>
+      <c r="G54" s="200"/>
+      <c r="H54" s="201"/>
+      <c r="I54" s="201"/>
+      <c r="J54" s="205"/>
+      <c r="K54" s="206"/>
+      <c r="L54" s="206"/>
+      <c r="M54" s="206"/>
+      <c r="N54" s="206"/>
+      <c r="O54" s="206"/>
+      <c r="P54" s="206"/>
+      <c r="Q54" s="206"/>
+      <c r="R54" s="207"/>
+      <c r="S54" s="205"/>
+      <c r="T54" s="206"/>
+      <c r="U54" s="207"/>
+      <c r="V54" s="205"/>
+      <c r="W54" s="206"/>
+      <c r="X54" s="206"/>
+      <c r="Y54" s="206"/>
+      <c r="Z54" s="206"/>
+      <c r="AA54" s="206"/>
+      <c r="AB54" s="206"/>
+      <c r="AC54" s="206"/>
+      <c r="AD54" s="207"/>
       <c r="AE54" s="50"/>
       <c r="AF54" s="50"/>
       <c r="AG54" s="50"/>
@@ -20198,9 +20422,9 @@
       <c r="D55" s="50"/>
       <c r="E55" s="50"/>
       <c r="F55" s="50"/>
-      <c r="G55" s="232"/>
-      <c r="H55" s="232"/>
-      <c r="I55" s="232"/>
+      <c r="G55" s="218"/>
+      <c r="H55" s="218"/>
+      <c r="I55" s="218"/>
       <c r="J55" s="52"/>
       <c r="K55" s="50"/>
       <c r="L55" s="50"/>
@@ -20210,18 +20434,18 @@
       <c r="P55" s="50"/>
       <c r="Q55" s="50"/>
       <c r="R55" s="50"/>
-      <c r="S55" s="232"/>
-      <c r="T55" s="232"/>
-      <c r="U55" s="232"/>
-      <c r="V55" s="232"/>
-      <c r="W55" s="232"/>
-      <c r="X55" s="232"/>
-      <c r="Y55" s="232"/>
-      <c r="Z55" s="232"/>
-      <c r="AA55" s="232"/>
-      <c r="AB55" s="232"/>
-      <c r="AC55" s="232"/>
-      <c r="AD55" s="232"/>
+      <c r="S55" s="218"/>
+      <c r="T55" s="218"/>
+      <c r="U55" s="218"/>
+      <c r="V55" s="218"/>
+      <c r="W55" s="218"/>
+      <c r="X55" s="218"/>
+      <c r="Y55" s="218"/>
+      <c r="Z55" s="218"/>
+      <c r="AA55" s="218"/>
+      <c r="AB55" s="218"/>
+      <c r="AC55" s="218"/>
+      <c r="AD55" s="218"/>
       <c r="AE55" s="50"/>
       <c r="AF55" s="50"/>
       <c r="AG55" s="50"/>
@@ -20237,9 +20461,9 @@
       <c r="D56" s="50"/>
       <c r="E56" s="50"/>
       <c r="F56" s="50"/>
-      <c r="G56" s="232"/>
-      <c r="H56" s="232"/>
-      <c r="I56" s="232"/>
+      <c r="G56" s="218"/>
+      <c r="H56" s="218"/>
+      <c r="I56" s="218"/>
       <c r="J56" s="52"/>
       <c r="K56" s="50"/>
       <c r="L56" s="50"/>
@@ -20249,18 +20473,18 @@
       <c r="P56" s="50"/>
       <c r="Q56" s="50"/>
       <c r="R56" s="50"/>
-      <c r="S56" s="232"/>
-      <c r="T56" s="232"/>
-      <c r="U56" s="232"/>
-      <c r="V56" s="232"/>
-      <c r="W56" s="232"/>
-      <c r="X56" s="232"/>
-      <c r="Y56" s="232"/>
-      <c r="Z56" s="232"/>
-      <c r="AA56" s="232"/>
-      <c r="AB56" s="232"/>
-      <c r="AC56" s="232"/>
-      <c r="AD56" s="232"/>
+      <c r="S56" s="218"/>
+      <c r="T56" s="218"/>
+      <c r="U56" s="218"/>
+      <c r="V56" s="218"/>
+      <c r="W56" s="218"/>
+      <c r="X56" s="218"/>
+      <c r="Y56" s="218"/>
+      <c r="Z56" s="218"/>
+      <c r="AA56" s="218"/>
+      <c r="AB56" s="218"/>
+      <c r="AC56" s="218"/>
+      <c r="AD56" s="218"/>
       <c r="AE56" s="50"/>
       <c r="AF56" s="50"/>
       <c r="AG56" s="50"/>
@@ -20388,836 +20612,836 @@
     </row>
     <row r="60" spans="1:37" ht="12.75" customHeight="1">
       <c r="A60" s="96"/>
-      <c r="B60" s="233" t="s">
+      <c r="B60" s="225" t="s">
         <v>233</v>
       </c>
-      <c r="C60" s="226" t="s">
+      <c r="C60" s="227" t="s">
         <v>156</v>
       </c>
-      <c r="D60" s="227"/>
-      <c r="E60" s="228"/>
-      <c r="F60" s="226" t="s">
+      <c r="D60" s="228"/>
+      <c r="E60" s="229"/>
+      <c r="F60" s="227" t="s">
         <v>157</v>
       </c>
-      <c r="G60" s="227"/>
-      <c r="H60" s="228"/>
-      <c r="I60" s="226" t="s">
+      <c r="G60" s="228"/>
+      <c r="H60" s="229"/>
+      <c r="I60" s="227" t="s">
         <v>158</v>
       </c>
-      <c r="J60" s="227"/>
-      <c r="K60" s="228"/>
-      <c r="L60" s="226" t="s">
+      <c r="J60" s="228"/>
+      <c r="K60" s="229"/>
+      <c r="L60" s="227" t="s">
         <v>212</v>
       </c>
-      <c r="M60" s="227"/>
-      <c r="N60" s="228"/>
-      <c r="O60" s="226" t="s">
+      <c r="M60" s="228"/>
+      <c r="N60" s="229"/>
+      <c r="O60" s="227" t="s">
         <v>160</v>
       </c>
-      <c r="P60" s="227"/>
-      <c r="Q60" s="227"/>
-      <c r="R60" s="227"/>
-      <c r="S60" s="228"/>
-      <c r="T60" s="233" t="s">
+      <c r="P60" s="228"/>
+      <c r="Q60" s="228"/>
+      <c r="R60" s="228"/>
+      <c r="S60" s="229"/>
+      <c r="T60" s="225" t="s">
         <v>162</v>
       </c>
-      <c r="U60" s="226" t="s">
+      <c r="U60" s="227" t="s">
         <v>167</v>
       </c>
-      <c r="V60" s="227"/>
-      <c r="W60" s="228"/>
-      <c r="X60" s="226" t="s">
+      <c r="V60" s="228"/>
+      <c r="W60" s="229"/>
+      <c r="X60" s="227" t="s">
         <v>192</v>
       </c>
-      <c r="Y60" s="227"/>
-      <c r="Z60" s="228"/>
-      <c r="AA60" s="226" t="s">
+      <c r="Y60" s="228"/>
+      <c r="Z60" s="229"/>
+      <c r="AA60" s="227" t="s">
         <v>193</v>
       </c>
-      <c r="AB60" s="227"/>
-      <c r="AC60" s="228"/>
-      <c r="AD60" s="226" t="s">
+      <c r="AB60" s="228"/>
+      <c r="AC60" s="229"/>
+      <c r="AD60" s="227" t="s">
         <v>234</v>
       </c>
-      <c r="AE60" s="227"/>
-      <c r="AF60" s="228"/>
-      <c r="AG60" s="226" t="s">
+      <c r="AE60" s="228"/>
+      <c r="AF60" s="229"/>
+      <c r="AG60" s="227" t="s">
         <v>235</v>
       </c>
-      <c r="AH60" s="227"/>
-      <c r="AI60" s="227"/>
-      <c r="AJ60" s="228"/>
+      <c r="AH60" s="228"/>
+      <c r="AI60" s="228"/>
+      <c r="AJ60" s="229"/>
       <c r="AK60" s="97"/>
     </row>
     <row r="61" spans="1:37" ht="12.75" customHeight="1" thickBot="1">
       <c r="A61" s="96"/>
-      <c r="B61" s="234"/>
-      <c r="C61" s="229"/>
-      <c r="D61" s="230"/>
-      <c r="E61" s="231"/>
-      <c r="F61" s="229"/>
-      <c r="G61" s="230"/>
-      <c r="H61" s="231"/>
-      <c r="I61" s="229"/>
-      <c r="J61" s="230"/>
-      <c r="K61" s="231"/>
-      <c r="L61" s="229"/>
-      <c r="M61" s="230"/>
-      <c r="N61" s="231"/>
-      <c r="O61" s="229"/>
-      <c r="P61" s="230"/>
-      <c r="Q61" s="230"/>
-      <c r="R61" s="230"/>
-      <c r="S61" s="231"/>
-      <c r="T61" s="234"/>
-      <c r="U61" s="229"/>
-      <c r="V61" s="230"/>
-      <c r="W61" s="231"/>
-      <c r="X61" s="229"/>
-      <c r="Y61" s="230"/>
-      <c r="Z61" s="231"/>
-      <c r="AA61" s="229"/>
-      <c r="AB61" s="230"/>
-      <c r="AC61" s="231"/>
-      <c r="AD61" s="229"/>
-      <c r="AE61" s="230"/>
-      <c r="AF61" s="231"/>
-      <c r="AG61" s="229"/>
-      <c r="AH61" s="230"/>
-      <c r="AI61" s="230"/>
-      <c r="AJ61" s="231"/>
+      <c r="B61" s="226"/>
+      <c r="C61" s="230"/>
+      <c r="D61" s="231"/>
+      <c r="E61" s="232"/>
+      <c r="F61" s="230"/>
+      <c r="G61" s="231"/>
+      <c r="H61" s="232"/>
+      <c r="I61" s="230"/>
+      <c r="J61" s="231"/>
+      <c r="K61" s="232"/>
+      <c r="L61" s="230"/>
+      <c r="M61" s="231"/>
+      <c r="N61" s="232"/>
+      <c r="O61" s="230"/>
+      <c r="P61" s="231"/>
+      <c r="Q61" s="231"/>
+      <c r="R61" s="231"/>
+      <c r="S61" s="232"/>
+      <c r="T61" s="226"/>
+      <c r="U61" s="230"/>
+      <c r="V61" s="231"/>
+      <c r="W61" s="232"/>
+      <c r="X61" s="230"/>
+      <c r="Y61" s="231"/>
+      <c r="Z61" s="232"/>
+      <c r="AA61" s="230"/>
+      <c r="AB61" s="231"/>
+      <c r="AC61" s="232"/>
+      <c r="AD61" s="230"/>
+      <c r="AE61" s="231"/>
+      <c r="AF61" s="232"/>
+      <c r="AG61" s="230"/>
+      <c r="AH61" s="231"/>
+      <c r="AI61" s="231"/>
+      <c r="AJ61" s="232"/>
       <c r="AK61" s="97"/>
     </row>
     <row r="62" spans="1:37" ht="12.5" customHeight="1">
       <c r="A62" s="96"/>
-      <c r="B62" s="205">
+      <c r="B62" s="233">
         <v>135</v>
       </c>
-      <c r="C62" s="199" t="s">
+      <c r="C62" s="235" t="s">
         <v>236</v>
       </c>
-      <c r="D62" s="200"/>
-      <c r="E62" s="201"/>
-      <c r="F62" s="199" t="s">
+      <c r="D62" s="236"/>
+      <c r="E62" s="237"/>
+      <c r="F62" s="235" t="s">
         <v>217</v>
       </c>
-      <c r="G62" s="200"/>
-      <c r="H62" s="201"/>
-      <c r="I62" s="199" t="s">
+      <c r="G62" s="236"/>
+      <c r="H62" s="237"/>
+      <c r="I62" s="235" t="s">
         <v>237</v>
       </c>
-      <c r="J62" s="200"/>
-      <c r="K62" s="201"/>
-      <c r="L62" s="199" t="s">
+      <c r="J62" s="236"/>
+      <c r="K62" s="237"/>
+      <c r="L62" s="235" t="s">
         <v>219</v>
       </c>
-      <c r="M62" s="200"/>
-      <c r="N62" s="201"/>
-      <c r="O62" s="199" t="s">
+      <c r="M62" s="236"/>
+      <c r="N62" s="237"/>
+      <c r="O62" s="235" t="s">
         <v>238</v>
       </c>
-      <c r="P62" s="200"/>
-      <c r="Q62" s="200"/>
-      <c r="R62" s="200"/>
-      <c r="S62" s="201"/>
-      <c r="T62" s="205" t="s">
+      <c r="P62" s="236"/>
+      <c r="Q62" s="236"/>
+      <c r="R62" s="236"/>
+      <c r="S62" s="237"/>
+      <c r="T62" s="233" t="s">
         <v>213</v>
       </c>
-      <c r="U62" s="199" t="s">
+      <c r="U62" s="235" t="s">
         <v>239</v>
       </c>
-      <c r="V62" s="200"/>
-      <c r="W62" s="201"/>
-      <c r="X62" s="207" t="s">
+      <c r="V62" s="236"/>
+      <c r="W62" s="237"/>
+      <c r="X62" s="247" t="s">
         <v>240</v>
       </c>
-      <c r="Y62" s="208"/>
-      <c r="Z62" s="209"/>
-      <c r="AA62" s="213" t="s">
+      <c r="Y62" s="248"/>
+      <c r="Z62" s="249"/>
+      <c r="AA62" s="253" t="s">
         <v>241</v>
       </c>
-      <c r="AB62" s="214"/>
-      <c r="AC62" s="215"/>
-      <c r="AD62" s="213" t="s">
+      <c r="AB62" s="254"/>
+      <c r="AC62" s="255"/>
+      <c r="AD62" s="253" t="s">
         <v>242</v>
       </c>
-      <c r="AE62" s="214"/>
-      <c r="AF62" s="215"/>
-      <c r="AG62" s="219"/>
-      <c r="AH62" s="220"/>
-      <c r="AI62" s="223"/>
-      <c r="AJ62" s="220"/>
+      <c r="AE62" s="254"/>
+      <c r="AF62" s="255"/>
+      <c r="AG62" s="241"/>
+      <c r="AH62" s="242"/>
+      <c r="AI62" s="245"/>
+      <c r="AJ62" s="242"/>
       <c r="AK62" s="97"/>
     </row>
     <row r="63" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
       <c r="A63" s="96"/>
-      <c r="B63" s="206"/>
-      <c r="C63" s="202"/>
-      <c r="D63" s="203"/>
-      <c r="E63" s="204"/>
-      <c r="F63" s="202"/>
-      <c r="G63" s="203"/>
-      <c r="H63" s="204"/>
-      <c r="I63" s="202"/>
-      <c r="J63" s="203"/>
-      <c r="K63" s="204"/>
-      <c r="L63" s="202"/>
-      <c r="M63" s="203"/>
-      <c r="N63" s="204"/>
-      <c r="O63" s="202"/>
-      <c r="P63" s="203"/>
-      <c r="Q63" s="203"/>
-      <c r="R63" s="203"/>
-      <c r="S63" s="204"/>
-      <c r="T63" s="206"/>
-      <c r="U63" s="202"/>
-      <c r="V63" s="203"/>
-      <c r="W63" s="204"/>
-      <c r="X63" s="210"/>
-      <c r="Y63" s="211"/>
-      <c r="Z63" s="212"/>
-      <c r="AA63" s="216"/>
-      <c r="AB63" s="217"/>
-      <c r="AC63" s="218"/>
-      <c r="AD63" s="216"/>
-      <c r="AE63" s="217"/>
-      <c r="AF63" s="218"/>
-      <c r="AG63" s="221"/>
-      <c r="AH63" s="222"/>
-      <c r="AI63" s="224"/>
-      <c r="AJ63" s="222"/>
+      <c r="B63" s="234"/>
+      <c r="C63" s="238"/>
+      <c r="D63" s="239"/>
+      <c r="E63" s="240"/>
+      <c r="F63" s="238"/>
+      <c r="G63" s="239"/>
+      <c r="H63" s="240"/>
+      <c r="I63" s="238"/>
+      <c r="J63" s="239"/>
+      <c r="K63" s="240"/>
+      <c r="L63" s="238"/>
+      <c r="M63" s="239"/>
+      <c r="N63" s="240"/>
+      <c r="O63" s="238"/>
+      <c r="P63" s="239"/>
+      <c r="Q63" s="239"/>
+      <c r="R63" s="239"/>
+      <c r="S63" s="240"/>
+      <c r="T63" s="234"/>
+      <c r="U63" s="238"/>
+      <c r="V63" s="239"/>
+      <c r="W63" s="240"/>
+      <c r="X63" s="250"/>
+      <c r="Y63" s="251"/>
+      <c r="Z63" s="252"/>
+      <c r="AA63" s="256"/>
+      <c r="AB63" s="257"/>
+      <c r="AC63" s="258"/>
+      <c r="AD63" s="256"/>
+      <c r="AE63" s="257"/>
+      <c r="AF63" s="258"/>
+      <c r="AG63" s="243"/>
+      <c r="AH63" s="244"/>
+      <c r="AI63" s="246"/>
+      <c r="AJ63" s="244"/>
       <c r="AK63" s="97"/>
     </row>
     <row r="64" spans="1:37" ht="12.5" customHeight="1">
       <c r="A64" s="96"/>
-      <c r="B64" s="205">
+      <c r="B64" s="233">
         <v>134</v>
       </c>
-      <c r="C64" s="199" t="s">
+      <c r="C64" s="235" t="s">
         <v>243</v>
       </c>
-      <c r="D64" s="200"/>
-      <c r="E64" s="201"/>
-      <c r="F64" s="199" t="s">
+      <c r="D64" s="236"/>
+      <c r="E64" s="237"/>
+      <c r="F64" s="235" t="s">
         <v>244</v>
       </c>
-      <c r="G64" s="200"/>
-      <c r="H64" s="201"/>
-      <c r="I64" s="199" t="s">
+      <c r="G64" s="236"/>
+      <c r="H64" s="237"/>
+      <c r="I64" s="235" t="s">
         <v>245</v>
       </c>
-      <c r="J64" s="200"/>
-      <c r="K64" s="201"/>
-      <c r="L64" s="199" t="s">
+      <c r="J64" s="236"/>
+      <c r="K64" s="237"/>
+      <c r="L64" s="235" t="s">
         <v>246</v>
       </c>
-      <c r="M64" s="200"/>
-      <c r="N64" s="201"/>
-      <c r="O64" s="199" t="s">
+      <c r="M64" s="236"/>
+      <c r="N64" s="237"/>
+      <c r="O64" s="235" t="s">
         <v>247</v>
       </c>
-      <c r="P64" s="200"/>
-      <c r="Q64" s="200"/>
-      <c r="R64" s="200"/>
-      <c r="S64" s="201"/>
-      <c r="T64" s="205" t="s">
+      <c r="P64" s="236"/>
+      <c r="Q64" s="236"/>
+      <c r="R64" s="236"/>
+      <c r="S64" s="237"/>
+      <c r="T64" s="233" t="s">
         <v>213</v>
       </c>
-      <c r="U64" s="199" t="s">
+      <c r="U64" s="235" t="s">
         <v>239</v>
       </c>
-      <c r="V64" s="200"/>
-      <c r="W64" s="201"/>
-      <c r="X64" s="207" t="s">
+      <c r="V64" s="236"/>
+      <c r="W64" s="237"/>
+      <c r="X64" s="247" t="s">
         <v>240</v>
       </c>
-      <c r="Y64" s="208"/>
-      <c r="Z64" s="209"/>
-      <c r="AA64" s="213" t="s">
+      <c r="Y64" s="248"/>
+      <c r="Z64" s="249"/>
+      <c r="AA64" s="253" t="s">
         <v>248</v>
       </c>
-      <c r="AB64" s="214"/>
-      <c r="AC64" s="215"/>
-      <c r="AD64" s="213" t="s">
+      <c r="AB64" s="254"/>
+      <c r="AC64" s="255"/>
+      <c r="AD64" s="253" t="s">
         <v>241</v>
       </c>
-      <c r="AE64" s="214"/>
-      <c r="AF64" s="215"/>
-      <c r="AG64" s="219"/>
-      <c r="AH64" s="220"/>
-      <c r="AI64" s="223"/>
-      <c r="AJ64" s="220"/>
+      <c r="AE64" s="254"/>
+      <c r="AF64" s="255"/>
+      <c r="AG64" s="241"/>
+      <c r="AH64" s="242"/>
+      <c r="AI64" s="245"/>
+      <c r="AJ64" s="242"/>
       <c r="AK64" s="97"/>
     </row>
     <row r="65" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
       <c r="A65" s="96"/>
-      <c r="B65" s="206"/>
-      <c r="C65" s="202"/>
-      <c r="D65" s="203"/>
-      <c r="E65" s="204"/>
-      <c r="F65" s="202"/>
-      <c r="G65" s="203"/>
-      <c r="H65" s="204"/>
-      <c r="I65" s="202"/>
-      <c r="J65" s="203"/>
-      <c r="K65" s="204"/>
-      <c r="L65" s="202"/>
-      <c r="M65" s="203"/>
-      <c r="N65" s="204"/>
-      <c r="O65" s="202"/>
-      <c r="P65" s="203"/>
-      <c r="Q65" s="203"/>
-      <c r="R65" s="203"/>
-      <c r="S65" s="204"/>
-      <c r="T65" s="206"/>
-      <c r="U65" s="202"/>
-      <c r="V65" s="203"/>
-      <c r="W65" s="204"/>
-      <c r="X65" s="210"/>
-      <c r="Y65" s="211"/>
-      <c r="Z65" s="212"/>
-      <c r="AA65" s="216"/>
-      <c r="AB65" s="217"/>
-      <c r="AC65" s="218"/>
-      <c r="AD65" s="216"/>
-      <c r="AE65" s="217"/>
-      <c r="AF65" s="218"/>
-      <c r="AG65" s="221"/>
-      <c r="AH65" s="222"/>
-      <c r="AI65" s="224"/>
-      <c r="AJ65" s="222"/>
+      <c r="B65" s="234"/>
+      <c r="C65" s="238"/>
+      <c r="D65" s="239"/>
+      <c r="E65" s="240"/>
+      <c r="F65" s="238"/>
+      <c r="G65" s="239"/>
+      <c r="H65" s="240"/>
+      <c r="I65" s="238"/>
+      <c r="J65" s="239"/>
+      <c r="K65" s="240"/>
+      <c r="L65" s="238"/>
+      <c r="M65" s="239"/>
+      <c r="N65" s="240"/>
+      <c r="O65" s="238"/>
+      <c r="P65" s="239"/>
+      <c r="Q65" s="239"/>
+      <c r="R65" s="239"/>
+      <c r="S65" s="240"/>
+      <c r="T65" s="234"/>
+      <c r="U65" s="238"/>
+      <c r="V65" s="239"/>
+      <c r="W65" s="240"/>
+      <c r="X65" s="250"/>
+      <c r="Y65" s="251"/>
+      <c r="Z65" s="252"/>
+      <c r="AA65" s="256"/>
+      <c r="AB65" s="257"/>
+      <c r="AC65" s="258"/>
+      <c r="AD65" s="256"/>
+      <c r="AE65" s="257"/>
+      <c r="AF65" s="258"/>
+      <c r="AG65" s="243"/>
+      <c r="AH65" s="244"/>
+      <c r="AI65" s="246"/>
+      <c r="AJ65" s="244"/>
       <c r="AK65" s="97"/>
     </row>
     <row r="66" spans="1:37" ht="12.5" customHeight="1">
       <c r="A66" s="96"/>
-      <c r="B66" s="205">
+      <c r="B66" s="233">
         <v>133</v>
       </c>
-      <c r="C66" s="199" t="s">
+      <c r="C66" s="235" t="s">
         <v>249</v>
       </c>
-      <c r="D66" s="200"/>
-      <c r="E66" s="201"/>
-      <c r="F66" s="199" t="s">
+      <c r="D66" s="236"/>
+      <c r="E66" s="237"/>
+      <c r="F66" s="235" t="s">
         <v>250</v>
       </c>
-      <c r="G66" s="200"/>
-      <c r="H66" s="201"/>
-      <c r="I66" s="199" t="s">
+      <c r="G66" s="236"/>
+      <c r="H66" s="237"/>
+      <c r="I66" s="235" t="s">
         <v>251</v>
       </c>
-      <c r="J66" s="200"/>
-      <c r="K66" s="201"/>
-      <c r="L66" s="199" t="s">
+      <c r="J66" s="236"/>
+      <c r="K66" s="237"/>
+      <c r="L66" s="235" t="s">
         <v>252</v>
       </c>
-      <c r="M66" s="200"/>
-      <c r="N66" s="201"/>
-      <c r="O66" s="199" t="s">
+      <c r="M66" s="236"/>
+      <c r="N66" s="237"/>
+      <c r="O66" s="235" t="s">
         <v>253</v>
       </c>
-      <c r="P66" s="200"/>
-      <c r="Q66" s="200"/>
-      <c r="R66" s="200"/>
-      <c r="S66" s="201"/>
-      <c r="T66" s="205" t="s">
+      <c r="P66" s="236"/>
+      <c r="Q66" s="236"/>
+      <c r="R66" s="236"/>
+      <c r="S66" s="237"/>
+      <c r="T66" s="233" t="s">
         <v>213</v>
       </c>
-      <c r="U66" s="199" t="s">
+      <c r="U66" s="235" t="s">
         <v>239</v>
       </c>
-      <c r="V66" s="200"/>
-      <c r="W66" s="201"/>
-      <c r="X66" s="207" t="s">
+      <c r="V66" s="236"/>
+      <c r="W66" s="237"/>
+      <c r="X66" s="247" t="s">
         <v>240</v>
       </c>
-      <c r="Y66" s="208"/>
-      <c r="Z66" s="209"/>
-      <c r="AA66" s="213" t="s">
+      <c r="Y66" s="248"/>
+      <c r="Z66" s="249"/>
+      <c r="AA66" s="253" t="s">
         <v>254</v>
       </c>
-      <c r="AB66" s="214"/>
-      <c r="AC66" s="215"/>
-      <c r="AD66" s="213" t="s">
+      <c r="AB66" s="254"/>
+      <c r="AC66" s="255"/>
+      <c r="AD66" s="253" t="s">
         <v>241</v>
       </c>
-      <c r="AE66" s="214"/>
-      <c r="AF66" s="215"/>
-      <c r="AG66" s="219"/>
-      <c r="AH66" s="220"/>
-      <c r="AI66" s="223"/>
-      <c r="AJ66" s="220"/>
+      <c r="AE66" s="254"/>
+      <c r="AF66" s="255"/>
+      <c r="AG66" s="241"/>
+      <c r="AH66" s="242"/>
+      <c r="AI66" s="245"/>
+      <c r="AJ66" s="242"/>
       <c r="AK66" s="97"/>
     </row>
     <row r="67" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
       <c r="A67" s="96"/>
-      <c r="B67" s="206"/>
-      <c r="C67" s="202"/>
-      <c r="D67" s="203"/>
-      <c r="E67" s="204"/>
-      <c r="F67" s="202"/>
-      <c r="G67" s="203"/>
-      <c r="H67" s="204"/>
-      <c r="I67" s="202"/>
-      <c r="J67" s="203"/>
-      <c r="K67" s="204"/>
-      <c r="L67" s="202"/>
-      <c r="M67" s="203"/>
-      <c r="N67" s="204"/>
-      <c r="O67" s="202"/>
-      <c r="P67" s="203"/>
-      <c r="Q67" s="203"/>
-      <c r="R67" s="203"/>
-      <c r="S67" s="204"/>
-      <c r="T67" s="206"/>
-      <c r="U67" s="202"/>
-      <c r="V67" s="203"/>
-      <c r="W67" s="204"/>
-      <c r="X67" s="210"/>
-      <c r="Y67" s="211"/>
-      <c r="Z67" s="212"/>
-      <c r="AA67" s="216"/>
-      <c r="AB67" s="217"/>
-      <c r="AC67" s="218"/>
-      <c r="AD67" s="216"/>
-      <c r="AE67" s="217"/>
-      <c r="AF67" s="218"/>
-      <c r="AG67" s="221"/>
-      <c r="AH67" s="222"/>
-      <c r="AI67" s="224"/>
-      <c r="AJ67" s="222"/>
+      <c r="B67" s="234"/>
+      <c r="C67" s="238"/>
+      <c r="D67" s="239"/>
+      <c r="E67" s="240"/>
+      <c r="F67" s="238"/>
+      <c r="G67" s="239"/>
+      <c r="H67" s="240"/>
+      <c r="I67" s="238"/>
+      <c r="J67" s="239"/>
+      <c r="K67" s="240"/>
+      <c r="L67" s="238"/>
+      <c r="M67" s="239"/>
+      <c r="N67" s="240"/>
+      <c r="O67" s="238"/>
+      <c r="P67" s="239"/>
+      <c r="Q67" s="239"/>
+      <c r="R67" s="239"/>
+      <c r="S67" s="240"/>
+      <c r="T67" s="234"/>
+      <c r="U67" s="238"/>
+      <c r="V67" s="239"/>
+      <c r="W67" s="240"/>
+      <c r="X67" s="250"/>
+      <c r="Y67" s="251"/>
+      <c r="Z67" s="252"/>
+      <c r="AA67" s="256"/>
+      <c r="AB67" s="257"/>
+      <c r="AC67" s="258"/>
+      <c r="AD67" s="256"/>
+      <c r="AE67" s="257"/>
+      <c r="AF67" s="258"/>
+      <c r="AG67" s="243"/>
+      <c r="AH67" s="244"/>
+      <c r="AI67" s="246"/>
+      <c r="AJ67" s="244"/>
       <c r="AK67" s="97"/>
     </row>
     <row r="68" spans="1:37" ht="12.5" customHeight="1">
       <c r="A68" s="96"/>
-      <c r="B68" s="205">
+      <c r="B68" s="233">
         <v>111</v>
       </c>
-      <c r="C68" s="199" t="s">
+      <c r="C68" s="235" t="s">
         <v>255</v>
       </c>
-      <c r="D68" s="200"/>
-      <c r="E68" s="201"/>
-      <c r="F68" s="199" t="s">
+      <c r="D68" s="236"/>
+      <c r="E68" s="237"/>
+      <c r="F68" s="235" t="s">
         <v>256</v>
       </c>
-      <c r="G68" s="200"/>
-      <c r="H68" s="201"/>
-      <c r="I68" s="199" t="s">
+      <c r="G68" s="236"/>
+      <c r="H68" s="237"/>
+      <c r="I68" s="235" t="s">
         <v>257</v>
       </c>
-      <c r="J68" s="200"/>
-      <c r="K68" s="201"/>
-      <c r="L68" s="199" t="s">
+      <c r="J68" s="236"/>
+      <c r="K68" s="237"/>
+      <c r="L68" s="235" t="s">
         <v>258</v>
       </c>
-      <c r="M68" s="200"/>
-      <c r="N68" s="201"/>
-      <c r="O68" s="199" t="s">
+      <c r="M68" s="236"/>
+      <c r="N68" s="237"/>
+      <c r="O68" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="P68" s="200"/>
-      <c r="Q68" s="200"/>
-      <c r="R68" s="200"/>
-      <c r="S68" s="201"/>
-      <c r="T68" s="205" t="s">
+      <c r="P68" s="236"/>
+      <c r="Q68" s="236"/>
+      <c r="R68" s="236"/>
+      <c r="S68" s="237"/>
+      <c r="T68" s="233" t="s">
         <v>213</v>
       </c>
-      <c r="U68" s="199" t="s">
+      <c r="U68" s="235" t="s">
         <v>239</v>
       </c>
-      <c r="V68" s="200"/>
-      <c r="W68" s="201"/>
-      <c r="X68" s="207" t="s">
+      <c r="V68" s="236"/>
+      <c r="W68" s="237"/>
+      <c r="X68" s="247" t="s">
         <v>240</v>
       </c>
-      <c r="Y68" s="208"/>
-      <c r="Z68" s="209"/>
-      <c r="AA68" s="213" t="s">
+      <c r="Y68" s="248"/>
+      <c r="Z68" s="249"/>
+      <c r="AA68" s="253" t="s">
         <v>260</v>
       </c>
-      <c r="AB68" s="214"/>
-      <c r="AC68" s="215"/>
-      <c r="AD68" s="213"/>
-      <c r="AE68" s="214"/>
-      <c r="AF68" s="215"/>
-      <c r="AG68" s="219"/>
-      <c r="AH68" s="220"/>
-      <c r="AI68" s="223"/>
-      <c r="AJ68" s="220"/>
+      <c r="AB68" s="254"/>
+      <c r="AC68" s="255"/>
+      <c r="AD68" s="253"/>
+      <c r="AE68" s="254"/>
+      <c r="AF68" s="255"/>
+      <c r="AG68" s="241"/>
+      <c r="AH68" s="242"/>
+      <c r="AI68" s="245"/>
+      <c r="AJ68" s="242"/>
       <c r="AK68" s="97"/>
     </row>
     <row r="69" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
       <c r="A69" s="96"/>
-      <c r="B69" s="206"/>
-      <c r="C69" s="202"/>
-      <c r="D69" s="203"/>
-      <c r="E69" s="204"/>
-      <c r="F69" s="202"/>
-      <c r="G69" s="203"/>
-      <c r="H69" s="204"/>
-      <c r="I69" s="202"/>
-      <c r="J69" s="203"/>
-      <c r="K69" s="204"/>
-      <c r="L69" s="202"/>
-      <c r="M69" s="203"/>
-      <c r="N69" s="204"/>
-      <c r="O69" s="202"/>
-      <c r="P69" s="203"/>
-      <c r="Q69" s="203"/>
-      <c r="R69" s="203"/>
-      <c r="S69" s="204"/>
-      <c r="T69" s="206"/>
-      <c r="U69" s="202"/>
-      <c r="V69" s="203"/>
-      <c r="W69" s="204"/>
-      <c r="X69" s="210"/>
-      <c r="Y69" s="211"/>
-      <c r="Z69" s="212"/>
-      <c r="AA69" s="216"/>
-      <c r="AB69" s="217"/>
-      <c r="AC69" s="218"/>
-      <c r="AD69" s="216"/>
-      <c r="AE69" s="217"/>
-      <c r="AF69" s="218"/>
-      <c r="AG69" s="221"/>
-      <c r="AH69" s="222"/>
-      <c r="AI69" s="224"/>
-      <c r="AJ69" s="222"/>
+      <c r="B69" s="234"/>
+      <c r="C69" s="238"/>
+      <c r="D69" s="239"/>
+      <c r="E69" s="240"/>
+      <c r="F69" s="238"/>
+      <c r="G69" s="239"/>
+      <c r="H69" s="240"/>
+      <c r="I69" s="238"/>
+      <c r="J69" s="239"/>
+      <c r="K69" s="240"/>
+      <c r="L69" s="238"/>
+      <c r="M69" s="239"/>
+      <c r="N69" s="240"/>
+      <c r="O69" s="238"/>
+      <c r="P69" s="239"/>
+      <c r="Q69" s="239"/>
+      <c r="R69" s="239"/>
+      <c r="S69" s="240"/>
+      <c r="T69" s="234"/>
+      <c r="U69" s="238"/>
+      <c r="V69" s="239"/>
+      <c r="W69" s="240"/>
+      <c r="X69" s="250"/>
+      <c r="Y69" s="251"/>
+      <c r="Z69" s="252"/>
+      <c r="AA69" s="256"/>
+      <c r="AB69" s="257"/>
+      <c r="AC69" s="258"/>
+      <c r="AD69" s="256"/>
+      <c r="AE69" s="257"/>
+      <c r="AF69" s="258"/>
+      <c r="AG69" s="243"/>
+      <c r="AH69" s="244"/>
+      <c r="AI69" s="246"/>
+      <c r="AJ69" s="244"/>
       <c r="AK69" s="97"/>
     </row>
     <row r="70" spans="1:37" ht="12.5" customHeight="1">
       <c r="A70" s="96"/>
-      <c r="B70" s="225">
+      <c r="B70" s="259">
         <v>105</v>
       </c>
-      <c r="C70" s="199" t="s">
+      <c r="C70" s="235" t="s">
         <v>243</v>
       </c>
-      <c r="D70" s="200"/>
-      <c r="E70" s="201"/>
-      <c r="F70" s="199" t="s">
+      <c r="D70" s="236"/>
+      <c r="E70" s="237"/>
+      <c r="F70" s="235" t="s">
         <v>261</v>
       </c>
-      <c r="G70" s="200"/>
-      <c r="H70" s="201"/>
-      <c r="I70" s="199" t="s">
+      <c r="G70" s="236"/>
+      <c r="H70" s="237"/>
+      <c r="I70" s="235" t="s">
         <v>245</v>
       </c>
-      <c r="J70" s="200"/>
-      <c r="K70" s="201"/>
-      <c r="L70" s="199" t="s">
+      <c r="J70" s="236"/>
+      <c r="K70" s="237"/>
+      <c r="L70" s="235" t="s">
         <v>262</v>
       </c>
-      <c r="M70" s="200"/>
-      <c r="N70" s="201"/>
-      <c r="O70" s="199" t="s">
+      <c r="M70" s="236"/>
+      <c r="N70" s="237"/>
+      <c r="O70" s="235" t="s">
         <v>263</v>
       </c>
-      <c r="P70" s="200"/>
-      <c r="Q70" s="200"/>
-      <c r="R70" s="200"/>
-      <c r="S70" s="201"/>
-      <c r="T70" s="205" t="s">
+      <c r="P70" s="236"/>
+      <c r="Q70" s="236"/>
+      <c r="R70" s="236"/>
+      <c r="S70" s="237"/>
+      <c r="T70" s="233" t="s">
         <v>213</v>
       </c>
-      <c r="U70" s="199" t="s">
+      <c r="U70" s="235" t="s">
         <v>239</v>
       </c>
-      <c r="V70" s="200"/>
-      <c r="W70" s="201"/>
-      <c r="X70" s="207" t="s">
+      <c r="V70" s="236"/>
+      <c r="W70" s="237"/>
+      <c r="X70" s="247" t="s">
         <v>264</v>
       </c>
-      <c r="Y70" s="208"/>
-      <c r="Z70" s="209"/>
-      <c r="AA70" s="213" t="s">
+      <c r="Y70" s="248"/>
+      <c r="Z70" s="249"/>
+      <c r="AA70" s="253" t="s">
         <v>265</v>
       </c>
-      <c r="AB70" s="214"/>
-      <c r="AC70" s="215"/>
-      <c r="AD70" s="213" t="s">
+      <c r="AB70" s="254"/>
+      <c r="AC70" s="255"/>
+      <c r="AD70" s="253" t="s">
         <v>266</v>
       </c>
-      <c r="AE70" s="214"/>
-      <c r="AF70" s="215"/>
-      <c r="AG70" s="219"/>
-      <c r="AH70" s="220"/>
-      <c r="AI70" s="223"/>
-      <c r="AJ70" s="220"/>
+      <c r="AE70" s="254"/>
+      <c r="AF70" s="255"/>
+      <c r="AG70" s="241"/>
+      <c r="AH70" s="242"/>
+      <c r="AI70" s="245"/>
+      <c r="AJ70" s="242"/>
       <c r="AK70" s="97"/>
     </row>
     <row r="71" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
       <c r="A71" s="96"/>
-      <c r="B71" s="206"/>
-      <c r="C71" s="202"/>
-      <c r="D71" s="203"/>
-      <c r="E71" s="204"/>
-      <c r="F71" s="202"/>
-      <c r="G71" s="203"/>
-      <c r="H71" s="204"/>
-      <c r="I71" s="202"/>
-      <c r="J71" s="203"/>
-      <c r="K71" s="204"/>
-      <c r="L71" s="202"/>
-      <c r="M71" s="203"/>
-      <c r="N71" s="204"/>
-      <c r="O71" s="202"/>
-      <c r="P71" s="203"/>
-      <c r="Q71" s="203"/>
-      <c r="R71" s="203"/>
-      <c r="S71" s="204"/>
-      <c r="T71" s="206"/>
-      <c r="U71" s="202"/>
-      <c r="V71" s="203"/>
-      <c r="W71" s="204"/>
-      <c r="X71" s="210"/>
-      <c r="Y71" s="211"/>
-      <c r="Z71" s="212"/>
-      <c r="AA71" s="216"/>
-      <c r="AB71" s="217"/>
-      <c r="AC71" s="218"/>
-      <c r="AD71" s="216"/>
-      <c r="AE71" s="217"/>
-      <c r="AF71" s="218"/>
-      <c r="AG71" s="221"/>
-      <c r="AH71" s="222"/>
-      <c r="AI71" s="224"/>
-      <c r="AJ71" s="222"/>
+      <c r="B71" s="234"/>
+      <c r="C71" s="238"/>
+      <c r="D71" s="239"/>
+      <c r="E71" s="240"/>
+      <c r="F71" s="238"/>
+      <c r="G71" s="239"/>
+      <c r="H71" s="240"/>
+      <c r="I71" s="238"/>
+      <c r="J71" s="239"/>
+      <c r="K71" s="240"/>
+      <c r="L71" s="238"/>
+      <c r="M71" s="239"/>
+      <c r="N71" s="240"/>
+      <c r="O71" s="238"/>
+      <c r="P71" s="239"/>
+      <c r="Q71" s="239"/>
+      <c r="R71" s="239"/>
+      <c r="S71" s="240"/>
+      <c r="T71" s="234"/>
+      <c r="U71" s="238"/>
+      <c r="V71" s="239"/>
+      <c r="W71" s="240"/>
+      <c r="X71" s="250"/>
+      <c r="Y71" s="251"/>
+      <c r="Z71" s="252"/>
+      <c r="AA71" s="256"/>
+      <c r="AB71" s="257"/>
+      <c r="AC71" s="258"/>
+      <c r="AD71" s="256"/>
+      <c r="AE71" s="257"/>
+      <c r="AF71" s="258"/>
+      <c r="AG71" s="243"/>
+      <c r="AH71" s="244"/>
+      <c r="AI71" s="246"/>
+      <c r="AJ71" s="244"/>
       <c r="AK71" s="97"/>
     </row>
     <row r="72" spans="1:37" ht="12.5" customHeight="1">
       <c r="A72" s="96"/>
-      <c r="B72" s="198"/>
-      <c r="C72" s="198"/>
-      <c r="D72" s="198"/>
-      <c r="E72" s="198"/>
-      <c r="F72" s="198"/>
-      <c r="G72" s="198"/>
-      <c r="H72" s="198"/>
-      <c r="I72" s="198"/>
-      <c r="J72" s="198"/>
-      <c r="K72" s="198"/>
-      <c r="L72" s="198"/>
-      <c r="M72" s="198"/>
-      <c r="N72" s="198"/>
-      <c r="O72" s="198"/>
-      <c r="P72" s="198"/>
-      <c r="Q72" s="198"/>
-      <c r="R72" s="198"/>
-      <c r="S72" s="198"/>
-      <c r="T72" s="198"/>
-      <c r="U72" s="198"/>
-      <c r="V72" s="198"/>
-      <c r="W72" s="198"/>
-      <c r="X72" s="197"/>
-      <c r="Y72" s="197"/>
-      <c r="Z72" s="197"/>
-      <c r="AA72" s="198"/>
-      <c r="AB72" s="198"/>
-      <c r="AC72" s="198"/>
-      <c r="AD72" s="198"/>
-      <c r="AE72" s="198"/>
-      <c r="AF72" s="198"/>
-      <c r="AG72" s="198"/>
-      <c r="AH72" s="198"/>
-      <c r="AI72" s="198"/>
-      <c r="AJ72" s="198"/>
+      <c r="B72" s="261"/>
+      <c r="C72" s="261"/>
+      <c r="D72" s="261"/>
+      <c r="E72" s="261"/>
+      <c r="F72" s="261"/>
+      <c r="G72" s="261"/>
+      <c r="H72" s="261"/>
+      <c r="I72" s="261"/>
+      <c r="J72" s="261"/>
+      <c r="K72" s="261"/>
+      <c r="L72" s="261"/>
+      <c r="M72" s="261"/>
+      <c r="N72" s="261"/>
+      <c r="O72" s="261"/>
+      <c r="P72" s="261"/>
+      <c r="Q72" s="261"/>
+      <c r="R72" s="261"/>
+      <c r="S72" s="261"/>
+      <c r="T72" s="261"/>
+      <c r="U72" s="261"/>
+      <c r="V72" s="261"/>
+      <c r="W72" s="261"/>
+      <c r="X72" s="260"/>
+      <c r="Y72" s="260"/>
+      <c r="Z72" s="260"/>
+      <c r="AA72" s="261"/>
+      <c r="AB72" s="261"/>
+      <c r="AC72" s="261"/>
+      <c r="AD72" s="261"/>
+      <c r="AE72" s="261"/>
+      <c r="AF72" s="261"/>
+      <c r="AG72" s="261"/>
+      <c r="AH72" s="261"/>
+      <c r="AI72" s="261"/>
+      <c r="AJ72" s="261"/>
       <c r="AK72" s="97"/>
     </row>
     <row r="73" spans="1:37" ht="12.5" customHeight="1">
       <c r="A73" s="96"/>
-      <c r="B73" s="198"/>
-      <c r="C73" s="198"/>
-      <c r="D73" s="198"/>
-      <c r="E73" s="198"/>
-      <c r="F73" s="198"/>
-      <c r="G73" s="198"/>
-      <c r="H73" s="198"/>
-      <c r="I73" s="198"/>
-      <c r="J73" s="198"/>
-      <c r="K73" s="198"/>
-      <c r="L73" s="198"/>
-      <c r="M73" s="198"/>
-      <c r="N73" s="198"/>
-      <c r="O73" s="198"/>
-      <c r="P73" s="198"/>
-      <c r="Q73" s="198"/>
-      <c r="R73" s="198"/>
-      <c r="S73" s="198"/>
-      <c r="T73" s="198"/>
-      <c r="U73" s="198"/>
-      <c r="V73" s="198"/>
-      <c r="W73" s="198"/>
-      <c r="X73" s="197"/>
-      <c r="Y73" s="197"/>
-      <c r="Z73" s="197"/>
-      <c r="AA73" s="198"/>
-      <c r="AB73" s="198"/>
-      <c r="AC73" s="198"/>
-      <c r="AD73" s="198"/>
-      <c r="AE73" s="198"/>
-      <c r="AF73" s="198"/>
-      <c r="AG73" s="198"/>
-      <c r="AH73" s="198"/>
-      <c r="AI73" s="198"/>
-      <c r="AJ73" s="198"/>
+      <c r="B73" s="261"/>
+      <c r="C73" s="261"/>
+      <c r="D73" s="261"/>
+      <c r="E73" s="261"/>
+      <c r="F73" s="261"/>
+      <c r="G73" s="261"/>
+      <c r="H73" s="261"/>
+      <c r="I73" s="261"/>
+      <c r="J73" s="261"/>
+      <c r="K73" s="261"/>
+      <c r="L73" s="261"/>
+      <c r="M73" s="261"/>
+      <c r="N73" s="261"/>
+      <c r="O73" s="261"/>
+      <c r="P73" s="261"/>
+      <c r="Q73" s="261"/>
+      <c r="R73" s="261"/>
+      <c r="S73" s="261"/>
+      <c r="T73" s="261"/>
+      <c r="U73" s="261"/>
+      <c r="V73" s="261"/>
+      <c r="W73" s="261"/>
+      <c r="X73" s="260"/>
+      <c r="Y73" s="260"/>
+      <c r="Z73" s="260"/>
+      <c r="AA73" s="261"/>
+      <c r="AB73" s="261"/>
+      <c r="AC73" s="261"/>
+      <c r="AD73" s="261"/>
+      <c r="AE73" s="261"/>
+      <c r="AF73" s="261"/>
+      <c r="AG73" s="261"/>
+      <c r="AH73" s="261"/>
+      <c r="AI73" s="261"/>
+      <c r="AJ73" s="261"/>
       <c r="AK73" s="97"/>
     </row>
     <row r="74" spans="1:37" ht="12.5" customHeight="1">
       <c r="A74" s="96"/>
-      <c r="B74" s="198"/>
-      <c r="C74" s="198"/>
-      <c r="D74" s="198"/>
-      <c r="E74" s="198"/>
-      <c r="F74" s="198"/>
-      <c r="G74" s="198"/>
-      <c r="H74" s="198"/>
-      <c r="I74" s="198"/>
-      <c r="J74" s="198"/>
-      <c r="K74" s="198"/>
-      <c r="L74" s="198"/>
-      <c r="M74" s="198"/>
-      <c r="N74" s="198"/>
-      <c r="O74" s="198"/>
-      <c r="P74" s="198"/>
-      <c r="Q74" s="198"/>
-      <c r="R74" s="198"/>
-      <c r="S74" s="198"/>
-      <c r="T74" s="198"/>
-      <c r="U74" s="198"/>
-      <c r="V74" s="198"/>
-      <c r="W74" s="198"/>
-      <c r="X74" s="197"/>
-      <c r="Y74" s="197"/>
-      <c r="Z74" s="197"/>
-      <c r="AA74" s="198"/>
-      <c r="AB74" s="198"/>
-      <c r="AC74" s="198"/>
-      <c r="AD74" s="198"/>
-      <c r="AE74" s="198"/>
-      <c r="AF74" s="198"/>
-      <c r="AG74" s="198"/>
-      <c r="AH74" s="198"/>
-      <c r="AI74" s="198"/>
-      <c r="AJ74" s="198"/>
+      <c r="B74" s="261"/>
+      <c r="C74" s="261"/>
+      <c r="D74" s="261"/>
+      <c r="E74" s="261"/>
+      <c r="F74" s="261"/>
+      <c r="G74" s="261"/>
+      <c r="H74" s="261"/>
+      <c r="I74" s="261"/>
+      <c r="J74" s="261"/>
+      <c r="K74" s="261"/>
+      <c r="L74" s="261"/>
+      <c r="M74" s="261"/>
+      <c r="N74" s="261"/>
+      <c r="O74" s="261"/>
+      <c r="P74" s="261"/>
+      <c r="Q74" s="261"/>
+      <c r="R74" s="261"/>
+      <c r="S74" s="261"/>
+      <c r="T74" s="261"/>
+      <c r="U74" s="261"/>
+      <c r="V74" s="261"/>
+      <c r="W74" s="261"/>
+      <c r="X74" s="260"/>
+      <c r="Y74" s="260"/>
+      <c r="Z74" s="260"/>
+      <c r="AA74" s="261"/>
+      <c r="AB74" s="261"/>
+      <c r="AC74" s="261"/>
+      <c r="AD74" s="261"/>
+      <c r="AE74" s="261"/>
+      <c r="AF74" s="261"/>
+      <c r="AG74" s="261"/>
+      <c r="AH74" s="261"/>
+      <c r="AI74" s="261"/>
+      <c r="AJ74" s="261"/>
       <c r="AK74" s="97"/>
     </row>
     <row r="75" spans="1:37" ht="12.5" customHeight="1">
       <c r="A75" s="96"/>
-      <c r="B75" s="198"/>
-      <c r="C75" s="198"/>
-      <c r="D75" s="198"/>
-      <c r="E75" s="198"/>
-      <c r="F75" s="198"/>
-      <c r="G75" s="198"/>
-      <c r="H75" s="198"/>
-      <c r="I75" s="198"/>
-      <c r="J75" s="198"/>
-      <c r="K75" s="198"/>
-      <c r="L75" s="198"/>
-      <c r="M75" s="198"/>
-      <c r="N75" s="198"/>
-      <c r="O75" s="198"/>
-      <c r="P75" s="198"/>
-      <c r="Q75" s="198"/>
-      <c r="R75" s="198"/>
-      <c r="S75" s="198"/>
-      <c r="T75" s="198"/>
-      <c r="U75" s="198"/>
-      <c r="V75" s="198"/>
-      <c r="W75" s="198"/>
-      <c r="X75" s="197"/>
-      <c r="Y75" s="197"/>
-      <c r="Z75" s="197"/>
-      <c r="AA75" s="198"/>
-      <c r="AB75" s="198"/>
-      <c r="AC75" s="198"/>
-      <c r="AD75" s="198"/>
-      <c r="AE75" s="198"/>
-      <c r="AF75" s="198"/>
-      <c r="AG75" s="198"/>
-      <c r="AH75" s="198"/>
-      <c r="AI75" s="198"/>
-      <c r="AJ75" s="198"/>
+      <c r="B75" s="261"/>
+      <c r="C75" s="261"/>
+      <c r="D75" s="261"/>
+      <c r="E75" s="261"/>
+      <c r="F75" s="261"/>
+      <c r="G75" s="261"/>
+      <c r="H75" s="261"/>
+      <c r="I75" s="261"/>
+      <c r="J75" s="261"/>
+      <c r="K75" s="261"/>
+      <c r="L75" s="261"/>
+      <c r="M75" s="261"/>
+      <c r="N75" s="261"/>
+      <c r="O75" s="261"/>
+      <c r="P75" s="261"/>
+      <c r="Q75" s="261"/>
+      <c r="R75" s="261"/>
+      <c r="S75" s="261"/>
+      <c r="T75" s="261"/>
+      <c r="U75" s="261"/>
+      <c r="V75" s="261"/>
+      <c r="W75" s="261"/>
+      <c r="X75" s="260"/>
+      <c r="Y75" s="260"/>
+      <c r="Z75" s="260"/>
+      <c r="AA75" s="261"/>
+      <c r="AB75" s="261"/>
+      <c r="AC75" s="261"/>
+      <c r="AD75" s="261"/>
+      <c r="AE75" s="261"/>
+      <c r="AF75" s="261"/>
+      <c r="AG75" s="261"/>
+      <c r="AH75" s="261"/>
+      <c r="AI75" s="261"/>
+      <c r="AJ75" s="261"/>
       <c r="AK75" s="97"/>
     </row>
     <row r="76" spans="1:37" ht="12.5" customHeight="1">
       <c r="A76" s="96"/>
-      <c r="B76" s="198"/>
-      <c r="C76" s="198"/>
-      <c r="D76" s="198"/>
-      <c r="E76" s="198"/>
-      <c r="F76" s="198"/>
-      <c r="G76" s="198"/>
-      <c r="H76" s="198"/>
-      <c r="I76" s="198"/>
-      <c r="J76" s="198"/>
-      <c r="K76" s="198"/>
-      <c r="L76" s="198"/>
-      <c r="M76" s="198"/>
-      <c r="N76" s="198"/>
-      <c r="O76" s="198"/>
-      <c r="P76" s="198"/>
-      <c r="Q76" s="198"/>
-      <c r="R76" s="198"/>
-      <c r="S76" s="198"/>
-      <c r="T76" s="198"/>
-      <c r="U76" s="198"/>
-      <c r="V76" s="198"/>
-      <c r="W76" s="198"/>
-      <c r="X76" s="197"/>
-      <c r="Y76" s="197"/>
-      <c r="Z76" s="197"/>
-      <c r="AA76" s="198"/>
-      <c r="AB76" s="198"/>
-      <c r="AC76" s="198"/>
-      <c r="AD76" s="198"/>
-      <c r="AE76" s="198"/>
-      <c r="AF76" s="198"/>
-      <c r="AG76" s="198"/>
-      <c r="AH76" s="198"/>
-      <c r="AI76" s="198"/>
-      <c r="AJ76" s="198"/>
+      <c r="B76" s="261"/>
+      <c r="C76" s="261"/>
+      <c r="D76" s="261"/>
+      <c r="E76" s="261"/>
+      <c r="F76" s="261"/>
+      <c r="G76" s="261"/>
+      <c r="H76" s="261"/>
+      <c r="I76" s="261"/>
+      <c r="J76" s="261"/>
+      <c r="K76" s="261"/>
+      <c r="L76" s="261"/>
+      <c r="M76" s="261"/>
+      <c r="N76" s="261"/>
+      <c r="O76" s="261"/>
+      <c r="P76" s="261"/>
+      <c r="Q76" s="261"/>
+      <c r="R76" s="261"/>
+      <c r="S76" s="261"/>
+      <c r="T76" s="261"/>
+      <c r="U76" s="261"/>
+      <c r="V76" s="261"/>
+      <c r="W76" s="261"/>
+      <c r="X76" s="260"/>
+      <c r="Y76" s="260"/>
+      <c r="Z76" s="260"/>
+      <c r="AA76" s="261"/>
+      <c r="AB76" s="261"/>
+      <c r="AC76" s="261"/>
+      <c r="AD76" s="261"/>
+      <c r="AE76" s="261"/>
+      <c r="AF76" s="261"/>
+      <c r="AG76" s="261"/>
+      <c r="AH76" s="261"/>
+      <c r="AI76" s="261"/>
+      <c r="AJ76" s="261"/>
       <c r="AK76" s="97"/>
     </row>
     <row r="77" spans="1:37" ht="12.5" customHeight="1">
       <c r="A77" s="96"/>
-      <c r="B77" s="198"/>
-      <c r="C77" s="198"/>
-      <c r="D77" s="198"/>
-      <c r="E77" s="198"/>
-      <c r="F77" s="198"/>
-      <c r="G77" s="198"/>
-      <c r="H77" s="198"/>
-      <c r="I77" s="198"/>
-      <c r="J77" s="198"/>
-      <c r="K77" s="198"/>
-      <c r="L77" s="198"/>
-      <c r="M77" s="198"/>
-      <c r="N77" s="198"/>
-      <c r="O77" s="198"/>
-      <c r="P77" s="198"/>
-      <c r="Q77" s="198"/>
-      <c r="R77" s="198"/>
-      <c r="S77" s="198"/>
-      <c r="T77" s="198"/>
-      <c r="U77" s="198"/>
-      <c r="V77" s="198"/>
-      <c r="W77" s="198"/>
-      <c r="X77" s="197"/>
-      <c r="Y77" s="197"/>
-      <c r="Z77" s="197"/>
-      <c r="AA77" s="198"/>
-      <c r="AB77" s="198"/>
-      <c r="AC77" s="198"/>
-      <c r="AD77" s="198"/>
-      <c r="AE77" s="198"/>
-      <c r="AF77" s="198"/>
-      <c r="AG77" s="198"/>
-      <c r="AH77" s="198"/>
-      <c r="AI77" s="198"/>
-      <c r="AJ77" s="198"/>
+      <c r="B77" s="261"/>
+      <c r="C77" s="261"/>
+      <c r="D77" s="261"/>
+      <c r="E77" s="261"/>
+      <c r="F77" s="261"/>
+      <c r="G77" s="261"/>
+      <c r="H77" s="261"/>
+      <c r="I77" s="261"/>
+      <c r="J77" s="261"/>
+      <c r="K77" s="261"/>
+      <c r="L77" s="261"/>
+      <c r="M77" s="261"/>
+      <c r="N77" s="261"/>
+      <c r="O77" s="261"/>
+      <c r="P77" s="261"/>
+      <c r="Q77" s="261"/>
+      <c r="R77" s="261"/>
+      <c r="S77" s="261"/>
+      <c r="T77" s="261"/>
+      <c r="U77" s="261"/>
+      <c r="V77" s="261"/>
+      <c r="W77" s="261"/>
+      <c r="X77" s="260"/>
+      <c r="Y77" s="260"/>
+      <c r="Z77" s="260"/>
+      <c r="AA77" s="261"/>
+      <c r="AB77" s="261"/>
+      <c r="AC77" s="261"/>
+      <c r="AD77" s="261"/>
+      <c r="AE77" s="261"/>
+      <c r="AF77" s="261"/>
+      <c r="AG77" s="261"/>
+      <c r="AH77" s="261"/>
+      <c r="AI77" s="261"/>
+      <c r="AJ77" s="261"/>
       <c r="AK77" s="97"/>
     </row>
     <row r="78" spans="1:37" ht="12.75" customHeight="1">
@@ -21378,64 +21602,87 @@
     </row>
   </sheetData>
   <mergeCells count="163">
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="G8:I9"/>
-    <mergeCell ref="J8:R9"/>
-    <mergeCell ref="S8:U9"/>
-    <mergeCell ref="V8:AD9"/>
-    <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="I3:AD3"/>
-    <mergeCell ref="G14:I15"/>
-    <mergeCell ref="J14:R15"/>
-    <mergeCell ref="S14:U15"/>
-    <mergeCell ref="V14:AD15"/>
-    <mergeCell ref="G16:I17"/>
-    <mergeCell ref="S16:U17"/>
-    <mergeCell ref="V16:AD17"/>
-    <mergeCell ref="G10:I11"/>
-    <mergeCell ref="J10:R11"/>
-    <mergeCell ref="S10:U11"/>
-    <mergeCell ref="V10:AD11"/>
-    <mergeCell ref="G12:I13"/>
-    <mergeCell ref="J12:R13"/>
-    <mergeCell ref="S12:U13"/>
-    <mergeCell ref="V12:AD13"/>
-    <mergeCell ref="G51:I52"/>
-    <mergeCell ref="J51:R52"/>
-    <mergeCell ref="S51:U52"/>
-    <mergeCell ref="V51:AD52"/>
-    <mergeCell ref="G53:I54"/>
-    <mergeCell ref="J53:R54"/>
-    <mergeCell ref="S53:U54"/>
-    <mergeCell ref="V53:AD54"/>
-    <mergeCell ref="G47:I48"/>
-    <mergeCell ref="J47:R48"/>
-    <mergeCell ref="S47:U48"/>
-    <mergeCell ref="V47:AD48"/>
-    <mergeCell ref="G49:I50"/>
-    <mergeCell ref="J49:R50"/>
-    <mergeCell ref="S49:U50"/>
-    <mergeCell ref="V49:AD50"/>
-    <mergeCell ref="G55:I56"/>
-    <mergeCell ref="S55:U56"/>
-    <mergeCell ref="V55:AD56"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:E61"/>
-    <mergeCell ref="F60:H61"/>
-    <mergeCell ref="I60:K61"/>
-    <mergeCell ref="L60:N61"/>
-    <mergeCell ref="O60:S61"/>
-    <mergeCell ref="T60:T61"/>
-    <mergeCell ref="U60:W61"/>
-    <mergeCell ref="X60:Z61"/>
-    <mergeCell ref="AA60:AC61"/>
-    <mergeCell ref="AD60:AF61"/>
+    <mergeCell ref="X76:Z77"/>
+    <mergeCell ref="AA76:AC77"/>
+    <mergeCell ref="AD76:AF77"/>
+    <mergeCell ref="AG76:AH77"/>
+    <mergeCell ref="AI76:AJ77"/>
+    <mergeCell ref="AG74:AH75"/>
+    <mergeCell ref="AI74:AJ75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:E77"/>
+    <mergeCell ref="F76:H77"/>
+    <mergeCell ref="I76:K77"/>
+    <mergeCell ref="L76:N77"/>
+    <mergeCell ref="O76:S77"/>
+    <mergeCell ref="T76:T77"/>
+    <mergeCell ref="U76:W77"/>
+    <mergeCell ref="O74:S75"/>
+    <mergeCell ref="T74:T75"/>
+    <mergeCell ref="U74:W75"/>
+    <mergeCell ref="X74:Z75"/>
+    <mergeCell ref="AA74:AC75"/>
+    <mergeCell ref="AD74:AF75"/>
+    <mergeCell ref="X72:Z73"/>
+    <mergeCell ref="AA72:AC73"/>
+    <mergeCell ref="AD72:AF73"/>
+    <mergeCell ref="AG72:AH73"/>
+    <mergeCell ref="AI72:AJ73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:E75"/>
+    <mergeCell ref="F74:H75"/>
+    <mergeCell ref="I74:K75"/>
+    <mergeCell ref="L74:N75"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:E73"/>
+    <mergeCell ref="F72:H73"/>
+    <mergeCell ref="I72:K73"/>
+    <mergeCell ref="L72:N73"/>
+    <mergeCell ref="O72:S73"/>
+    <mergeCell ref="T72:T73"/>
+    <mergeCell ref="U72:W73"/>
+    <mergeCell ref="O70:S71"/>
+    <mergeCell ref="T70:T71"/>
+    <mergeCell ref="U70:W71"/>
+    <mergeCell ref="X68:Z69"/>
+    <mergeCell ref="AA68:AC69"/>
+    <mergeCell ref="AD68:AF69"/>
+    <mergeCell ref="AG68:AH69"/>
+    <mergeCell ref="AI68:AJ69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:E71"/>
+    <mergeCell ref="F70:H71"/>
+    <mergeCell ref="I70:K71"/>
+    <mergeCell ref="L70:N71"/>
+    <mergeCell ref="AG70:AH71"/>
+    <mergeCell ref="AI70:AJ71"/>
+    <mergeCell ref="X70:Z71"/>
+    <mergeCell ref="AA70:AC71"/>
+    <mergeCell ref="AD70:AF71"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:E69"/>
+    <mergeCell ref="F68:H69"/>
+    <mergeCell ref="I68:K69"/>
+    <mergeCell ref="L68:N69"/>
+    <mergeCell ref="O68:S69"/>
+    <mergeCell ref="T68:T69"/>
+    <mergeCell ref="U68:W69"/>
+    <mergeCell ref="O66:S67"/>
+    <mergeCell ref="T66:T67"/>
+    <mergeCell ref="U66:W67"/>
+    <mergeCell ref="AD64:AF65"/>
+    <mergeCell ref="AG64:AH65"/>
+    <mergeCell ref="AI64:AJ65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:E67"/>
+    <mergeCell ref="F66:H67"/>
+    <mergeCell ref="I66:K67"/>
+    <mergeCell ref="L66:N67"/>
+    <mergeCell ref="AG66:AH67"/>
+    <mergeCell ref="AI66:AJ67"/>
+    <mergeCell ref="X66:Z67"/>
+    <mergeCell ref="AA66:AC67"/>
+    <mergeCell ref="AD66:AF67"/>
     <mergeCell ref="AG60:AJ61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="C62:E63"/>
@@ -21460,87 +21707,64 @@
     <mergeCell ref="AD62:AF63"/>
     <mergeCell ref="X64:Z65"/>
     <mergeCell ref="AA64:AC65"/>
-    <mergeCell ref="T68:T69"/>
-    <mergeCell ref="U68:W69"/>
-    <mergeCell ref="O66:S67"/>
-    <mergeCell ref="T66:T67"/>
-    <mergeCell ref="U66:W67"/>
-    <mergeCell ref="AD64:AF65"/>
-    <mergeCell ref="AG64:AH65"/>
-    <mergeCell ref="AI64:AJ65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:E67"/>
-    <mergeCell ref="F66:H67"/>
-    <mergeCell ref="I66:K67"/>
-    <mergeCell ref="L66:N67"/>
-    <mergeCell ref="AG66:AH67"/>
-    <mergeCell ref="AI66:AJ67"/>
-    <mergeCell ref="X66:Z67"/>
-    <mergeCell ref="AA66:AC67"/>
-    <mergeCell ref="AD66:AF67"/>
-    <mergeCell ref="O70:S71"/>
-    <mergeCell ref="T70:T71"/>
-    <mergeCell ref="U70:W71"/>
-    <mergeCell ref="X68:Z69"/>
-    <mergeCell ref="AA68:AC69"/>
-    <mergeCell ref="AD68:AF69"/>
-    <mergeCell ref="AG68:AH69"/>
-    <mergeCell ref="AI68:AJ69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:E71"/>
-    <mergeCell ref="F70:H71"/>
-    <mergeCell ref="I70:K71"/>
-    <mergeCell ref="L70:N71"/>
-    <mergeCell ref="AG70:AH71"/>
-    <mergeCell ref="AI70:AJ71"/>
-    <mergeCell ref="X70:Z71"/>
-    <mergeCell ref="AA70:AC71"/>
-    <mergeCell ref="AD70:AF71"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:E69"/>
-    <mergeCell ref="F68:H69"/>
-    <mergeCell ref="I68:K69"/>
-    <mergeCell ref="L68:N69"/>
-    <mergeCell ref="O68:S69"/>
-    <mergeCell ref="X72:Z73"/>
-    <mergeCell ref="AA72:AC73"/>
-    <mergeCell ref="AD72:AF73"/>
-    <mergeCell ref="AG72:AH73"/>
-    <mergeCell ref="AI72:AJ73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:E75"/>
-    <mergeCell ref="F74:H75"/>
-    <mergeCell ref="I74:K75"/>
-    <mergeCell ref="L74:N75"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:E73"/>
-    <mergeCell ref="F72:H73"/>
-    <mergeCell ref="I72:K73"/>
-    <mergeCell ref="L72:N73"/>
-    <mergeCell ref="O72:S73"/>
-    <mergeCell ref="T72:T73"/>
-    <mergeCell ref="U72:W73"/>
-    <mergeCell ref="X76:Z77"/>
-    <mergeCell ref="AA76:AC77"/>
-    <mergeCell ref="AD76:AF77"/>
-    <mergeCell ref="AG76:AH77"/>
-    <mergeCell ref="AI76:AJ77"/>
-    <mergeCell ref="AG74:AH75"/>
-    <mergeCell ref="AI74:AJ75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:E77"/>
-    <mergeCell ref="F76:H77"/>
-    <mergeCell ref="I76:K77"/>
-    <mergeCell ref="L76:N77"/>
-    <mergeCell ref="O76:S77"/>
-    <mergeCell ref="T76:T77"/>
-    <mergeCell ref="U76:W77"/>
-    <mergeCell ref="O74:S75"/>
-    <mergeCell ref="T74:T75"/>
-    <mergeCell ref="U74:W75"/>
-    <mergeCell ref="X74:Z75"/>
-    <mergeCell ref="AA74:AC75"/>
-    <mergeCell ref="AD74:AF75"/>
+    <mergeCell ref="G55:I56"/>
+    <mergeCell ref="S55:U56"/>
+    <mergeCell ref="V55:AD56"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:E61"/>
+    <mergeCell ref="F60:H61"/>
+    <mergeCell ref="I60:K61"/>
+    <mergeCell ref="L60:N61"/>
+    <mergeCell ref="O60:S61"/>
+    <mergeCell ref="T60:T61"/>
+    <mergeCell ref="U60:W61"/>
+    <mergeCell ref="X60:Z61"/>
+    <mergeCell ref="AA60:AC61"/>
+    <mergeCell ref="AD60:AF61"/>
+    <mergeCell ref="G51:I52"/>
+    <mergeCell ref="J51:R52"/>
+    <mergeCell ref="S51:U52"/>
+    <mergeCell ref="V51:AD52"/>
+    <mergeCell ref="G53:I54"/>
+    <mergeCell ref="J53:R54"/>
+    <mergeCell ref="S53:U54"/>
+    <mergeCell ref="V53:AD54"/>
+    <mergeCell ref="G47:I48"/>
+    <mergeCell ref="J47:R48"/>
+    <mergeCell ref="S47:U48"/>
+    <mergeCell ref="V47:AD48"/>
+    <mergeCell ref="G49:I50"/>
+    <mergeCell ref="J49:R50"/>
+    <mergeCell ref="S49:U50"/>
+    <mergeCell ref="V49:AD50"/>
+    <mergeCell ref="G14:I15"/>
+    <mergeCell ref="J14:R15"/>
+    <mergeCell ref="S14:U15"/>
+    <mergeCell ref="V14:AD15"/>
+    <mergeCell ref="G16:I17"/>
+    <mergeCell ref="S16:U17"/>
+    <mergeCell ref="V16:AD17"/>
+    <mergeCell ref="G10:I11"/>
+    <mergeCell ref="J10:R11"/>
+    <mergeCell ref="S10:U11"/>
+    <mergeCell ref="V10:AD11"/>
+    <mergeCell ref="G12:I13"/>
+    <mergeCell ref="J12:R13"/>
+    <mergeCell ref="S12:U13"/>
+    <mergeCell ref="V12:AD13"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="G8:I9"/>
+    <mergeCell ref="J8:R9"/>
+    <mergeCell ref="S8:U9"/>
+    <mergeCell ref="V8:AD9"/>
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="I3:AD3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -21574,31 +21798,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:167" ht="12.75" customHeight="1">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="195" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="196"/>
-      <c r="M1" s="196"/>
-      <c r="N1" s="196"/>
-      <c r="O1" s="196"/>
-      <c r="P1" s="196"/>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="196"/>
-      <c r="T1" s="196"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="196"/>
-      <c r="W1" s="196"/>
+      <c r="B1" s="195"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
+      <c r="V1" s="195"/>
+      <c r="W1" s="195"/>
     </row>
     <row r="2" spans="1:167" ht="13" customHeight="1">
       <c r="A2" s="141" t="s">
@@ -21657,10 +21881,10 @@
       <c r="Q3" s="142"/>
       <c r="R3" s="142"/>
       <c r="S3" s="142"/>
-      <c r="T3" s="195"/>
-      <c r="U3" s="195"/>
-      <c r="V3" s="195"/>
-      <c r="W3" s="195"/>
+      <c r="T3" s="192"/>
+      <c r="U3" s="192"/>
+      <c r="V3" s="192"/>
+      <c r="W3" s="192"/>
       <c r="X3" s="19"/>
       <c r="Y3" s="20"/>
       <c r="Z3" s="20"/>
@@ -24102,17 +24326,17 @@
       <c r="E92" s="80"/>
       <c r="F92" s="80"/>
       <c r="G92" s="80"/>
-      <c r="H92" s="192" t="s">
+      <c r="H92" s="196" t="s">
         <v>288</v>
       </c>
-      <c r="I92" s="192"/>
-      <c r="J92" s="192"/>
-      <c r="K92" s="192"/>
-      <c r="L92" s="192"/>
-      <c r="M92" s="192"/>
-      <c r="N92" s="192"/>
-      <c r="O92" s="192"/>
-      <c r="P92" s="192"/>
+      <c r="I92" s="196"/>
+      <c r="J92" s="196"/>
+      <c r="K92" s="196"/>
+      <c r="L92" s="196"/>
+      <c r="M92" s="196"/>
+      <c r="N92" s="196"/>
+      <c r="O92" s="196"/>
+      <c r="P92" s="196"/>
       <c r="Q92" s="50"/>
       <c r="R92" s="50"/>
       <c r="S92" s="52"/>
@@ -24129,15 +24353,15 @@
       <c r="E93" s="80"/>
       <c r="F93" s="80"/>
       <c r="G93" s="80"/>
-      <c r="H93" s="192"/>
-      <c r="I93" s="192"/>
-      <c r="J93" s="192"/>
-      <c r="K93" s="192"/>
-      <c r="L93" s="192"/>
-      <c r="M93" s="192"/>
-      <c r="N93" s="192"/>
-      <c r="O93" s="192"/>
-      <c r="P93" s="192"/>
+      <c r="H93" s="196"/>
+      <c r="I93" s="196"/>
+      <c r="J93" s="196"/>
+      <c r="K93" s="196"/>
+      <c r="L93" s="196"/>
+      <c r="M93" s="196"/>
+      <c r="N93" s="196"/>
+      <c r="O93" s="196"/>
+      <c r="P93" s="196"/>
       <c r="Q93" s="50"/>
       <c r="R93" s="50"/>
       <c r="S93" s="52"/>
@@ -24154,15 +24378,15 @@
       <c r="E94" s="80"/>
       <c r="F94" s="80"/>
       <c r="G94" s="80"/>
-      <c r="H94" s="192"/>
-      <c r="I94" s="192"/>
-      <c r="J94" s="192"/>
-      <c r="K94" s="192"/>
-      <c r="L94" s="192"/>
-      <c r="M94" s="192"/>
-      <c r="N94" s="192"/>
-      <c r="O94" s="192"/>
-      <c r="P94" s="192"/>
+      <c r="H94" s="196"/>
+      <c r="I94" s="196"/>
+      <c r="J94" s="196"/>
+      <c r="K94" s="196"/>
+      <c r="L94" s="196"/>
+      <c r="M94" s="196"/>
+      <c r="N94" s="196"/>
+      <c r="O94" s="196"/>
+      <c r="P94" s="196"/>
       <c r="Q94" s="50"/>
       <c r="R94" s="50"/>
       <c r="S94" s="52"/>
@@ -24672,6 +24896,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="K61:N61"/>
+    <mergeCell ref="K67:M67"/>
+    <mergeCell ref="H92:P94"/>
+    <mergeCell ref="K98:N98"/>
+    <mergeCell ref="K104:M104"/>
     <mergeCell ref="G3:S3"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="V3:W3"/>
@@ -24680,11 +24909,6 @@
     <mergeCell ref="G2:S2"/>
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="V2:W2"/>
-    <mergeCell ref="K61:N61"/>
-    <mergeCell ref="K67:M67"/>
-    <mergeCell ref="H92:P94"/>
-    <mergeCell ref="K98:N98"/>
-    <mergeCell ref="K104:M104"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -24719,31 +24943,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:167" ht="12.75" customHeight="1">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="195" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="196"/>
-      <c r="M1" s="196"/>
-      <c r="N1" s="196"/>
-      <c r="O1" s="196"/>
-      <c r="P1" s="196"/>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="196"/>
-      <c r="T1" s="196"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="196"/>
-      <c r="W1" s="196"/>
+      <c r="B1" s="195"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
+      <c r="V1" s="195"/>
+      <c r="W1" s="195"/>
     </row>
     <row r="2" spans="1:167" ht="13" customHeight="1">
       <c r="A2" s="141" t="s">
@@ -24802,10 +25026,10 @@
       <c r="Q3" s="142"/>
       <c r="R3" s="142"/>
       <c r="S3" s="142"/>
-      <c r="T3" s="195"/>
-      <c r="U3" s="195"/>
-      <c r="V3" s="195"/>
-      <c r="W3" s="195"/>
+      <c r="T3" s="192"/>
+      <c r="U3" s="192"/>
+      <c r="V3" s="192"/>
+      <c r="W3" s="192"/>
       <c r="X3" s="19"/>
       <c r="Y3" s="20"/>
       <c r="Z3" s="20"/>
@@ -27213,17 +27437,17 @@
       <c r="E92" s="80"/>
       <c r="F92" s="80"/>
       <c r="G92" s="80"/>
-      <c r="H92" s="192" t="s">
+      <c r="H92" s="196" t="s">
         <v>294</v>
       </c>
-      <c r="I92" s="192"/>
-      <c r="J92" s="192"/>
-      <c r="K92" s="192"/>
-      <c r="L92" s="192"/>
-      <c r="M92" s="192"/>
-      <c r="N92" s="192"/>
-      <c r="O92" s="192"/>
-      <c r="P92" s="192"/>
+      <c r="I92" s="196"/>
+      <c r="J92" s="196"/>
+      <c r="K92" s="196"/>
+      <c r="L92" s="196"/>
+      <c r="M92" s="196"/>
+      <c r="N92" s="196"/>
+      <c r="O92" s="196"/>
+      <c r="P92" s="196"/>
       <c r="Q92" s="50"/>
       <c r="R92" s="50"/>
       <c r="S92" s="52"/>
@@ -27240,15 +27464,15 @@
       <c r="E93" s="80"/>
       <c r="F93" s="80"/>
       <c r="G93" s="80"/>
-      <c r="H93" s="192"/>
-      <c r="I93" s="192"/>
-      <c r="J93" s="192"/>
-      <c r="K93" s="192"/>
-      <c r="L93" s="192"/>
-      <c r="M93" s="192"/>
-      <c r="N93" s="192"/>
-      <c r="O93" s="192"/>
-      <c r="P93" s="192"/>
+      <c r="H93" s="196"/>
+      <c r="I93" s="196"/>
+      <c r="J93" s="196"/>
+      <c r="K93" s="196"/>
+      <c r="L93" s="196"/>
+      <c r="M93" s="196"/>
+      <c r="N93" s="196"/>
+      <c r="O93" s="196"/>
+      <c r="P93" s="196"/>
       <c r="Q93" s="50"/>
       <c r="R93" s="50"/>
       <c r="S93" s="52"/>
@@ -27265,15 +27489,15 @@
       <c r="E94" s="80"/>
       <c r="F94" s="80"/>
       <c r="G94" s="80"/>
-      <c r="H94" s="192"/>
-      <c r="I94" s="192"/>
-      <c r="J94" s="192"/>
-      <c r="K94" s="192"/>
-      <c r="L94" s="192"/>
-      <c r="M94" s="192"/>
-      <c r="N94" s="192"/>
-      <c r="O94" s="192"/>
-      <c r="P94" s="192"/>
+      <c r="H94" s="196"/>
+      <c r="I94" s="196"/>
+      <c r="J94" s="196"/>
+      <c r="K94" s="196"/>
+      <c r="L94" s="196"/>
+      <c r="M94" s="196"/>
+      <c r="N94" s="196"/>
+      <c r="O94" s="196"/>
+      <c r="P94" s="196"/>
       <c r="Q94" s="50"/>
       <c r="R94" s="50"/>
       <c r="S94" s="52"/>
@@ -27783,6 +28007,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="K61:N61"/>
+    <mergeCell ref="K67:M67"/>
+    <mergeCell ref="H92:P94"/>
+    <mergeCell ref="K98:N98"/>
+    <mergeCell ref="K104:M104"/>
     <mergeCell ref="K24:N24"/>
     <mergeCell ref="K30:M30"/>
     <mergeCell ref="F55:R57"/>
@@ -27794,11 +28023,6 @@
     <mergeCell ref="G3:S3"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="V3:W3"/>
-    <mergeCell ref="K61:N61"/>
-    <mergeCell ref="K67:M67"/>
-    <mergeCell ref="H92:P94"/>
-    <mergeCell ref="K98:N98"/>
-    <mergeCell ref="K104:M104"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -28360,15 +28584,15 @@
       <c r="R6" s="30"/>
       <c r="S6" s="30"/>
       <c r="T6" s="31"/>
-      <c r="U6" s="266" t="s">
+      <c r="U6" s="269" t="s">
         <v>170</v>
       </c>
-      <c r="V6" s="267"/>
-      <c r="W6" s="267"/>
-      <c r="X6" s="267"/>
-      <c r="Y6" s="267"/>
-      <c r="Z6" s="267"/>
-      <c r="AA6" s="268"/>
+      <c r="V6" s="270"/>
+      <c r="W6" s="270"/>
+      <c r="X6" s="270"/>
+      <c r="Y6" s="270"/>
+      <c r="Z6" s="270"/>
+      <c r="AA6" s="271"/>
       <c r="AB6" s="63"/>
       <c r="AC6" s="30"/>
       <c r="AD6" s="30"/>
@@ -28405,15 +28629,15 @@
       <c r="R7" s="30"/>
       <c r="S7" s="30"/>
       <c r="T7" s="31"/>
-      <c r="U7" s="266" t="s">
+      <c r="U7" s="269" t="s">
         <v>170</v>
       </c>
-      <c r="V7" s="267"/>
-      <c r="W7" s="267"/>
-      <c r="X7" s="267"/>
-      <c r="Y7" s="267"/>
-      <c r="Z7" s="267"/>
-      <c r="AA7" s="268"/>
+      <c r="V7" s="270"/>
+      <c r="W7" s="270"/>
+      <c r="X7" s="270"/>
+      <c r="Y7" s="270"/>
+      <c r="Z7" s="270"/>
+      <c r="AA7" s="271"/>
       <c r="AB7" s="63"/>
       <c r="AC7" s="30"/>
       <c r="AD7" s="30"/>
@@ -28450,15 +28674,15 @@
       <c r="R8" s="30"/>
       <c r="S8" s="30"/>
       <c r="T8" s="31"/>
-      <c r="U8" s="266" t="s">
+      <c r="U8" s="269" t="s">
         <v>171</v>
       </c>
-      <c r="V8" s="267"/>
-      <c r="W8" s="267"/>
-      <c r="X8" s="267"/>
-      <c r="Y8" s="267"/>
-      <c r="Z8" s="267"/>
-      <c r="AA8" s="268"/>
+      <c r="V8" s="270"/>
+      <c r="W8" s="270"/>
+      <c r="X8" s="270"/>
+      <c r="Y8" s="270"/>
+      <c r="Z8" s="270"/>
+      <c r="AA8" s="271"/>
       <c r="AB8" s="63"/>
       <c r="AC8" s="30"/>
       <c r="AD8" s="30"/>
@@ -28495,15 +28719,15 @@
       <c r="R9" s="32"/>
       <c r="S9" s="32"/>
       <c r="T9" s="58"/>
-      <c r="U9" s="266" t="s">
+      <c r="U9" s="269" t="s">
         <v>171</v>
       </c>
-      <c r="V9" s="267"/>
-      <c r="W9" s="267"/>
-      <c r="X9" s="267"/>
-      <c r="Y9" s="267"/>
-      <c r="Z9" s="267"/>
-      <c r="AA9" s="268"/>
+      <c r="V9" s="270"/>
+      <c r="W9" s="270"/>
+      <c r="X9" s="270"/>
+      <c r="Y9" s="270"/>
+      <c r="Z9" s="270"/>
+      <c r="AA9" s="271"/>
       <c r="AB9" s="63"/>
       <c r="AC9" s="30"/>
       <c r="AD9" s="30"/>
@@ -28542,15 +28766,15 @@
       <c r="R10" s="32"/>
       <c r="S10" s="32"/>
       <c r="T10" s="58"/>
-      <c r="U10" s="269" t="s">
+      <c r="U10" s="272" t="s">
         <v>172</v>
       </c>
-      <c r="V10" s="270"/>
-      <c r="W10" s="270"/>
-      <c r="X10" s="270"/>
-      <c r="Y10" s="270"/>
-      <c r="Z10" s="270"/>
-      <c r="AA10" s="271"/>
+      <c r="V10" s="273"/>
+      <c r="W10" s="273"/>
+      <c r="X10" s="273"/>
+      <c r="Y10" s="273"/>
+      <c r="Z10" s="273"/>
+      <c r="AA10" s="274"/>
       <c r="AB10" s="30"/>
       <c r="AC10" s="30"/>
       <c r="AD10" s="30"/>
@@ -28589,15 +28813,15 @@
       <c r="R11" s="32"/>
       <c r="S11" s="32"/>
       <c r="T11" s="58"/>
-      <c r="U11" s="272" t="s">
+      <c r="U11" s="263" t="s">
         <v>173</v>
       </c>
-      <c r="V11" s="273"/>
-      <c r="W11" s="273"/>
-      <c r="X11" s="273"/>
-      <c r="Y11" s="273"/>
-      <c r="Z11" s="273"/>
-      <c r="AA11" s="274"/>
+      <c r="V11" s="264"/>
+      <c r="W11" s="264"/>
+      <c r="X11" s="264"/>
+      <c r="Y11" s="264"/>
+      <c r="Z11" s="264"/>
+      <c r="AA11" s="265"/>
       <c r="AB11" s="30"/>
       <c r="AC11" s="30"/>
       <c r="AD11" s="30"/>
@@ -28632,15 +28856,15 @@
       <c r="R12" s="32"/>
       <c r="S12" s="32"/>
       <c r="T12" s="58"/>
-      <c r="U12" s="272" t="s">
+      <c r="U12" s="263" t="s">
         <v>174</v>
       </c>
-      <c r="V12" s="273"/>
-      <c r="W12" s="273"/>
-      <c r="X12" s="273"/>
-      <c r="Y12" s="273"/>
-      <c r="Z12" s="273"/>
-      <c r="AA12" s="274"/>
+      <c r="V12" s="264"/>
+      <c r="W12" s="264"/>
+      <c r="X12" s="264"/>
+      <c r="Y12" s="264"/>
+      <c r="Z12" s="264"/>
+      <c r="AA12" s="265"/>
       <c r="AB12" s="30"/>
       <c r="AC12" s="30"/>
       <c r="AD12" s="30"/>
@@ -28677,15 +28901,15 @@
       <c r="R13" s="32"/>
       <c r="S13" s="32"/>
       <c r="T13" s="58"/>
-      <c r="U13" s="272" t="s">
+      <c r="U13" s="263" t="s">
         <v>175</v>
       </c>
-      <c r="V13" s="273"/>
-      <c r="W13" s="273"/>
-      <c r="X13" s="273"/>
-      <c r="Y13" s="273"/>
-      <c r="Z13" s="273"/>
-      <c r="AA13" s="274"/>
+      <c r="V13" s="264"/>
+      <c r="W13" s="264"/>
+      <c r="X13" s="264"/>
+      <c r="Y13" s="264"/>
+      <c r="Z13" s="264"/>
+      <c r="AA13" s="265"/>
       <c r="AB13" s="30"/>
       <c r="AC13" s="30"/>
       <c r="AD13" s="30"/>
@@ -28722,15 +28946,15 @@
       <c r="R14" s="32"/>
       <c r="S14" s="30"/>
       <c r="T14" s="31"/>
-      <c r="U14" s="272" t="s">
+      <c r="U14" s="263" t="s">
         <v>178</v>
       </c>
-      <c r="V14" s="273"/>
-      <c r="W14" s="273"/>
-      <c r="X14" s="273"/>
-      <c r="Y14" s="273"/>
-      <c r="Z14" s="273"/>
-      <c r="AA14" s="274"/>
+      <c r="V14" s="264"/>
+      <c r="W14" s="264"/>
+      <c r="X14" s="264"/>
+      <c r="Y14" s="264"/>
+      <c r="Z14" s="264"/>
+      <c r="AA14" s="265"/>
       <c r="AB14" s="30"/>
       <c r="AC14" s="30"/>
       <c r="AD14" s="30"/>
@@ -28767,15 +28991,15 @@
       <c r="R15" s="30"/>
       <c r="S15" s="32"/>
       <c r="T15" s="58"/>
-      <c r="U15" s="269" t="s">
+      <c r="U15" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="V15" s="270"/>
-      <c r="W15" s="270"/>
-      <c r="X15" s="270"/>
-      <c r="Y15" s="270"/>
-      <c r="Z15" s="270"/>
-      <c r="AA15" s="271"/>
+      <c r="V15" s="273"/>
+      <c r="W15" s="273"/>
+      <c r="X15" s="273"/>
+      <c r="Y15" s="273"/>
+      <c r="Z15" s="273"/>
+      <c r="AA15" s="274"/>
       <c r="AB15" s="30"/>
       <c r="AC15" s="30"/>
       <c r="AD15" s="30"/>
@@ -28812,15 +29036,15 @@
       <c r="R16" s="30"/>
       <c r="S16" s="30"/>
       <c r="T16" s="31"/>
-      <c r="U16" s="269" t="s">
+      <c r="U16" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="V16" s="270"/>
-      <c r="W16" s="270"/>
-      <c r="X16" s="270"/>
-      <c r="Y16" s="270"/>
-      <c r="Z16" s="270"/>
-      <c r="AA16" s="271"/>
+      <c r="V16" s="273"/>
+      <c r="W16" s="273"/>
+      <c r="X16" s="273"/>
+      <c r="Y16" s="273"/>
+      <c r="Z16" s="273"/>
+      <c r="AA16" s="274"/>
       <c r="AB16" s="30"/>
       <c r="AC16" s="30"/>
       <c r="AD16" s="30"/>
@@ -28857,15 +29081,15 @@
       <c r="R17" s="30"/>
       <c r="S17" s="30"/>
       <c r="T17" s="31"/>
-      <c r="U17" s="272" t="s">
+      <c r="U17" s="263" t="s">
         <v>177</v>
       </c>
-      <c r="V17" s="273"/>
-      <c r="W17" s="273"/>
-      <c r="X17" s="273"/>
-      <c r="Y17" s="273"/>
-      <c r="Z17" s="273"/>
-      <c r="AA17" s="274"/>
+      <c r="V17" s="264"/>
+      <c r="W17" s="264"/>
+      <c r="X17" s="264"/>
+      <c r="Y17" s="264"/>
+      <c r="Z17" s="264"/>
+      <c r="AA17" s="265"/>
       <c r="AB17" s="30"/>
       <c r="AC17" s="30"/>
       <c r="AD17" s="30"/>
@@ -28900,13 +29124,13 @@
       <c r="R18" s="30"/>
       <c r="S18" s="30"/>
       <c r="T18" s="31"/>
-      <c r="U18" s="272"/>
-      <c r="V18" s="273"/>
-      <c r="W18" s="273"/>
-      <c r="X18" s="273"/>
-      <c r="Y18" s="273"/>
-      <c r="Z18" s="273"/>
-      <c r="AA18" s="274"/>
+      <c r="U18" s="263"/>
+      <c r="V18" s="264"/>
+      <c r="W18" s="264"/>
+      <c r="X18" s="264"/>
+      <c r="Y18" s="264"/>
+      <c r="Z18" s="264"/>
+      <c r="AA18" s="265"/>
       <c r="AB18" s="30"/>
       <c r="AC18" s="30"/>
       <c r="AD18" s="30"/>
@@ -28935,13 +29159,13 @@
       <c r="R19" s="30"/>
       <c r="S19" s="30"/>
       <c r="T19" s="31"/>
-      <c r="U19" s="272"/>
-      <c r="V19" s="273"/>
-      <c r="W19" s="273"/>
-      <c r="X19" s="273"/>
-      <c r="Y19" s="273"/>
-      <c r="Z19" s="273"/>
-      <c r="AA19" s="274"/>
+      <c r="U19" s="263"/>
+      <c r="V19" s="264"/>
+      <c r="W19" s="264"/>
+      <c r="X19" s="264"/>
+      <c r="Y19" s="264"/>
+      <c r="Z19" s="264"/>
+      <c r="AA19" s="265"/>
       <c r="AB19" s="30"/>
       <c r="AC19" s="30"/>
       <c r="AD19" s="30"/>
@@ -28972,13 +29196,13 @@
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="58"/>
-      <c r="U20" s="272"/>
-      <c r="V20" s="273"/>
-      <c r="W20" s="273"/>
-      <c r="X20" s="273"/>
-      <c r="Y20" s="273"/>
-      <c r="Z20" s="273"/>
-      <c r="AA20" s="274"/>
+      <c r="U20" s="263"/>
+      <c r="V20" s="264"/>
+      <c r="W20" s="264"/>
+      <c r="X20" s="264"/>
+      <c r="Y20" s="264"/>
+      <c r="Z20" s="264"/>
+      <c r="AA20" s="265"/>
       <c r="AB20" s="30"/>
       <c r="AC20" s="30"/>
       <c r="AD20" s="30"/>
@@ -29014,13 +29238,13 @@
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="58"/>
-      <c r="U21" s="272"/>
-      <c r="V21" s="273"/>
-      <c r="W21" s="273"/>
-      <c r="X21" s="273"/>
-      <c r="Y21" s="273"/>
-      <c r="Z21" s="273"/>
-      <c r="AA21" s="274"/>
+      <c r="U21" s="263"/>
+      <c r="V21" s="264"/>
+      <c r="W21" s="264"/>
+      <c r="X21" s="264"/>
+      <c r="Y21" s="264"/>
+      <c r="Z21" s="264"/>
+      <c r="AA21" s="265"/>
       <c r="AB21" s="30"/>
       <c r="AC21" s="30"/>
       <c r="AD21" s="30"/>
@@ -29182,13 +29406,13 @@
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="58"/>
-      <c r="U25" s="263"/>
-      <c r="V25" s="264"/>
-      <c r="W25" s="264"/>
-      <c r="X25" s="264"/>
-      <c r="Y25" s="264"/>
-      <c r="Z25" s="264"/>
-      <c r="AA25" s="265"/>
+      <c r="U25" s="266"/>
+      <c r="V25" s="267"/>
+      <c r="W25" s="267"/>
+      <c r="X25" s="267"/>
+      <c r="Y25" s="267"/>
+      <c r="Z25" s="267"/>
+      <c r="AA25" s="268"/>
       <c r="AB25" s="30"/>
       <c r="AC25" s="30"/>
       <c r="AD25" s="30"/>
@@ -29224,15 +29448,15 @@
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="58"/>
-      <c r="U26" s="263" t="s">
+      <c r="U26" s="266" t="s">
         <v>270</v>
       </c>
-      <c r="V26" s="264"/>
-      <c r="W26" s="264"/>
-      <c r="X26" s="264"/>
-      <c r="Y26" s="264"/>
-      <c r="Z26" s="264"/>
-      <c r="AA26" s="265"/>
+      <c r="V26" s="267"/>
+      <c r="W26" s="267"/>
+      <c r="X26" s="267"/>
+      <c r="Y26" s="267"/>
+      <c r="Z26" s="267"/>
+      <c r="AA26" s="268"/>
       <c r="AB26" s="30"/>
       <c r="AC26" s="30"/>
       <c r="AD26" s="30"/>
@@ -29892,17 +30116,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="U17:AA17"/>
-    <mergeCell ref="U18:AA18"/>
-    <mergeCell ref="U20:AA20"/>
-    <mergeCell ref="U21:AA21"/>
-    <mergeCell ref="U19:AA19"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AF2:AG2"/>
     <mergeCell ref="U25:AA25"/>
     <mergeCell ref="U26:AA26"/>
     <mergeCell ref="A3:F3"/>
@@ -29919,6 +30132,17 @@
     <mergeCell ref="U14:AA14"/>
     <mergeCell ref="U15:AA15"/>
     <mergeCell ref="U16:AA16"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="U17:AA17"/>
+    <mergeCell ref="U18:AA18"/>
+    <mergeCell ref="U20:AA20"/>
+    <mergeCell ref="U21:AA21"/>
+    <mergeCell ref="U19:AA19"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -30474,15 +30698,15 @@
       <c r="R6" s="30"/>
       <c r="S6" s="30"/>
       <c r="T6" s="31"/>
-      <c r="U6" s="266" t="s">
+      <c r="U6" s="269" t="s">
         <v>170</v>
       </c>
-      <c r="V6" s="267"/>
-      <c r="W6" s="267"/>
-      <c r="X6" s="267"/>
-      <c r="Y6" s="267"/>
-      <c r="Z6" s="267"/>
-      <c r="AA6" s="268"/>
+      <c r="V6" s="270"/>
+      <c r="W6" s="270"/>
+      <c r="X6" s="270"/>
+      <c r="Y6" s="270"/>
+      <c r="Z6" s="270"/>
+      <c r="AA6" s="271"/>
       <c r="AB6" s="63"/>
       <c r="AC6" s="30"/>
       <c r="AD6" s="30"/>
@@ -30517,15 +30741,15 @@
       <c r="R7" s="30"/>
       <c r="S7" s="30"/>
       <c r="T7" s="31"/>
-      <c r="U7" s="266" t="s">
+      <c r="U7" s="269" t="s">
         <v>170</v>
       </c>
-      <c r="V7" s="267"/>
-      <c r="W7" s="267"/>
-      <c r="X7" s="267"/>
-      <c r="Y7" s="267"/>
-      <c r="Z7" s="267"/>
-      <c r="AA7" s="268"/>
+      <c r="V7" s="270"/>
+      <c r="W7" s="270"/>
+      <c r="X7" s="270"/>
+      <c r="Y7" s="270"/>
+      <c r="Z7" s="270"/>
+      <c r="AA7" s="271"/>
       <c r="AB7" s="63"/>
       <c r="AC7" s="30"/>
       <c r="AD7" s="30"/>
@@ -30560,15 +30784,15 @@
       <c r="R8" s="30"/>
       <c r="S8" s="30"/>
       <c r="T8" s="31"/>
-      <c r="U8" s="266" t="s">
+      <c r="U8" s="269" t="s">
         <v>171</v>
       </c>
-      <c r="V8" s="267"/>
-      <c r="W8" s="267"/>
-      <c r="X8" s="267"/>
-      <c r="Y8" s="267"/>
-      <c r="Z8" s="267"/>
-      <c r="AA8" s="268"/>
+      <c r="V8" s="270"/>
+      <c r="W8" s="270"/>
+      <c r="X8" s="270"/>
+      <c r="Y8" s="270"/>
+      <c r="Z8" s="270"/>
+      <c r="AA8" s="271"/>
       <c r="AB8" s="63"/>
       <c r="AC8" s="30"/>
       <c r="AD8" s="30"/>
@@ -30603,15 +30827,15 @@
       <c r="R9" s="32"/>
       <c r="S9" s="32"/>
       <c r="T9" s="58"/>
-      <c r="U9" s="266" t="s">
+      <c r="U9" s="269" t="s">
         <v>171</v>
       </c>
-      <c r="V9" s="267"/>
-      <c r="W9" s="267"/>
-      <c r="X9" s="267"/>
-      <c r="Y9" s="267"/>
-      <c r="Z9" s="267"/>
-      <c r="AA9" s="268"/>
+      <c r="V9" s="270"/>
+      <c r="W9" s="270"/>
+      <c r="X9" s="270"/>
+      <c r="Y9" s="270"/>
+      <c r="Z9" s="270"/>
+      <c r="AA9" s="271"/>
       <c r="AB9" s="63"/>
       <c r="AC9" s="30"/>
       <c r="AD9" s="30"/>
@@ -30648,15 +30872,15 @@
       <c r="R10" s="32"/>
       <c r="S10" s="32"/>
       <c r="T10" s="58"/>
-      <c r="U10" s="269" t="s">
+      <c r="U10" s="272" t="s">
         <v>172</v>
       </c>
-      <c r="V10" s="270"/>
-      <c r="W10" s="270"/>
-      <c r="X10" s="270"/>
-      <c r="Y10" s="270"/>
-      <c r="Z10" s="270"/>
-      <c r="AA10" s="271"/>
+      <c r="V10" s="273"/>
+      <c r="W10" s="273"/>
+      <c r="X10" s="273"/>
+      <c r="Y10" s="273"/>
+      <c r="Z10" s="273"/>
+      <c r="AA10" s="274"/>
       <c r="AB10" s="30"/>
       <c r="AC10" s="30"/>
       <c r="AD10" s="30"/>
@@ -30689,15 +30913,15 @@
       <c r="R11" s="32"/>
       <c r="S11" s="32"/>
       <c r="T11" s="58"/>
-      <c r="U11" s="272" t="s">
+      <c r="U11" s="263" t="s">
         <v>174</v>
       </c>
-      <c r="V11" s="273"/>
-      <c r="W11" s="273"/>
-      <c r="X11" s="273"/>
-      <c r="Y11" s="273"/>
-      <c r="Z11" s="273"/>
-      <c r="AA11" s="274"/>
+      <c r="V11" s="264"/>
+      <c r="W11" s="264"/>
+      <c r="X11" s="264"/>
+      <c r="Y11" s="264"/>
+      <c r="Z11" s="264"/>
+      <c r="AA11" s="265"/>
       <c r="AB11" s="30"/>
       <c r="AC11" s="30"/>
       <c r="AD11" s="30"/>
@@ -30732,15 +30956,15 @@
       <c r="R12" s="30"/>
       <c r="S12" s="30"/>
       <c r="T12" s="31"/>
-      <c r="U12" s="272" t="s">
+      <c r="U12" s="263" t="s">
         <v>177</v>
       </c>
-      <c r="V12" s="273"/>
-      <c r="W12" s="273"/>
-      <c r="X12" s="273"/>
-      <c r="Y12" s="273"/>
-      <c r="Z12" s="273"/>
-      <c r="AA12" s="274"/>
+      <c r="V12" s="264"/>
+      <c r="W12" s="264"/>
+      <c r="X12" s="264"/>
+      <c r="Y12" s="264"/>
+      <c r="Z12" s="264"/>
+      <c r="AA12" s="265"/>
       <c r="AB12" s="30"/>
       <c r="AC12" s="30"/>
       <c r="AD12" s="30"/>
@@ -30773,13 +30997,13 @@
       <c r="R13" s="30"/>
       <c r="S13" s="30"/>
       <c r="T13" s="31"/>
-      <c r="U13" s="272"/>
-      <c r="V13" s="273"/>
-      <c r="W13" s="273"/>
-      <c r="X13" s="273"/>
-      <c r="Y13" s="273"/>
-      <c r="Z13" s="273"/>
-      <c r="AA13" s="274"/>
+      <c r="U13" s="263"/>
+      <c r="V13" s="264"/>
+      <c r="W13" s="264"/>
+      <c r="X13" s="264"/>
+      <c r="Y13" s="264"/>
+      <c r="Z13" s="264"/>
+      <c r="AA13" s="265"/>
       <c r="AB13" s="30"/>
       <c r="AC13" s="30"/>
       <c r="AD13" s="30"/>
@@ -30808,13 +31032,13 @@
       <c r="R14" s="32"/>
       <c r="S14" s="30"/>
       <c r="T14" s="31"/>
-      <c r="U14" s="272"/>
-      <c r="V14" s="273"/>
-      <c r="W14" s="273"/>
-      <c r="X14" s="273"/>
-      <c r="Y14" s="273"/>
-      <c r="Z14" s="273"/>
-      <c r="AA14" s="274"/>
+      <c r="U14" s="263"/>
+      <c r="V14" s="264"/>
+      <c r="W14" s="264"/>
+      <c r="X14" s="264"/>
+      <c r="Y14" s="264"/>
+      <c r="Z14" s="264"/>
+      <c r="AA14" s="265"/>
       <c r="AB14" s="30"/>
       <c r="AC14" s="30"/>
       <c r="AD14" s="30"/>
@@ -30845,13 +31069,13 @@
       <c r="R15" s="30"/>
       <c r="S15" s="32"/>
       <c r="T15" s="58"/>
-      <c r="U15" s="269"/>
-      <c r="V15" s="270"/>
-      <c r="W15" s="270"/>
-      <c r="X15" s="270"/>
-      <c r="Y15" s="270"/>
-      <c r="Z15" s="270"/>
-      <c r="AA15" s="271"/>
+      <c r="U15" s="272"/>
+      <c r="V15" s="273"/>
+      <c r="W15" s="273"/>
+      <c r="X15" s="273"/>
+      <c r="Y15" s="273"/>
+      <c r="Z15" s="273"/>
+      <c r="AA15" s="274"/>
       <c r="AB15" s="30"/>
       <c r="AC15" s="30"/>
       <c r="AD15" s="30"/>
@@ -30888,13 +31112,13 @@
       <c r="R16" s="30"/>
       <c r="S16" s="30"/>
       <c r="T16" s="31"/>
-      <c r="U16" s="269"/>
-      <c r="V16" s="270"/>
-      <c r="W16" s="270"/>
-      <c r="X16" s="270"/>
-      <c r="Y16" s="270"/>
-      <c r="Z16" s="270"/>
-      <c r="AA16" s="271"/>
+      <c r="U16" s="272"/>
+      <c r="V16" s="273"/>
+      <c r="W16" s="273"/>
+      <c r="X16" s="273"/>
+      <c r="Y16" s="273"/>
+      <c r="Z16" s="273"/>
+      <c r="AA16" s="274"/>
       <c r="AB16" s="30"/>
       <c r="AC16" s="30"/>
       <c r="AD16" s="30"/>
@@ -30931,13 +31155,13 @@
       <c r="R17" s="30"/>
       <c r="S17" s="30"/>
       <c r="T17" s="31"/>
-      <c r="U17" s="272"/>
-      <c r="V17" s="273"/>
-      <c r="W17" s="273"/>
-      <c r="X17" s="273"/>
-      <c r="Y17" s="273"/>
-      <c r="Z17" s="273"/>
-      <c r="AA17" s="274"/>
+      <c r="U17" s="263"/>
+      <c r="V17" s="264"/>
+      <c r="W17" s="264"/>
+      <c r="X17" s="264"/>
+      <c r="Y17" s="264"/>
+      <c r="Z17" s="264"/>
+      <c r="AA17" s="265"/>
       <c r="AB17" s="30"/>
       <c r="AC17" s="30"/>
       <c r="AD17" s="30"/>
@@ -30974,13 +31198,13 @@
       <c r="R18" s="30"/>
       <c r="S18" s="30"/>
       <c r="T18" s="31"/>
-      <c r="U18" s="272"/>
-      <c r="V18" s="273"/>
-      <c r="W18" s="273"/>
-      <c r="X18" s="273"/>
-      <c r="Y18" s="273"/>
-      <c r="Z18" s="273"/>
-      <c r="AA18" s="274"/>
+      <c r="U18" s="263"/>
+      <c r="V18" s="264"/>
+      <c r="W18" s="264"/>
+      <c r="X18" s="264"/>
+      <c r="Y18" s="264"/>
+      <c r="Z18" s="264"/>
+      <c r="AA18" s="265"/>
       <c r="AB18" s="30"/>
       <c r="AC18" s="30"/>
       <c r="AD18" s="30"/>
@@ -31017,13 +31241,13 @@
       <c r="R19" s="30"/>
       <c r="S19" s="30"/>
       <c r="T19" s="31"/>
-      <c r="U19" s="272"/>
-      <c r="V19" s="273"/>
-      <c r="W19" s="273"/>
-      <c r="X19" s="273"/>
-      <c r="Y19" s="273"/>
-      <c r="Z19" s="273"/>
-      <c r="AA19" s="274"/>
+      <c r="U19" s="263"/>
+      <c r="V19" s="264"/>
+      <c r="W19" s="264"/>
+      <c r="X19" s="264"/>
+      <c r="Y19" s="264"/>
+      <c r="Z19" s="264"/>
+      <c r="AA19" s="265"/>
       <c r="AB19" s="30"/>
       <c r="AC19" s="30"/>
       <c r="AD19" s="30"/>
@@ -31060,13 +31284,13 @@
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="58"/>
-      <c r="U20" s="272"/>
-      <c r="V20" s="273"/>
-      <c r="W20" s="273"/>
-      <c r="X20" s="273"/>
-      <c r="Y20" s="273"/>
-      <c r="Z20" s="273"/>
-      <c r="AA20" s="274"/>
+      <c r="U20" s="263"/>
+      <c r="V20" s="264"/>
+      <c r="W20" s="264"/>
+      <c r="X20" s="264"/>
+      <c r="Y20" s="264"/>
+      <c r="Z20" s="264"/>
+      <c r="AA20" s="265"/>
       <c r="AB20" s="30"/>
       <c r="AC20" s="30"/>
       <c r="AD20" s="30"/>
@@ -31102,13 +31326,13 @@
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="58"/>
-      <c r="U21" s="272"/>
-      <c r="V21" s="273"/>
-      <c r="W21" s="273"/>
-      <c r="X21" s="273"/>
-      <c r="Y21" s="273"/>
-      <c r="Z21" s="273"/>
-      <c r="AA21" s="274"/>
+      <c r="U21" s="263"/>
+      <c r="V21" s="264"/>
+      <c r="W21" s="264"/>
+      <c r="X21" s="264"/>
+      <c r="Y21" s="264"/>
+      <c r="Z21" s="264"/>
+      <c r="AA21" s="265"/>
       <c r="AB21" s="30"/>
       <c r="AC21" s="30"/>
       <c r="AD21" s="30"/>
@@ -31580,16 +31804,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="U18:AA18"/>
-    <mergeCell ref="U19:AA19"/>
-    <mergeCell ref="U20:AA20"/>
-    <mergeCell ref="U21:AA21"/>
-    <mergeCell ref="U12:AA12"/>
-    <mergeCell ref="U13:AA13"/>
-    <mergeCell ref="U14:AA14"/>
-    <mergeCell ref="U15:AA15"/>
-    <mergeCell ref="U16:AA16"/>
-    <mergeCell ref="U17:AA17"/>
     <mergeCell ref="U11:AA11"/>
     <mergeCell ref="A1:AG1"/>
     <mergeCell ref="A2:F2"/>
@@ -31605,6 +31819,16 @@
     <mergeCell ref="U8:AA8"/>
     <mergeCell ref="U9:AA9"/>
     <mergeCell ref="U10:AA10"/>
+    <mergeCell ref="U18:AA18"/>
+    <mergeCell ref="U19:AA19"/>
+    <mergeCell ref="U20:AA20"/>
+    <mergeCell ref="U21:AA21"/>
+    <mergeCell ref="U12:AA12"/>
+    <mergeCell ref="U13:AA13"/>
+    <mergeCell ref="U14:AA14"/>
+    <mergeCell ref="U15:AA15"/>
+    <mergeCell ref="U16:AA16"/>
+    <mergeCell ref="U17:AA17"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -32164,15 +32388,15 @@
       <c r="R6" s="30"/>
       <c r="S6" s="30"/>
       <c r="T6" s="31"/>
-      <c r="U6" s="266" t="s">
+      <c r="U6" s="269" t="s">
         <v>170</v>
       </c>
-      <c r="V6" s="267"/>
-      <c r="W6" s="267"/>
-      <c r="X6" s="267"/>
-      <c r="Y6" s="267"/>
-      <c r="Z6" s="267"/>
-      <c r="AA6" s="268"/>
+      <c r="V6" s="270"/>
+      <c r="W6" s="270"/>
+      <c r="X6" s="270"/>
+      <c r="Y6" s="270"/>
+      <c r="Z6" s="270"/>
+      <c r="AA6" s="271"/>
       <c r="AB6" s="275" t="s">
         <v>273</v>
       </c>
@@ -32213,15 +32437,15 @@
       <c r="R7" s="30"/>
       <c r="S7" s="30"/>
       <c r="T7" s="31"/>
-      <c r="U7" s="266" t="s">
+      <c r="U7" s="269" t="s">
         <v>170</v>
       </c>
-      <c r="V7" s="267"/>
-      <c r="W7" s="267"/>
-      <c r="X7" s="267"/>
-      <c r="Y7" s="267"/>
-      <c r="Z7" s="267"/>
-      <c r="AA7" s="268"/>
+      <c r="V7" s="270"/>
+      <c r="W7" s="270"/>
+      <c r="X7" s="270"/>
+      <c r="Y7" s="270"/>
+      <c r="Z7" s="270"/>
+      <c r="AA7" s="271"/>
       <c r="AB7" s="63"/>
       <c r="AC7" s="30"/>
       <c r="AD7" s="30" t="s">
@@ -32262,15 +32486,15 @@
       <c r="R8" s="30"/>
       <c r="S8" s="30"/>
       <c r="T8" s="31"/>
-      <c r="U8" s="266" t="s">
+      <c r="U8" s="269" t="s">
         <v>171</v>
       </c>
-      <c r="V8" s="267"/>
-      <c r="W8" s="267"/>
-      <c r="X8" s="267"/>
-      <c r="Y8" s="267"/>
-      <c r="Z8" s="267"/>
-      <c r="AA8" s="268"/>
+      <c r="V8" s="270"/>
+      <c r="W8" s="270"/>
+      <c r="X8" s="270"/>
+      <c r="Y8" s="270"/>
+      <c r="Z8" s="270"/>
+      <c r="AA8" s="271"/>
       <c r="AB8" s="63"/>
       <c r="AC8" s="30"/>
       <c r="AD8" s="30" t="s">
@@ -32311,15 +32535,15 @@
       <c r="R9" s="32"/>
       <c r="S9" s="32"/>
       <c r="T9" s="58"/>
-      <c r="U9" s="266" t="s">
+      <c r="U9" s="269" t="s">
         <v>171</v>
       </c>
-      <c r="V9" s="267"/>
-      <c r="W9" s="267"/>
-      <c r="X9" s="267"/>
-      <c r="Y9" s="267"/>
-      <c r="Z9" s="267"/>
-      <c r="AA9" s="268"/>
+      <c r="V9" s="270"/>
+      <c r="W9" s="270"/>
+      <c r="X9" s="270"/>
+      <c r="Y9" s="270"/>
+      <c r="Z9" s="270"/>
+      <c r="AA9" s="271"/>
       <c r="AB9" s="63"/>
       <c r="AC9" s="30"/>
       <c r="AD9" s="30" t="s">
@@ -32362,15 +32586,15 @@
       <c r="R10" s="32"/>
       <c r="S10" s="32"/>
       <c r="T10" s="58"/>
-      <c r="U10" s="269" t="s">
+      <c r="U10" s="272" t="s">
         <v>172</v>
       </c>
-      <c r="V10" s="270"/>
-      <c r="W10" s="270"/>
-      <c r="X10" s="270"/>
-      <c r="Y10" s="270"/>
-      <c r="Z10" s="270"/>
-      <c r="AA10" s="271"/>
+      <c r="V10" s="273"/>
+      <c r="W10" s="273"/>
+      <c r="X10" s="273"/>
+      <c r="Y10" s="273"/>
+      <c r="Z10" s="273"/>
+      <c r="AA10" s="274"/>
       <c r="AB10" s="30"/>
       <c r="AC10" s="30"/>
       <c r="AD10" s="30" t="s">
@@ -32413,15 +32637,15 @@
       <c r="R11" s="32"/>
       <c r="S11" s="32"/>
       <c r="T11" s="58"/>
-      <c r="U11" s="272" t="s">
+      <c r="U11" s="263" t="s">
         <v>173</v>
       </c>
-      <c r="V11" s="273"/>
-      <c r="W11" s="273"/>
-      <c r="X11" s="273"/>
-      <c r="Y11" s="273"/>
-      <c r="Z11" s="273"/>
-      <c r="AA11" s="274"/>
+      <c r="V11" s="264"/>
+      <c r="W11" s="264"/>
+      <c r="X11" s="264"/>
+      <c r="Y11" s="264"/>
+      <c r="Z11" s="264"/>
+      <c r="AA11" s="265"/>
       <c r="AB11" s="30"/>
       <c r="AC11" s="30"/>
       <c r="AD11" s="30" t="s">
@@ -32460,13 +32684,13 @@
       <c r="R12" s="32"/>
       <c r="S12" s="32"/>
       <c r="T12" s="58"/>
-      <c r="U12" s="272"/>
-      <c r="V12" s="273"/>
-      <c r="W12" s="273"/>
-      <c r="X12" s="273"/>
-      <c r="Y12" s="273"/>
-      <c r="Z12" s="273"/>
-      <c r="AA12" s="274"/>
+      <c r="U12" s="263"/>
+      <c r="V12" s="264"/>
+      <c r="W12" s="264"/>
+      <c r="X12" s="264"/>
+      <c r="Y12" s="264"/>
+      <c r="Z12" s="264"/>
+      <c r="AA12" s="265"/>
       <c r="AB12" s="30"/>
       <c r="AC12" s="30"/>
       <c r="AD12" s="30" t="s">
@@ -32507,15 +32731,15 @@
       <c r="R13" s="32"/>
       <c r="S13" s="32"/>
       <c r="T13" s="58"/>
-      <c r="U13" s="272" t="s">
+      <c r="U13" s="263" t="s">
         <v>175</v>
       </c>
-      <c r="V13" s="273"/>
-      <c r="W13" s="273"/>
-      <c r="X13" s="273"/>
-      <c r="Y13" s="273"/>
-      <c r="Z13" s="273"/>
-      <c r="AA13" s="274"/>
+      <c r="V13" s="264"/>
+      <c r="W13" s="264"/>
+      <c r="X13" s="264"/>
+      <c r="Y13" s="264"/>
+      <c r="Z13" s="264"/>
+      <c r="AA13" s="265"/>
       <c r="AB13" s="30"/>
       <c r="AC13" s="30"/>
       <c r="AD13" s="30" t="s">
@@ -32556,13 +32780,13 @@
       <c r="R14" s="32"/>
       <c r="S14" s="30"/>
       <c r="T14" s="31"/>
-      <c r="U14" s="272"/>
-      <c r="V14" s="273"/>
-      <c r="W14" s="273"/>
-      <c r="X14" s="273"/>
-      <c r="Y14" s="273"/>
-      <c r="Z14" s="273"/>
-      <c r="AA14" s="274"/>
+      <c r="U14" s="263"/>
+      <c r="V14" s="264"/>
+      <c r="W14" s="264"/>
+      <c r="X14" s="264"/>
+      <c r="Y14" s="264"/>
+      <c r="Z14" s="264"/>
+      <c r="AA14" s="265"/>
       <c r="AB14" s="30"/>
       <c r="AC14" s="30"/>
       <c r="AD14" s="30" t="s">
@@ -32603,15 +32827,15 @@
       <c r="R15" s="30"/>
       <c r="S15" s="32"/>
       <c r="T15" s="58"/>
-      <c r="U15" s="269" t="s">
+      <c r="U15" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="V15" s="270"/>
-      <c r="W15" s="270"/>
-      <c r="X15" s="270"/>
-      <c r="Y15" s="270"/>
-      <c r="Z15" s="270"/>
-      <c r="AA15" s="271"/>
+      <c r="V15" s="273"/>
+      <c r="W15" s="273"/>
+      <c r="X15" s="273"/>
+      <c r="Y15" s="273"/>
+      <c r="Z15" s="273"/>
+      <c r="AA15" s="274"/>
       <c r="AB15" s="30"/>
       <c r="AC15" s="30"/>
       <c r="AD15" s="30" t="s">
@@ -32652,15 +32876,15 @@
       <c r="R16" s="30"/>
       <c r="S16" s="30"/>
       <c r="T16" s="31"/>
-      <c r="U16" s="269" t="s">
+      <c r="U16" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="V16" s="270"/>
-      <c r="W16" s="270"/>
-      <c r="X16" s="270"/>
-      <c r="Y16" s="270"/>
-      <c r="Z16" s="270"/>
-      <c r="AA16" s="271"/>
+      <c r="V16" s="273"/>
+      <c r="W16" s="273"/>
+      <c r="X16" s="273"/>
+      <c r="Y16" s="273"/>
+      <c r="Z16" s="273"/>
+      <c r="AA16" s="274"/>
       <c r="AB16" s="30"/>
       <c r="AC16" s="30"/>
       <c r="AD16" s="30" t="s">
@@ -32701,13 +32925,13 @@
       <c r="R17" s="30"/>
       <c r="S17" s="30"/>
       <c r="T17" s="31"/>
-      <c r="U17" s="272"/>
-      <c r="V17" s="273"/>
-      <c r="W17" s="273"/>
-      <c r="X17" s="273"/>
-      <c r="Y17" s="273"/>
-      <c r="Z17" s="273"/>
-      <c r="AA17" s="274"/>
+      <c r="U17" s="263"/>
+      <c r="V17" s="264"/>
+      <c r="W17" s="264"/>
+      <c r="X17" s="264"/>
+      <c r="Y17" s="264"/>
+      <c r="Z17" s="264"/>
+      <c r="AA17" s="265"/>
       <c r="AB17" s="30"/>
       <c r="AC17" s="30"/>
       <c r="AD17" s="30" t="s">
@@ -32744,13 +32968,13 @@
       <c r="R18" s="30"/>
       <c r="S18" s="30"/>
       <c r="T18" s="31"/>
-      <c r="U18" s="272"/>
-      <c r="V18" s="273"/>
-      <c r="W18" s="273"/>
-      <c r="X18" s="273"/>
-      <c r="Y18" s="273"/>
-      <c r="Z18" s="273"/>
-      <c r="AA18" s="274"/>
+      <c r="U18" s="263"/>
+      <c r="V18" s="264"/>
+      <c r="W18" s="264"/>
+      <c r="X18" s="264"/>
+      <c r="Y18" s="264"/>
+      <c r="Z18" s="264"/>
+      <c r="AA18" s="265"/>
       <c r="AB18" s="30"/>
       <c r="AC18" s="30"/>
       <c r="AD18" s="30"/>
@@ -32779,13 +33003,13 @@
       <c r="R19" s="30"/>
       <c r="S19" s="30"/>
       <c r="T19" s="31"/>
-      <c r="U19" s="272"/>
-      <c r="V19" s="273"/>
-      <c r="W19" s="273"/>
-      <c r="X19" s="273"/>
-      <c r="Y19" s="273"/>
-      <c r="Z19" s="273"/>
-      <c r="AA19" s="274"/>
+      <c r="U19" s="263"/>
+      <c r="V19" s="264"/>
+      <c r="W19" s="264"/>
+      <c r="X19" s="264"/>
+      <c r="Y19" s="264"/>
+      <c r="Z19" s="264"/>
+      <c r="AA19" s="265"/>
       <c r="AB19" s="30"/>
       <c r="AC19" s="30"/>
       <c r="AD19" s="30"/>
@@ -32816,13 +33040,13 @@
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="58"/>
-      <c r="U20" s="272"/>
-      <c r="V20" s="273"/>
-      <c r="W20" s="273"/>
-      <c r="X20" s="273"/>
-      <c r="Y20" s="273"/>
-      <c r="Z20" s="273"/>
-      <c r="AA20" s="274"/>
+      <c r="U20" s="263"/>
+      <c r="V20" s="264"/>
+      <c r="W20" s="264"/>
+      <c r="X20" s="264"/>
+      <c r="Y20" s="264"/>
+      <c r="Z20" s="264"/>
+      <c r="AA20" s="265"/>
       <c r="AB20" s="30"/>
       <c r="AC20" s="30"/>
       <c r="AD20" s="30"/>
@@ -32860,13 +33084,13 @@
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="58"/>
-      <c r="U21" s="272"/>
-      <c r="V21" s="273"/>
-      <c r="W21" s="273"/>
-      <c r="X21" s="273"/>
-      <c r="Y21" s="273"/>
-      <c r="Z21" s="273"/>
-      <c r="AA21" s="274"/>
+      <c r="U21" s="263"/>
+      <c r="V21" s="264"/>
+      <c r="W21" s="264"/>
+      <c r="X21" s="264"/>
+      <c r="Y21" s="264"/>
+      <c r="Z21" s="264"/>
+      <c r="AA21" s="265"/>
       <c r="AB21" s="30"/>
       <c r="AC21" s="30"/>
       <c r="AD21" s="30"/>
@@ -33036,13 +33260,13 @@
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="58"/>
-      <c r="U25" s="263"/>
-      <c r="V25" s="264"/>
-      <c r="W25" s="264"/>
-      <c r="X25" s="264"/>
-      <c r="Y25" s="264"/>
-      <c r="Z25" s="264"/>
-      <c r="AA25" s="265"/>
+      <c r="U25" s="266"/>
+      <c r="V25" s="267"/>
+      <c r="W25" s="267"/>
+      <c r="X25" s="267"/>
+      <c r="Y25" s="267"/>
+      <c r="Z25" s="267"/>
+      <c r="AA25" s="268"/>
       <c r="AB25" s="30"/>
       <c r="AC25" s="30"/>
       <c r="AD25" s="30"/>
@@ -33080,15 +33304,15 @@
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="58"/>
-      <c r="U26" s="263" t="s">
+      <c r="U26" s="266" t="s">
         <v>270</v>
       </c>
-      <c r="V26" s="264"/>
-      <c r="W26" s="264"/>
-      <c r="X26" s="264"/>
-      <c r="Y26" s="264"/>
-      <c r="Z26" s="264"/>
-      <c r="AA26" s="265"/>
+      <c r="V26" s="267"/>
+      <c r="W26" s="267"/>
+      <c r="X26" s="267"/>
+      <c r="Y26" s="267"/>
+      <c r="Z26" s="267"/>
+      <c r="AA26" s="268"/>
       <c r="AB26" s="30"/>
       <c r="AC26" s="30"/>
       <c r="AD26" s="30"/>
@@ -33903,15 +34127,15 @@
       <c r="R46" s="30"/>
       <c r="S46" s="30"/>
       <c r="T46" s="31"/>
-      <c r="U46" s="263" t="s">
+      <c r="U46" s="266" t="s">
         <v>270</v>
       </c>
-      <c r="V46" s="264"/>
-      <c r="W46" s="264"/>
-      <c r="X46" s="264"/>
-      <c r="Y46" s="264"/>
-      <c r="Z46" s="264"/>
-      <c r="AA46" s="265"/>
+      <c r="V46" s="267"/>
+      <c r="W46" s="267"/>
+      <c r="X46" s="267"/>
+      <c r="Y46" s="267"/>
+      <c r="Z46" s="267"/>
+      <c r="AA46" s="268"/>
       <c r="AB46" s="30"/>
       <c r="AC46" s="30"/>
       <c r="AD46" s="30" t="s">
@@ -34627,15 +34851,13 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="G3:AC3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="U26:AA26"/>
+    <mergeCell ref="AB41:AG41"/>
+    <mergeCell ref="U46:AA46"/>
+    <mergeCell ref="U18:AA18"/>
+    <mergeCell ref="U19:AA19"/>
+    <mergeCell ref="U20:AA20"/>
+    <mergeCell ref="U21:AA21"/>
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="U25:AA25"/>
     <mergeCell ref="U12:AA12"/>
@@ -34650,13 +34872,15 @@
     <mergeCell ref="U9:AA9"/>
     <mergeCell ref="U10:AA10"/>
     <mergeCell ref="U11:AA11"/>
-    <mergeCell ref="U26:AA26"/>
-    <mergeCell ref="AB41:AG41"/>
-    <mergeCell ref="U46:AA46"/>
-    <mergeCell ref="U18:AA18"/>
-    <mergeCell ref="U19:AA19"/>
-    <mergeCell ref="U20:AA20"/>
-    <mergeCell ref="U21:AA21"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:AC3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -36953,30 +37177,30 @@
       <c r="D6" s="30"/>
       <c r="E6" s="30"/>
       <c r="F6" s="31"/>
-      <c r="G6" s="129" t="s">
+      <c r="G6" s="132" t="s">
         <v>298</v>
       </c>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="130"/>
-      <c r="Q6" s="130"/>
-      <c r="R6" s="130"/>
-      <c r="S6" s="130"/>
-      <c r="T6" s="130"/>
-      <c r="U6" s="130"/>
-      <c r="V6" s="130"/>
-      <c r="W6" s="130"/>
-      <c r="X6" s="130"/>
-      <c r="Y6" s="130"/>
-      <c r="Z6" s="130"/>
-      <c r="AA6" s="130"/>
-      <c r="AB6" s="131"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
+      <c r="N6" s="133"/>
+      <c r="O6" s="133"/>
+      <c r="P6" s="133"/>
+      <c r="Q6" s="133"/>
+      <c r="R6" s="133"/>
+      <c r="S6" s="133"/>
+      <c r="T6" s="133"/>
+      <c r="U6" s="133"/>
+      <c r="V6" s="133"/>
+      <c r="W6" s="133"/>
+      <c r="X6" s="133"/>
+      <c r="Y6" s="133"/>
+      <c r="Z6" s="133"/>
+      <c r="AA6" s="133"/>
+      <c r="AB6" s="134"/>
       <c r="AC6" s="30"/>
       <c r="AD6" s="30"/>
       <c r="AE6" s="30"/>
@@ -36992,30 +37216,30 @@
       <c r="D7" s="30"/>
       <c r="E7" s="30"/>
       <c r="F7" s="31"/>
-      <c r="G7" s="129" t="s">
+      <c r="G7" s="132" t="s">
         <v>299</v>
       </c>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="130"/>
-      <c r="S7" s="130"/>
-      <c r="T7" s="130"/>
-      <c r="U7" s="130"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="130"/>
-      <c r="Y7" s="130"/>
-      <c r="Z7" s="130"/>
-      <c r="AA7" s="130"/>
-      <c r="AB7" s="131"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="133"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="133"/>
+      <c r="X7" s="133"/>
+      <c r="Y7" s="133"/>
+      <c r="Z7" s="133"/>
+      <c r="AA7" s="133"/>
+      <c r="AB7" s="134"/>
       <c r="AC7" s="29"/>
       <c r="AD7" s="30"/>
       <c r="AE7" s="30"/>
@@ -37031,30 +37255,30 @@
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
-      <c r="G8" s="129" t="s">
+      <c r="G8" s="132" t="s">
         <v>302</v>
       </c>
-      <c r="H8" s="130"/>
-      <c r="I8" s="130"/>
-      <c r="J8" s="130"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="130"/>
-      <c r="N8" s="130"/>
-      <c r="O8" s="130"/>
-      <c r="P8" s="130"/>
-      <c r="Q8" s="130"/>
-      <c r="R8" s="130"/>
-      <c r="S8" s="130"/>
-      <c r="T8" s="130"/>
-      <c r="U8" s="130"/>
-      <c r="V8" s="130"/>
-      <c r="W8" s="130"/>
-      <c r="X8" s="130"/>
-      <c r="Y8" s="130"/>
-      <c r="Z8" s="130"/>
-      <c r="AA8" s="130"/>
-      <c r="AB8" s="131"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="133"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
+      <c r="N8" s="133"/>
+      <c r="O8" s="133"/>
+      <c r="P8" s="133"/>
+      <c r="Q8" s="133"/>
+      <c r="R8" s="133"/>
+      <c r="S8" s="133"/>
+      <c r="T8" s="133"/>
+      <c r="U8" s="133"/>
+      <c r="V8" s="133"/>
+      <c r="W8" s="133"/>
+      <c r="X8" s="133"/>
+      <c r="Y8" s="133"/>
+      <c r="Z8" s="133"/>
+      <c r="AA8" s="133"/>
+      <c r="AB8" s="134"/>
       <c r="AC8" s="29"/>
       <c r="AD8" s="30"/>
       <c r="AE8" s="30"/>
@@ -37070,30 +37294,30 @@
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="31"/>
-      <c r="G9" s="129" t="s">
+      <c r="G9" s="132" t="s">
         <v>303</v>
       </c>
-      <c r="H9" s="130"/>
-      <c r="I9" s="130"/>
-      <c r="J9" s="130"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="130"/>
-      <c r="N9" s="130"/>
-      <c r="O9" s="130"/>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="130"/>
-      <c r="R9" s="130"/>
-      <c r="S9" s="130"/>
-      <c r="T9" s="130"/>
-      <c r="U9" s="130"/>
-      <c r="V9" s="130"/>
-      <c r="W9" s="130"/>
-      <c r="X9" s="130"/>
-      <c r="Y9" s="130"/>
-      <c r="Z9" s="130"/>
-      <c r="AA9" s="130"/>
-      <c r="AB9" s="131"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="133"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="133"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="133"/>
+      <c r="T9" s="133"/>
+      <c r="U9" s="133"/>
+      <c r="V9" s="133"/>
+      <c r="W9" s="133"/>
+      <c r="X9" s="133"/>
+      <c r="Y9" s="133"/>
+      <c r="Z9" s="133"/>
+      <c r="AA9" s="133"/>
+      <c r="AB9" s="134"/>
       <c r="AC9" s="29"/>
       <c r="AD9" s="30"/>
       <c r="AE9" s="30"/>
@@ -37109,30 +37333,30 @@
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="58"/>
-      <c r="G10" s="129" t="s">
+      <c r="G10" s="132" t="s">
         <v>305</v>
       </c>
-      <c r="H10" s="130"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="130"/>
-      <c r="K10" s="130"/>
-      <c r="L10" s="130"/>
-      <c r="M10" s="130"/>
-      <c r="N10" s="130"/>
-      <c r="O10" s="130"/>
-      <c r="P10" s="130"/>
-      <c r="Q10" s="130"/>
-      <c r="R10" s="130"/>
-      <c r="S10" s="130"/>
-      <c r="T10" s="130"/>
-      <c r="U10" s="130"/>
-      <c r="V10" s="130"/>
-      <c r="W10" s="130"/>
-      <c r="X10" s="130"/>
-      <c r="Y10" s="130"/>
-      <c r="Z10" s="130"/>
-      <c r="AA10" s="130"/>
-      <c r="AB10" s="131"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="133"/>
+      <c r="N10" s="133"/>
+      <c r="O10" s="133"/>
+      <c r="P10" s="133"/>
+      <c r="Q10" s="133"/>
+      <c r="R10" s="133"/>
+      <c r="S10" s="133"/>
+      <c r="T10" s="133"/>
+      <c r="U10" s="133"/>
+      <c r="V10" s="133"/>
+      <c r="W10" s="133"/>
+      <c r="X10" s="133"/>
+      <c r="Y10" s="133"/>
+      <c r="Z10" s="133"/>
+      <c r="AA10" s="133"/>
+      <c r="AB10" s="134"/>
       <c r="AC10" s="29"/>
       <c r="AD10" s="30"/>
       <c r="AE10" s="30"/>
@@ -37148,30 +37372,30 @@
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
       <c r="F11" s="58"/>
-      <c r="G11" s="129" t="s">
+      <c r="G11" s="132" t="s">
         <v>307</v>
       </c>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="130"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="130"/>
-      <c r="N11" s="130"/>
-      <c r="O11" s="130"/>
-      <c r="P11" s="130"/>
-      <c r="Q11" s="130"/>
-      <c r="R11" s="130"/>
-      <c r="S11" s="130"/>
-      <c r="T11" s="130"/>
-      <c r="U11" s="130"/>
-      <c r="V11" s="130"/>
-      <c r="W11" s="130"/>
-      <c r="X11" s="130"/>
-      <c r="Y11" s="130"/>
-      <c r="Z11" s="130"/>
-      <c r="AA11" s="130"/>
-      <c r="AB11" s="131"/>
+      <c r="H11" s="133"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="133"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="133"/>
+      <c r="N11" s="133"/>
+      <c r="O11" s="133"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
+      <c r="R11" s="133"/>
+      <c r="S11" s="133"/>
+      <c r="T11" s="133"/>
+      <c r="U11" s="133"/>
+      <c r="V11" s="133"/>
+      <c r="W11" s="133"/>
+      <c r="X11" s="133"/>
+      <c r="Y11" s="133"/>
+      <c r="Z11" s="133"/>
+      <c r="AA11" s="133"/>
+      <c r="AB11" s="134"/>
       <c r="AC11" s="29"/>
       <c r="AD11" s="30"/>
       <c r="AE11" s="30"/>
@@ -37187,37 +37411,37 @@
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
       <c r="F12" s="58"/>
-      <c r="G12" s="129" t="s">
+      <c r="G12" s="132" t="s">
         <v>320</v>
       </c>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="130"/>
-      <c r="M12" s="130"/>
-      <c r="N12" s="130"/>
-      <c r="O12" s="130"/>
-      <c r="P12" s="130"/>
-      <c r="Q12" s="130"/>
-      <c r="R12" s="130"/>
-      <c r="S12" s="130"/>
-      <c r="T12" s="130"/>
-      <c r="U12" s="130"/>
-      <c r="V12" s="130"/>
-      <c r="W12" s="130"/>
-      <c r="X12" s="130"/>
-      <c r="Y12" s="130"/>
-      <c r="Z12" s="130"/>
-      <c r="AA12" s="130"/>
-      <c r="AB12" s="131"/>
-      <c r="AC12" s="129" t="s">
+      <c r="H12" s="133"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="133"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="133"/>
+      <c r="M12" s="133"/>
+      <c r="N12" s="133"/>
+      <c r="O12" s="133"/>
+      <c r="P12" s="133"/>
+      <c r="Q12" s="133"/>
+      <c r="R12" s="133"/>
+      <c r="S12" s="133"/>
+      <c r="T12" s="133"/>
+      <c r="U12" s="133"/>
+      <c r="V12" s="133"/>
+      <c r="W12" s="133"/>
+      <c r="X12" s="133"/>
+      <c r="Y12" s="133"/>
+      <c r="Z12" s="133"/>
+      <c r="AA12" s="133"/>
+      <c r="AB12" s="134"/>
+      <c r="AC12" s="132" t="s">
         <v>315</v>
       </c>
-      <c r="AD12" s="130"/>
-      <c r="AE12" s="130"/>
-      <c r="AF12" s="130"/>
-      <c r="AG12" s="131"/>
+      <c r="AD12" s="133"/>
+      <c r="AE12" s="133"/>
+      <c r="AF12" s="133"/>
+      <c r="AG12" s="134"/>
     </row>
     <row r="13" spans="1:177" ht="22.5" customHeight="1">
       <c r="A13" s="29" t="s">
@@ -37228,30 +37452,30 @@
       <c r="D13" s="30"/>
       <c r="E13" s="30"/>
       <c r="F13" s="58"/>
-      <c r="G13" s="129" t="s">
+      <c r="G13" s="132" t="s">
         <v>310</v>
       </c>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="130"/>
-      <c r="R13" s="130"/>
-      <c r="S13" s="130"/>
-      <c r="T13" s="130"/>
-      <c r="U13" s="130"/>
-      <c r="V13" s="130"/>
-      <c r="W13" s="130"/>
-      <c r="X13" s="130"/>
-      <c r="Y13" s="130"/>
-      <c r="Z13" s="130"/>
-      <c r="AA13" s="130"/>
-      <c r="AB13" s="131"/>
+      <c r="H13" s="133"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="133"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="133"/>
+      <c r="P13" s="133"/>
+      <c r="Q13" s="133"/>
+      <c r="R13" s="133"/>
+      <c r="S13" s="133"/>
+      <c r="T13" s="133"/>
+      <c r="U13" s="133"/>
+      <c r="V13" s="133"/>
+      <c r="W13" s="133"/>
+      <c r="X13" s="133"/>
+      <c r="Y13" s="133"/>
+      <c r="Z13" s="133"/>
+      <c r="AA13" s="133"/>
+      <c r="AB13" s="134"/>
       <c r="AC13" s="29"/>
       <c r="AD13" s="30"/>
       <c r="AE13" s="30"/>
@@ -37267,37 +37491,37 @@
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>
       <c r="F14" s="31"/>
-      <c r="G14" s="129" t="s">
+      <c r="G14" s="132" t="s">
         <v>313</v>
       </c>
-      <c r="H14" s="130"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-      <c r="M14" s="130"/>
-      <c r="N14" s="130"/>
-      <c r="O14" s="130"/>
-      <c r="P14" s="130"/>
-      <c r="Q14" s="130"/>
-      <c r="R14" s="130"/>
-      <c r="S14" s="130"/>
-      <c r="T14" s="130"/>
-      <c r="U14" s="130"/>
-      <c r="V14" s="130"/>
-      <c r="W14" s="130"/>
-      <c r="X14" s="130"/>
-      <c r="Y14" s="130"/>
-      <c r="Z14" s="130"/>
-      <c r="AA14" s="130"/>
-      <c r="AB14" s="131"/>
-      <c r="AC14" s="129" t="s">
+      <c r="H14" s="133"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="133"/>
+      <c r="N14" s="133"/>
+      <c r="O14" s="133"/>
+      <c r="P14" s="133"/>
+      <c r="Q14" s="133"/>
+      <c r="R14" s="133"/>
+      <c r="S14" s="133"/>
+      <c r="T14" s="133"/>
+      <c r="U14" s="133"/>
+      <c r="V14" s="133"/>
+      <c r="W14" s="133"/>
+      <c r="X14" s="133"/>
+      <c r="Y14" s="133"/>
+      <c r="Z14" s="133"/>
+      <c r="AA14" s="133"/>
+      <c r="AB14" s="134"/>
+      <c r="AC14" s="132" t="s">
         <v>312</v>
       </c>
-      <c r="AD14" s="130"/>
-      <c r="AE14" s="130"/>
-      <c r="AF14" s="130"/>
-      <c r="AG14" s="131"/>
+      <c r="AD14" s="133"/>
+      <c r="AE14" s="133"/>
+      <c r="AF14" s="133"/>
+      <c r="AG14" s="134"/>
     </row>
     <row r="15" spans="1:177" ht="22.5" customHeight="1">
       <c r="A15" s="29" t="s">
@@ -37308,30 +37532,30 @@
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
       <c r="F15" s="58"/>
-      <c r="G15" s="129" t="s">
+      <c r="G15" s="132" t="s">
         <v>316</v>
       </c>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="130"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="130"/>
-      <c r="P15" s="130"/>
-      <c r="Q15" s="130"/>
-      <c r="R15" s="130"/>
-      <c r="S15" s="130"/>
-      <c r="T15" s="130"/>
-      <c r="U15" s="130"/>
-      <c r="V15" s="130"/>
-      <c r="W15" s="130"/>
-      <c r="X15" s="130"/>
-      <c r="Y15" s="130"/>
-      <c r="Z15" s="130"/>
-      <c r="AA15" s="130"/>
-      <c r="AB15" s="131"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="133"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="133"/>
+      <c r="P15" s="133"/>
+      <c r="Q15" s="133"/>
+      <c r="R15" s="133"/>
+      <c r="S15" s="133"/>
+      <c r="T15" s="133"/>
+      <c r="U15" s="133"/>
+      <c r="V15" s="133"/>
+      <c r="W15" s="133"/>
+      <c r="X15" s="133"/>
+      <c r="Y15" s="133"/>
+      <c r="Z15" s="133"/>
+      <c r="AA15" s="133"/>
+      <c r="AB15" s="134"/>
       <c r="AC15" s="29"/>
       <c r="AD15" s="30"/>
       <c r="AE15" s="30"/>
@@ -37347,30 +37571,30 @@
       <c r="D16" s="30"/>
       <c r="E16" s="30"/>
       <c r="F16" s="31"/>
-      <c r="G16" s="129" t="s">
+      <c r="G16" s="132" t="s">
         <v>318</v>
       </c>
-      <c r="H16" s="130"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
-      <c r="M16" s="130"/>
-      <c r="N16" s="130"/>
-      <c r="O16" s="130"/>
-      <c r="P16" s="130"/>
-      <c r="Q16" s="130"/>
-      <c r="R16" s="130"/>
-      <c r="S16" s="130"/>
-      <c r="T16" s="130"/>
-      <c r="U16" s="130"/>
-      <c r="V16" s="130"/>
-      <c r="W16" s="130"/>
-      <c r="X16" s="130"/>
-      <c r="Y16" s="130"/>
-      <c r="Z16" s="130"/>
-      <c r="AA16" s="130"/>
-      <c r="AB16" s="131"/>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="133"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="133"/>
+      <c r="M16" s="133"/>
+      <c r="N16" s="133"/>
+      <c r="O16" s="133"/>
+      <c r="P16" s="133"/>
+      <c r="Q16" s="133"/>
+      <c r="R16" s="133"/>
+      <c r="S16" s="133"/>
+      <c r="T16" s="133"/>
+      <c r="U16" s="133"/>
+      <c r="V16" s="133"/>
+      <c r="W16" s="133"/>
+      <c r="X16" s="133"/>
+      <c r="Y16" s="133"/>
+      <c r="Z16" s="133"/>
+      <c r="AA16" s="133"/>
+      <c r="AB16" s="134"/>
       <c r="AC16" s="29"/>
       <c r="AD16" s="30"/>
       <c r="AE16" s="30"/>
@@ -37386,37 +37610,37 @@
       <c r="D17" s="30"/>
       <c r="E17" s="30"/>
       <c r="F17" s="31"/>
-      <c r="G17" s="129" t="s">
+      <c r="G17" s="132" t="s">
         <v>321</v>
       </c>
-      <c r="H17" s="130"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="130"/>
-      <c r="N17" s="130"/>
-      <c r="O17" s="130"/>
-      <c r="P17" s="130"/>
-      <c r="Q17" s="130"/>
-      <c r="R17" s="130"/>
-      <c r="S17" s="130"/>
-      <c r="T17" s="130"/>
-      <c r="U17" s="130"/>
-      <c r="V17" s="130"/>
-      <c r="W17" s="130"/>
-      <c r="X17" s="130"/>
-      <c r="Y17" s="130"/>
-      <c r="Z17" s="130"/>
-      <c r="AA17" s="130"/>
-      <c r="AB17" s="131"/>
-      <c r="AC17" s="129" t="s">
+      <c r="H17" s="133"/>
+      <c r="I17" s="133"/>
+      <c r="J17" s="133"/>
+      <c r="K17" s="133"/>
+      <c r="L17" s="133"/>
+      <c r="M17" s="133"/>
+      <c r="N17" s="133"/>
+      <c r="O17" s="133"/>
+      <c r="P17" s="133"/>
+      <c r="Q17" s="133"/>
+      <c r="R17" s="133"/>
+      <c r="S17" s="133"/>
+      <c r="T17" s="133"/>
+      <c r="U17" s="133"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="133"/>
+      <c r="X17" s="133"/>
+      <c r="Y17" s="133"/>
+      <c r="Z17" s="133"/>
+      <c r="AA17" s="133"/>
+      <c r="AB17" s="134"/>
+      <c r="AC17" s="132" t="s">
         <v>322</v>
       </c>
-      <c r="AD17" s="130"/>
-      <c r="AE17" s="130"/>
-      <c r="AF17" s="130"/>
-      <c r="AG17" s="131"/>
+      <c r="AD17" s="133"/>
+      <c r="AE17" s="133"/>
+      <c r="AF17" s="133"/>
+      <c r="AG17" s="134"/>
     </row>
     <row r="18" spans="1:33" ht="12.75" customHeight="1">
       <c r="A18" s="120" t="s">
@@ -37832,30 +38056,30 @@
       <c r="D29" s="30"/>
       <c r="E29" s="30"/>
       <c r="F29" s="58"/>
-      <c r="G29" s="132" t="s">
+      <c r="G29" s="129" t="s">
         <v>333</v>
       </c>
-      <c r="H29" s="133"/>
-      <c r="I29" s="133"/>
-      <c r="J29" s="133"/>
-      <c r="K29" s="133"/>
-      <c r="L29" s="133"/>
-      <c r="M29" s="133"/>
-      <c r="N29" s="133"/>
-      <c r="O29" s="133"/>
-      <c r="P29" s="133"/>
-      <c r="Q29" s="133"/>
-      <c r="R29" s="133"/>
-      <c r="S29" s="133"/>
-      <c r="T29" s="133"/>
-      <c r="U29" s="133"/>
-      <c r="V29" s="133"/>
-      <c r="W29" s="133"/>
-      <c r="X29" s="133"/>
-      <c r="Y29" s="133"/>
-      <c r="Z29" s="133"/>
-      <c r="AA29" s="133"/>
-      <c r="AB29" s="134"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="130"/>
+      <c r="J29" s="130"/>
+      <c r="K29" s="130"/>
+      <c r="L29" s="130"/>
+      <c r="M29" s="130"/>
+      <c r="N29" s="130"/>
+      <c r="O29" s="130"/>
+      <c r="P29" s="130"/>
+      <c r="Q29" s="130"/>
+      <c r="R29" s="130"/>
+      <c r="S29" s="130"/>
+      <c r="T29" s="130"/>
+      <c r="U29" s="130"/>
+      <c r="V29" s="130"/>
+      <c r="W29" s="130"/>
+      <c r="X29" s="130"/>
+      <c r="Y29" s="130"/>
+      <c r="Z29" s="130"/>
+      <c r="AA29" s="130"/>
+      <c r="AB29" s="131"/>
       <c r="AC29" s="32"/>
       <c r="AD29" s="30"/>
       <c r="AE29" s="30"/>
@@ -38360,20 +38584,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="G17:AB17"/>
-    <mergeCell ref="AC17:AG17"/>
-    <mergeCell ref="G14:AB14"/>
-    <mergeCell ref="AC14:AG14"/>
-    <mergeCell ref="G15:AB15"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="G3:AC3"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="G29:AB29"/>
     <mergeCell ref="AC5:AG5"/>
@@ -38390,6 +38600,20 @@
     <mergeCell ref="G12:AB12"/>
     <mergeCell ref="G13:AB13"/>
     <mergeCell ref="G16:AB16"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:AC3"/>
+    <mergeCell ref="G17:AB17"/>
+    <mergeCell ref="AC17:AG17"/>
+    <mergeCell ref="G14:AB14"/>
+    <mergeCell ref="AC14:AG14"/>
+    <mergeCell ref="G15:AB15"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -38732,30 +38956,30 @@
       <c r="D5" s="30"/>
       <c r="E5" s="30"/>
       <c r="F5" s="31"/>
-      <c r="G5" s="129" t="s">
+      <c r="G5" s="132" t="s">
         <v>340</v>
       </c>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="130"/>
-      <c r="N5" s="130"/>
-      <c r="O5" s="130"/>
-      <c r="P5" s="130"/>
-      <c r="Q5" s="130"/>
-      <c r="R5" s="130"/>
-      <c r="S5" s="130"/>
-      <c r="T5" s="130"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="130"/>
-      <c r="W5" s="130"/>
-      <c r="X5" s="130"/>
-      <c r="Y5" s="130"/>
-      <c r="Z5" s="130"/>
-      <c r="AA5" s="130"/>
-      <c r="AB5" s="131"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
+      <c r="O5" s="133"/>
+      <c r="P5" s="133"/>
+      <c r="Q5" s="133"/>
+      <c r="R5" s="133"/>
+      <c r="S5" s="133"/>
+      <c r="T5" s="133"/>
+      <c r="U5" s="133"/>
+      <c r="V5" s="133"/>
+      <c r="W5" s="133"/>
+      <c r="X5" s="133"/>
+      <c r="Y5" s="133"/>
+      <c r="Z5" s="133"/>
+      <c r="AA5" s="133"/>
+      <c r="AB5" s="134"/>
       <c r="AC5" s="30"/>
       <c r="AD5" s="30"/>
       <c r="AE5" s="30"/>
@@ -38771,30 +38995,30 @@
       <c r="D6" s="30"/>
       <c r="E6" s="30"/>
       <c r="F6" s="31"/>
-      <c r="G6" s="129" t="s">
+      <c r="G6" s="132" t="s">
         <v>341</v>
       </c>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="130"/>
-      <c r="Q6" s="130"/>
-      <c r="R6" s="130"/>
-      <c r="S6" s="130"/>
-      <c r="T6" s="130"/>
-      <c r="U6" s="130"/>
-      <c r="V6" s="130"/>
-      <c r="W6" s="130"/>
-      <c r="X6" s="130"/>
-      <c r="Y6" s="130"/>
-      <c r="Z6" s="130"/>
-      <c r="AA6" s="130"/>
-      <c r="AB6" s="131"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
+      <c r="N6" s="133"/>
+      <c r="O6" s="133"/>
+      <c r="P6" s="133"/>
+      <c r="Q6" s="133"/>
+      <c r="R6" s="133"/>
+      <c r="S6" s="133"/>
+      <c r="T6" s="133"/>
+      <c r="U6" s="133"/>
+      <c r="V6" s="133"/>
+      <c r="W6" s="133"/>
+      <c r="X6" s="133"/>
+      <c r="Y6" s="133"/>
+      <c r="Z6" s="133"/>
+      <c r="AA6" s="133"/>
+      <c r="AB6" s="134"/>
       <c r="AC6" s="29"/>
       <c r="AD6" s="30"/>
       <c r="AE6" s="30"/>
@@ -38810,30 +39034,30 @@
       <c r="D7" s="30"/>
       <c r="E7" s="30"/>
       <c r="F7" s="31"/>
-      <c r="G7" s="129" t="s">
+      <c r="G7" s="132" t="s">
         <v>342</v>
       </c>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="130"/>
-      <c r="S7" s="130"/>
-      <c r="T7" s="130"/>
-      <c r="U7" s="130"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="130"/>
-      <c r="Y7" s="130"/>
-      <c r="Z7" s="130"/>
-      <c r="AA7" s="130"/>
-      <c r="AB7" s="131"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="133"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="133"/>
+      <c r="X7" s="133"/>
+      <c r="Y7" s="133"/>
+      <c r="Z7" s="133"/>
+      <c r="AA7" s="133"/>
+      <c r="AB7" s="134"/>
       <c r="AC7" s="29"/>
       <c r="AD7" s="30"/>
       <c r="AE7" s="30"/>
@@ -38849,30 +39073,30 @@
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
-      <c r="G8" s="129" t="s">
+      <c r="G8" s="132" t="s">
         <v>343</v>
       </c>
-      <c r="H8" s="130"/>
-      <c r="I8" s="130"/>
-      <c r="J8" s="130"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="130"/>
-      <c r="N8" s="130"/>
-      <c r="O8" s="130"/>
-      <c r="P8" s="130"/>
-      <c r="Q8" s="130"/>
-      <c r="R8" s="130"/>
-      <c r="S8" s="130"/>
-      <c r="T8" s="130"/>
-      <c r="U8" s="130"/>
-      <c r="V8" s="130"/>
-      <c r="W8" s="130"/>
-      <c r="X8" s="130"/>
-      <c r="Y8" s="130"/>
-      <c r="Z8" s="130"/>
-      <c r="AA8" s="130"/>
-      <c r="AB8" s="131"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="133"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
+      <c r="N8" s="133"/>
+      <c r="O8" s="133"/>
+      <c r="P8" s="133"/>
+      <c r="Q8" s="133"/>
+      <c r="R8" s="133"/>
+      <c r="S8" s="133"/>
+      <c r="T8" s="133"/>
+      <c r="U8" s="133"/>
+      <c r="V8" s="133"/>
+      <c r="W8" s="133"/>
+      <c r="X8" s="133"/>
+      <c r="Y8" s="133"/>
+      <c r="Z8" s="133"/>
+      <c r="AA8" s="133"/>
+      <c r="AB8" s="134"/>
       <c r="AC8" s="29"/>
       <c r="AD8" s="30"/>
       <c r="AE8" s="30"/>
@@ -38888,30 +39112,30 @@
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="58"/>
-      <c r="G9" s="129" t="s">
+      <c r="G9" s="132" t="s">
         <v>344</v>
       </c>
-      <c r="H9" s="130"/>
-      <c r="I9" s="130"/>
-      <c r="J9" s="130"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="130"/>
-      <c r="N9" s="130"/>
-      <c r="O9" s="130"/>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="130"/>
-      <c r="R9" s="130"/>
-      <c r="S9" s="130"/>
-      <c r="T9" s="130"/>
-      <c r="U9" s="130"/>
-      <c r="V9" s="130"/>
-      <c r="W9" s="130"/>
-      <c r="X9" s="130"/>
-      <c r="Y9" s="130"/>
-      <c r="Z9" s="130"/>
-      <c r="AA9" s="130"/>
-      <c r="AB9" s="131"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="133"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="133"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="133"/>
+      <c r="T9" s="133"/>
+      <c r="U9" s="133"/>
+      <c r="V9" s="133"/>
+      <c r="W9" s="133"/>
+      <c r="X9" s="133"/>
+      <c r="Y9" s="133"/>
+      <c r="Z9" s="133"/>
+      <c r="AA9" s="133"/>
+      <c r="AB9" s="134"/>
       <c r="AC9" s="29"/>
       <c r="AD9" s="30"/>
       <c r="AE9" s="30"/>
@@ -38927,37 +39151,37 @@
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="58"/>
-      <c r="G10" s="129" t="s">
+      <c r="G10" s="132" t="s">
         <v>345</v>
       </c>
-      <c r="H10" s="130"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="130"/>
-      <c r="K10" s="130"/>
-      <c r="L10" s="130"/>
-      <c r="M10" s="130"/>
-      <c r="N10" s="130"/>
-      <c r="O10" s="130"/>
-      <c r="P10" s="130"/>
-      <c r="Q10" s="130"/>
-      <c r="R10" s="130"/>
-      <c r="S10" s="130"/>
-      <c r="T10" s="130"/>
-      <c r="U10" s="130"/>
-      <c r="V10" s="130"/>
-      <c r="W10" s="130"/>
-      <c r="X10" s="130"/>
-      <c r="Y10" s="130"/>
-      <c r="Z10" s="130"/>
-      <c r="AA10" s="130"/>
-      <c r="AB10" s="131"/>
-      <c r="AC10" s="129" t="s">
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="133"/>
+      <c r="N10" s="133"/>
+      <c r="O10" s="133"/>
+      <c r="P10" s="133"/>
+      <c r="Q10" s="133"/>
+      <c r="R10" s="133"/>
+      <c r="S10" s="133"/>
+      <c r="T10" s="133"/>
+      <c r="U10" s="133"/>
+      <c r="V10" s="133"/>
+      <c r="W10" s="133"/>
+      <c r="X10" s="133"/>
+      <c r="Y10" s="133"/>
+      <c r="Z10" s="133"/>
+      <c r="AA10" s="133"/>
+      <c r="AB10" s="134"/>
+      <c r="AC10" s="132" t="s">
         <v>315</v>
       </c>
-      <c r="AD10" s="130"/>
-      <c r="AE10" s="130"/>
-      <c r="AF10" s="130"/>
-      <c r="AG10" s="131"/>
+      <c r="AD10" s="133"/>
+      <c r="AE10" s="133"/>
+      <c r="AF10" s="133"/>
+      <c r="AG10" s="134"/>
     </row>
     <row r="11" spans="1:177" ht="22.5" customHeight="1">
       <c r="A11" s="29" t="s">
@@ -38968,37 +39192,37 @@
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
       <c r="F11" s="31"/>
-      <c r="G11" s="129" t="s">
+      <c r="G11" s="132" t="s">
         <v>346</v>
       </c>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="130"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="130"/>
-      <c r="N11" s="130"/>
-      <c r="O11" s="130"/>
-      <c r="P11" s="130"/>
-      <c r="Q11" s="130"/>
-      <c r="R11" s="130"/>
-      <c r="S11" s="130"/>
-      <c r="T11" s="130"/>
-      <c r="U11" s="130"/>
-      <c r="V11" s="130"/>
-      <c r="W11" s="130"/>
-      <c r="X11" s="130"/>
-      <c r="Y11" s="130"/>
-      <c r="Z11" s="130"/>
-      <c r="AA11" s="130"/>
-      <c r="AB11" s="131"/>
-      <c r="AC11" s="129" t="s">
+      <c r="H11" s="133"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="133"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="133"/>
+      <c r="N11" s="133"/>
+      <c r="O11" s="133"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
+      <c r="R11" s="133"/>
+      <c r="S11" s="133"/>
+      <c r="T11" s="133"/>
+      <c r="U11" s="133"/>
+      <c r="V11" s="133"/>
+      <c r="W11" s="133"/>
+      <c r="X11" s="133"/>
+      <c r="Y11" s="133"/>
+      <c r="Z11" s="133"/>
+      <c r="AA11" s="133"/>
+      <c r="AB11" s="134"/>
+      <c r="AC11" s="132" t="s">
         <v>322</v>
       </c>
-      <c r="AD11" s="130"/>
-      <c r="AE11" s="130"/>
-      <c r="AF11" s="130"/>
-      <c r="AG11" s="131"/>
+      <c r="AD11" s="133"/>
+      <c r="AE11" s="133"/>
+      <c r="AF11" s="133"/>
+      <c r="AG11" s="134"/>
     </row>
     <row r="12" spans="1:177" ht="12.75" customHeight="1">
       <c r="A12" s="120" t="s">
@@ -39825,6 +40049,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G11:AB11"/>
+    <mergeCell ref="AC11:AG11"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="G9:AB9"/>
+    <mergeCell ref="G10:AB10"/>
+    <mergeCell ref="AC10:AG10"/>
     <mergeCell ref="G5:AB5"/>
     <mergeCell ref="G6:AB6"/>
     <mergeCell ref="G7:AB7"/>
@@ -39838,12 +40068,6 @@
     <mergeCell ref="G3:AC3"/>
     <mergeCell ref="AD3:AE3"/>
     <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="G11:AB11"/>
-    <mergeCell ref="AC11:AG11"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="G9:AB9"/>
-    <mergeCell ref="G10:AB10"/>
-    <mergeCell ref="AC10:AG10"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -39963,7 +40187,7 @@
       <c r="E3" s="142"/>
       <c r="F3" s="143"/>
       <c r="G3" s="141" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H3" s="142"/>
       <c r="I3" s="142"/>
@@ -40179,7 +40403,7 @@
     </row>
     <row r="5" spans="1:177" s="3" customFormat="1" ht="14" customHeight="1">
       <c r="A5" s="122" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B5" s="63"/>
       <c r="C5" s="63"/>
@@ -40367,30 +40591,30 @@
       <c r="D6" s="30"/>
       <c r="E6" s="30"/>
       <c r="F6" s="31"/>
-      <c r="G6" s="129" t="s">
-        <v>359</v>
-      </c>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="130"/>
-      <c r="Q6" s="130"/>
-      <c r="R6" s="130"/>
-      <c r="S6" s="130"/>
-      <c r="T6" s="130"/>
-      <c r="U6" s="130"/>
-      <c r="V6" s="130"/>
-      <c r="W6" s="130"/>
-      <c r="X6" s="130"/>
-      <c r="Y6" s="130"/>
-      <c r="Z6" s="130"/>
-      <c r="AA6" s="130"/>
-      <c r="AB6" s="131"/>
+      <c r="G6" s="132" t="s">
+        <v>370</v>
+      </c>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
+      <c r="N6" s="133"/>
+      <c r="O6" s="133"/>
+      <c r="P6" s="133"/>
+      <c r="Q6" s="133"/>
+      <c r="R6" s="133"/>
+      <c r="S6" s="133"/>
+      <c r="T6" s="133"/>
+      <c r="U6" s="133"/>
+      <c r="V6" s="133"/>
+      <c r="W6" s="133"/>
+      <c r="X6" s="133"/>
+      <c r="Y6" s="133"/>
+      <c r="Z6" s="133"/>
+      <c r="AA6" s="133"/>
+      <c r="AB6" s="134"/>
       <c r="AC6" s="30"/>
       <c r="AD6" s="30"/>
       <c r="AE6" s="30"/>
@@ -40406,30 +40630,30 @@
       <c r="D7" s="30"/>
       <c r="E7" s="30"/>
       <c r="F7" s="31"/>
-      <c r="G7" s="129" t="s">
-        <v>360</v>
-      </c>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="130"/>
-      <c r="S7" s="130"/>
-      <c r="T7" s="130"/>
-      <c r="U7" s="130"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="130"/>
-      <c r="Y7" s="130"/>
-      <c r="Z7" s="130"/>
-      <c r="AA7" s="130"/>
-      <c r="AB7" s="131"/>
+      <c r="G7" s="132" t="s">
+        <v>371</v>
+      </c>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="133"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="133"/>
+      <c r="X7" s="133"/>
+      <c r="Y7" s="133"/>
+      <c r="Z7" s="133"/>
+      <c r="AA7" s="133"/>
+      <c r="AB7" s="134"/>
       <c r="AC7" s="29"/>
       <c r="AD7" s="30"/>
       <c r="AE7" s="30"/>
@@ -40445,30 +40669,30 @@
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
-      <c r="G8" s="129" t="s">
-        <v>361</v>
-      </c>
-      <c r="H8" s="130"/>
-      <c r="I8" s="130"/>
-      <c r="J8" s="130"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="130"/>
-      <c r="N8" s="130"/>
-      <c r="O8" s="130"/>
-      <c r="P8" s="130"/>
-      <c r="Q8" s="130"/>
-      <c r="R8" s="130"/>
-      <c r="S8" s="130"/>
-      <c r="T8" s="130"/>
-      <c r="U8" s="130"/>
-      <c r="V8" s="130"/>
-      <c r="W8" s="130"/>
-      <c r="X8" s="130"/>
-      <c r="Y8" s="130"/>
-      <c r="Z8" s="130"/>
-      <c r="AA8" s="130"/>
-      <c r="AB8" s="131"/>
+      <c r="G8" s="132" t="s">
+        <v>372</v>
+      </c>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="133"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
+      <c r="N8" s="133"/>
+      <c r="O8" s="133"/>
+      <c r="P8" s="133"/>
+      <c r="Q8" s="133"/>
+      <c r="R8" s="133"/>
+      <c r="S8" s="133"/>
+      <c r="T8" s="133"/>
+      <c r="U8" s="133"/>
+      <c r="V8" s="133"/>
+      <c r="W8" s="133"/>
+      <c r="X8" s="133"/>
+      <c r="Y8" s="133"/>
+      <c r="Z8" s="133"/>
+      <c r="AA8" s="133"/>
+      <c r="AB8" s="134"/>
       <c r="AC8" s="29"/>
       <c r="AD8" s="30"/>
       <c r="AE8" s="30"/>
@@ -40484,30 +40708,30 @@
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="31"/>
-      <c r="G9" s="129" t="s">
-        <v>362</v>
-      </c>
-      <c r="H9" s="130"/>
-      <c r="I9" s="130"/>
-      <c r="J9" s="130"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="130"/>
-      <c r="N9" s="130"/>
-      <c r="O9" s="130"/>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="130"/>
-      <c r="R9" s="130"/>
-      <c r="S9" s="130"/>
-      <c r="T9" s="130"/>
-      <c r="U9" s="130"/>
-      <c r="V9" s="130"/>
-      <c r="W9" s="130"/>
-      <c r="X9" s="130"/>
-      <c r="Y9" s="130"/>
-      <c r="Z9" s="130"/>
-      <c r="AA9" s="130"/>
-      <c r="AB9" s="131"/>
+      <c r="G9" s="132" t="s">
+        <v>373</v>
+      </c>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="133"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="133"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="133"/>
+      <c r="T9" s="133"/>
+      <c r="U9" s="133"/>
+      <c r="V9" s="133"/>
+      <c r="W9" s="133"/>
+      <c r="X9" s="133"/>
+      <c r="Y9" s="133"/>
+      <c r="Z9" s="133"/>
+      <c r="AA9" s="133"/>
+      <c r="AB9" s="134"/>
       <c r="AC9" s="29"/>
       <c r="AD9" s="30"/>
       <c r="AE9" s="30"/>
@@ -40523,30 +40747,30 @@
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="58"/>
-      <c r="G10" s="129" t="s">
-        <v>363</v>
-      </c>
-      <c r="H10" s="130"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="130"/>
-      <c r="K10" s="130"/>
-      <c r="L10" s="130"/>
-      <c r="M10" s="130"/>
-      <c r="N10" s="130"/>
-      <c r="O10" s="130"/>
-      <c r="P10" s="130"/>
-      <c r="Q10" s="130"/>
-      <c r="R10" s="130"/>
-      <c r="S10" s="130"/>
-      <c r="T10" s="130"/>
-      <c r="U10" s="130"/>
-      <c r="V10" s="130"/>
-      <c r="W10" s="130"/>
-      <c r="X10" s="130"/>
-      <c r="Y10" s="130"/>
-      <c r="Z10" s="130"/>
-      <c r="AA10" s="130"/>
-      <c r="AB10" s="131"/>
+      <c r="G10" s="132" t="s">
+        <v>374</v>
+      </c>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="133"/>
+      <c r="N10" s="133"/>
+      <c r="O10" s="133"/>
+      <c r="P10" s="133"/>
+      <c r="Q10" s="133"/>
+      <c r="R10" s="133"/>
+      <c r="S10" s="133"/>
+      <c r="T10" s="133"/>
+      <c r="U10" s="133"/>
+      <c r="V10" s="133"/>
+      <c r="W10" s="133"/>
+      <c r="X10" s="133"/>
+      <c r="Y10" s="133"/>
+      <c r="Z10" s="133"/>
+      <c r="AA10" s="133"/>
+      <c r="AB10" s="134"/>
       <c r="AC10" s="29"/>
       <c r="AD10" s="30"/>
       <c r="AE10" s="30"/>
@@ -40562,30 +40786,30 @@
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
       <c r="F11" s="58"/>
-      <c r="G11" s="129" t="s">
-        <v>364</v>
-      </c>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="130"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="130"/>
-      <c r="N11" s="130"/>
-      <c r="O11" s="130"/>
-      <c r="P11" s="130"/>
-      <c r="Q11" s="130"/>
-      <c r="R11" s="130"/>
-      <c r="S11" s="130"/>
-      <c r="T11" s="130"/>
-      <c r="U11" s="130"/>
-      <c r="V11" s="130"/>
-      <c r="W11" s="130"/>
-      <c r="X11" s="130"/>
-      <c r="Y11" s="130"/>
-      <c r="Z11" s="130"/>
-      <c r="AA11" s="130"/>
-      <c r="AB11" s="131"/>
+      <c r="G11" s="132" t="s">
+        <v>375</v>
+      </c>
+      <c r="H11" s="133"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="133"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="133"/>
+      <c r="N11" s="133"/>
+      <c r="O11" s="133"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
+      <c r="R11" s="133"/>
+      <c r="S11" s="133"/>
+      <c r="T11" s="133"/>
+      <c r="U11" s="133"/>
+      <c r="V11" s="133"/>
+      <c r="W11" s="133"/>
+      <c r="X11" s="133"/>
+      <c r="Y11" s="133"/>
+      <c r="Z11" s="133"/>
+      <c r="AA11" s="133"/>
+      <c r="AB11" s="134"/>
       <c r="AC11" s="29"/>
       <c r="AD11" s="30"/>
       <c r="AE11" s="30"/>
@@ -40601,35 +40825,35 @@
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
       <c r="F12" s="58"/>
-      <c r="G12" s="129" t="s">
-        <v>368</v>
-      </c>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="130"/>
-      <c r="M12" s="130"/>
-      <c r="N12" s="130"/>
-      <c r="O12" s="130"/>
-      <c r="P12" s="130"/>
-      <c r="Q12" s="130"/>
-      <c r="R12" s="130"/>
-      <c r="S12" s="130"/>
-      <c r="T12" s="130"/>
-      <c r="U12" s="130"/>
-      <c r="V12" s="130"/>
-      <c r="W12" s="130"/>
-      <c r="X12" s="130"/>
-      <c r="Y12" s="130"/>
-      <c r="Z12" s="130"/>
-      <c r="AA12" s="130"/>
-      <c r="AB12" s="131"/>
-      <c r="AC12" s="129"/>
-      <c r="AD12" s="130"/>
-      <c r="AE12" s="130"/>
-      <c r="AF12" s="130"/>
-      <c r="AG12" s="131"/>
+      <c r="G12" s="132" t="s">
+        <v>379</v>
+      </c>
+      <c r="H12" s="133"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="133"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="133"/>
+      <c r="M12" s="133"/>
+      <c r="N12" s="133"/>
+      <c r="O12" s="133"/>
+      <c r="P12" s="133"/>
+      <c r="Q12" s="133"/>
+      <c r="R12" s="133"/>
+      <c r="S12" s="133"/>
+      <c r="T12" s="133"/>
+      <c r="U12" s="133"/>
+      <c r="V12" s="133"/>
+      <c r="W12" s="133"/>
+      <c r="X12" s="133"/>
+      <c r="Y12" s="133"/>
+      <c r="Z12" s="133"/>
+      <c r="AA12" s="133"/>
+      <c r="AB12" s="134"/>
+      <c r="AC12" s="132"/>
+      <c r="AD12" s="133"/>
+      <c r="AE12" s="133"/>
+      <c r="AF12" s="133"/>
+      <c r="AG12" s="134"/>
     </row>
     <row r="13" spans="1:177" ht="22.5" customHeight="1">
       <c r="A13" s="29" t="s">
@@ -40640,30 +40864,30 @@
       <c r="D13" s="30"/>
       <c r="E13" s="30"/>
       <c r="F13" s="58"/>
-      <c r="G13" s="129" t="s">
-        <v>365</v>
-      </c>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="130"/>
-      <c r="R13" s="130"/>
-      <c r="S13" s="130"/>
-      <c r="T13" s="130"/>
-      <c r="U13" s="130"/>
-      <c r="V13" s="130"/>
-      <c r="W13" s="130"/>
-      <c r="X13" s="130"/>
-      <c r="Y13" s="130"/>
-      <c r="Z13" s="130"/>
-      <c r="AA13" s="130"/>
-      <c r="AB13" s="131"/>
+      <c r="G13" s="132" t="s">
+        <v>376</v>
+      </c>
+      <c r="H13" s="133"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="133"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="133"/>
+      <c r="P13" s="133"/>
+      <c r="Q13" s="133"/>
+      <c r="R13" s="133"/>
+      <c r="S13" s="133"/>
+      <c r="T13" s="133"/>
+      <c r="U13" s="133"/>
+      <c r="V13" s="133"/>
+      <c r="W13" s="133"/>
+      <c r="X13" s="133"/>
+      <c r="Y13" s="133"/>
+      <c r="Z13" s="133"/>
+      <c r="AA13" s="133"/>
+      <c r="AB13" s="134"/>
       <c r="AC13" s="29"/>
       <c r="AD13" s="30"/>
       <c r="AE13" s="30"/>
@@ -40679,35 +40903,35 @@
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>
       <c r="F14" s="31"/>
-      <c r="G14" s="129" t="s">
-        <v>369</v>
-      </c>
-      <c r="H14" s="130"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-      <c r="M14" s="130"/>
-      <c r="N14" s="130"/>
-      <c r="O14" s="130"/>
-      <c r="P14" s="130"/>
-      <c r="Q14" s="130"/>
-      <c r="R14" s="130"/>
-      <c r="S14" s="130"/>
-      <c r="T14" s="130"/>
-      <c r="U14" s="130"/>
-      <c r="V14" s="130"/>
-      <c r="W14" s="130"/>
-      <c r="X14" s="130"/>
-      <c r="Y14" s="130"/>
-      <c r="Z14" s="130"/>
-      <c r="AA14" s="130"/>
-      <c r="AB14" s="131"/>
-      <c r="AC14" s="129"/>
-      <c r="AD14" s="130"/>
-      <c r="AE14" s="130"/>
-      <c r="AF14" s="130"/>
-      <c r="AG14" s="131"/>
+      <c r="G14" s="132" t="s">
+        <v>380</v>
+      </c>
+      <c r="H14" s="133"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="133"/>
+      <c r="N14" s="133"/>
+      <c r="O14" s="133"/>
+      <c r="P14" s="133"/>
+      <c r="Q14" s="133"/>
+      <c r="R14" s="133"/>
+      <c r="S14" s="133"/>
+      <c r="T14" s="133"/>
+      <c r="U14" s="133"/>
+      <c r="V14" s="133"/>
+      <c r="W14" s="133"/>
+      <c r="X14" s="133"/>
+      <c r="Y14" s="133"/>
+      <c r="Z14" s="133"/>
+      <c r="AA14" s="133"/>
+      <c r="AB14" s="134"/>
+      <c r="AC14" s="132"/>
+      <c r="AD14" s="133"/>
+      <c r="AE14" s="133"/>
+      <c r="AF14" s="133"/>
+      <c r="AG14" s="134"/>
     </row>
     <row r="15" spans="1:177" ht="22.5" customHeight="1">
       <c r="A15" s="29" t="s">
@@ -40718,30 +40942,30 @@
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
       <c r="F15" s="58"/>
-      <c r="G15" s="129" t="s">
-        <v>366</v>
-      </c>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="130"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="130"/>
-      <c r="P15" s="130"/>
-      <c r="Q15" s="130"/>
-      <c r="R15" s="130"/>
-      <c r="S15" s="130"/>
-      <c r="T15" s="130"/>
-      <c r="U15" s="130"/>
-      <c r="V15" s="130"/>
-      <c r="W15" s="130"/>
-      <c r="X15" s="130"/>
-      <c r="Y15" s="130"/>
-      <c r="Z15" s="130"/>
-      <c r="AA15" s="130"/>
-      <c r="AB15" s="131"/>
+      <c r="G15" s="132" t="s">
+        <v>377</v>
+      </c>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="133"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="133"/>
+      <c r="P15" s="133"/>
+      <c r="Q15" s="133"/>
+      <c r="R15" s="133"/>
+      <c r="S15" s="133"/>
+      <c r="T15" s="133"/>
+      <c r="U15" s="133"/>
+      <c r="V15" s="133"/>
+      <c r="W15" s="133"/>
+      <c r="X15" s="133"/>
+      <c r="Y15" s="133"/>
+      <c r="Z15" s="133"/>
+      <c r="AA15" s="133"/>
+      <c r="AB15" s="134"/>
       <c r="AC15" s="29"/>
       <c r="AD15" s="30"/>
       <c r="AE15" s="30"/>
@@ -40757,30 +40981,30 @@
       <c r="D16" s="30"/>
       <c r="E16" s="30"/>
       <c r="F16" s="31"/>
-      <c r="G16" s="129" t="s">
-        <v>367</v>
-      </c>
-      <c r="H16" s="130"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
-      <c r="M16" s="130"/>
-      <c r="N16" s="130"/>
-      <c r="O16" s="130"/>
-      <c r="P16" s="130"/>
-      <c r="Q16" s="130"/>
-      <c r="R16" s="130"/>
-      <c r="S16" s="130"/>
-      <c r="T16" s="130"/>
-      <c r="U16" s="130"/>
-      <c r="V16" s="130"/>
-      <c r="W16" s="130"/>
-      <c r="X16" s="130"/>
-      <c r="Y16" s="130"/>
-      <c r="Z16" s="130"/>
-      <c r="AA16" s="130"/>
-      <c r="AB16" s="131"/>
+      <c r="G16" s="132" t="s">
+        <v>378</v>
+      </c>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="133"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="133"/>
+      <c r="M16" s="133"/>
+      <c r="N16" s="133"/>
+      <c r="O16" s="133"/>
+      <c r="P16" s="133"/>
+      <c r="Q16" s="133"/>
+      <c r="R16" s="133"/>
+      <c r="S16" s="133"/>
+      <c r="T16" s="133"/>
+      <c r="U16" s="133"/>
+      <c r="V16" s="133"/>
+      <c r="W16" s="133"/>
+      <c r="X16" s="133"/>
+      <c r="Y16" s="133"/>
+      <c r="Z16" s="133"/>
+      <c r="AA16" s="133"/>
+      <c r="AB16" s="134"/>
       <c r="AC16" s="29"/>
       <c r="AD16" s="30"/>
       <c r="AE16" s="30"/>
@@ -40796,35 +41020,35 @@
       <c r="D17" s="30"/>
       <c r="E17" s="30"/>
       <c r="F17" s="31"/>
-      <c r="G17" s="129" t="s">
-        <v>370</v>
-      </c>
-      <c r="H17" s="130"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="130"/>
-      <c r="N17" s="130"/>
-      <c r="O17" s="130"/>
-      <c r="P17" s="130"/>
-      <c r="Q17" s="130"/>
-      <c r="R17" s="130"/>
-      <c r="S17" s="130"/>
-      <c r="T17" s="130"/>
-      <c r="U17" s="130"/>
-      <c r="V17" s="130"/>
-      <c r="W17" s="130"/>
-      <c r="X17" s="130"/>
-      <c r="Y17" s="130"/>
-      <c r="Z17" s="130"/>
-      <c r="AA17" s="130"/>
-      <c r="AB17" s="131"/>
-      <c r="AC17" s="129"/>
-      <c r="AD17" s="130"/>
-      <c r="AE17" s="130"/>
-      <c r="AF17" s="130"/>
-      <c r="AG17" s="131"/>
+      <c r="G17" s="132" t="s">
+        <v>381</v>
+      </c>
+      <c r="H17" s="133"/>
+      <c r="I17" s="133"/>
+      <c r="J17" s="133"/>
+      <c r="K17" s="133"/>
+      <c r="L17" s="133"/>
+      <c r="M17" s="133"/>
+      <c r="N17" s="133"/>
+      <c r="O17" s="133"/>
+      <c r="P17" s="133"/>
+      <c r="Q17" s="133"/>
+      <c r="R17" s="133"/>
+      <c r="S17" s="133"/>
+      <c r="T17" s="133"/>
+      <c r="U17" s="133"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="133"/>
+      <c r="X17" s="133"/>
+      <c r="Y17" s="133"/>
+      <c r="Z17" s="133"/>
+      <c r="AA17" s="133"/>
+      <c r="AB17" s="134"/>
+      <c r="AC17" s="132"/>
+      <c r="AD17" s="133"/>
+      <c r="AE17" s="133"/>
+      <c r="AF17" s="133"/>
+      <c r="AG17" s="134"/>
     </row>
     <row r="18" spans="1:33" ht="12.75" customHeight="1">
       <c r="A18" s="120" t="s">
@@ -41048,7 +41272,7 @@
     </row>
     <row r="24" spans="1:33" ht="14.5" customHeight="1">
       <c r="A24" s="123" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B24" s="124"/>
       <c r="C24" s="124"/>
@@ -41093,7 +41317,7 @@
       <c r="E25" s="30"/>
       <c r="F25" s="58"/>
       <c r="G25" s="32" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="H25" s="30"/>
       <c r="I25" s="30"/>
@@ -41159,7 +41383,7 @@
     </row>
     <row r="27" spans="1:33" ht="12.75" customHeight="1">
       <c r="A27" s="120" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B27" s="30"/>
       <c r="C27" s="30"/>
@@ -41167,7 +41391,7 @@
       <c r="E27" s="30"/>
       <c r="F27" s="58"/>
       <c r="G27" s="32" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="H27" s="30"/>
       <c r="I27" s="30"/>
@@ -41204,7 +41428,7 @@
       <c r="E28" s="30"/>
       <c r="F28" s="58"/>
       <c r="G28" s="32" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="H28" s="30"/>
       <c r="I28" s="30"/>
@@ -41240,30 +41464,30 @@
       <c r="D29" s="30"/>
       <c r="E29" s="30"/>
       <c r="F29" s="58"/>
-      <c r="G29" s="132" t="s">
-        <v>374</v>
-      </c>
-      <c r="H29" s="133"/>
-      <c r="I29" s="133"/>
-      <c r="J29" s="133"/>
-      <c r="K29" s="133"/>
-      <c r="L29" s="133"/>
-      <c r="M29" s="133"/>
-      <c r="N29" s="133"/>
-      <c r="O29" s="133"/>
-      <c r="P29" s="133"/>
-      <c r="Q29" s="133"/>
-      <c r="R29" s="133"/>
-      <c r="S29" s="133"/>
-      <c r="T29" s="133"/>
-      <c r="U29" s="133"/>
-      <c r="V29" s="133"/>
-      <c r="W29" s="133"/>
-      <c r="X29" s="133"/>
-      <c r="Y29" s="133"/>
-      <c r="Z29" s="133"/>
-      <c r="AA29" s="133"/>
-      <c r="AB29" s="134"/>
+      <c r="G29" s="129" t="s">
+        <v>385</v>
+      </c>
+      <c r="H29" s="130"/>
+      <c r="I29" s="130"/>
+      <c r="J29" s="130"/>
+      <c r="K29" s="130"/>
+      <c r="L29" s="130"/>
+      <c r="M29" s="130"/>
+      <c r="N29" s="130"/>
+      <c r="O29" s="130"/>
+      <c r="P29" s="130"/>
+      <c r="Q29" s="130"/>
+      <c r="R29" s="130"/>
+      <c r="S29" s="130"/>
+      <c r="T29" s="130"/>
+      <c r="U29" s="130"/>
+      <c r="V29" s="130"/>
+      <c r="W29" s="130"/>
+      <c r="X29" s="130"/>
+      <c r="Y29" s="130"/>
+      <c r="Z29" s="130"/>
+      <c r="AA29" s="130"/>
+      <c r="AB29" s="131"/>
       <c r="AC29" s="32"/>
       <c r="AD29" s="30"/>
       <c r="AE29" s="30"/>
@@ -41768,6 +41992,21 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="G15:AB15"/>
+    <mergeCell ref="G16:AB16"/>
+    <mergeCell ref="G17:AB17"/>
+    <mergeCell ref="AC17:AG17"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="G29:AB29"/>
+    <mergeCell ref="G10:AB10"/>
+    <mergeCell ref="G11:AB11"/>
+    <mergeCell ref="G12:AB12"/>
+    <mergeCell ref="AC12:AG12"/>
+    <mergeCell ref="G13:AB13"/>
+    <mergeCell ref="G14:AB14"/>
+    <mergeCell ref="AC14:AG14"/>
     <mergeCell ref="G9:AB9"/>
     <mergeCell ref="A1:AG1"/>
     <mergeCell ref="A2:F2"/>
@@ -41783,21 +42022,6 @@
     <mergeCell ref="G6:AB6"/>
     <mergeCell ref="G7:AB7"/>
     <mergeCell ref="G8:AB8"/>
-    <mergeCell ref="AC17:AG17"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="G29:AB29"/>
-    <mergeCell ref="G10:AB10"/>
-    <mergeCell ref="G11:AB11"/>
-    <mergeCell ref="G12:AB12"/>
-    <mergeCell ref="AC12:AG12"/>
-    <mergeCell ref="G13:AB13"/>
-    <mergeCell ref="G14:AB14"/>
-    <mergeCell ref="AC14:AG14"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="G15:AB15"/>
-    <mergeCell ref="G16:AB16"/>
-    <mergeCell ref="G17:AB17"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -43631,6 +43855,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="K4:P5"/>
+    <mergeCell ref="Q4:AA4"/>
+    <mergeCell ref="AB4:AG5"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="Q5:U5"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="G3:AC3"/>
     <mergeCell ref="AD3:AE3"/>
@@ -43640,12 +43870,6 @@
     <mergeCell ref="G2:AC2"/>
     <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="K4:P5"/>
-    <mergeCell ref="Q4:AA4"/>
-    <mergeCell ref="AB4:AG5"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="Q5:U5"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -43659,6 +43883,1850 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BC3B79-4045-4203-8CF6-A1AE25217D83}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:FU40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="4.08984375" style="1" customWidth="1"/>
+    <col min="5" max="6" width="4.08984375" style="4" customWidth="1"/>
+    <col min="7" max="33" width="4.08984375" style="1" customWidth="1"/>
+    <col min="34" max="37" width="4" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A1" s="138" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
+      <c r="Q1" s="139"/>
+      <c r="R1" s="139"/>
+      <c r="S1" s="139"/>
+      <c r="T1" s="139"/>
+      <c r="U1" s="139"/>
+      <c r="V1" s="139"/>
+      <c r="W1" s="139"/>
+      <c r="X1" s="139"/>
+      <c r="Y1" s="139"/>
+      <c r="Z1" s="139"/>
+      <c r="AA1" s="139"/>
+      <c r="AB1" s="139"/>
+      <c r="AC1" s="139"/>
+      <c r="AD1" s="139"/>
+      <c r="AE1" s="139"/>
+      <c r="AF1" s="139"/>
+      <c r="AG1" s="140"/>
+    </row>
+    <row r="2" spans="1:177" s="12" customFormat="1" ht="12">
+      <c r="A2" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="142"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="141" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" s="142"/>
+      <c r="I2" s="142"/>
+      <c r="J2" s="142"/>
+      <c r="K2" s="142"/>
+      <c r="L2" s="142"/>
+      <c r="M2" s="142"/>
+      <c r="N2" s="142"/>
+      <c r="O2" s="142"/>
+      <c r="P2" s="142"/>
+      <c r="Q2" s="142"/>
+      <c r="R2" s="142"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="142"/>
+      <c r="U2" s="142"/>
+      <c r="V2" s="142"/>
+      <c r="W2" s="142"/>
+      <c r="X2" s="142"/>
+      <c r="Y2" s="142"/>
+      <c r="Z2" s="142"/>
+      <c r="AA2" s="142"/>
+      <c r="AB2" s="142"/>
+      <c r="AC2" s="143"/>
+      <c r="AD2" s="141" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="143"/>
+      <c r="AF2" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="143"/>
+    </row>
+    <row r="3" spans="1:177" s="12" customFormat="1" ht="12">
+      <c r="A3" s="141" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="142"/>
+      <c r="C3" s="142"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="142"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="141" t="s">
+        <v>387</v>
+      </c>
+      <c r="H3" s="142"/>
+      <c r="I3" s="142"/>
+      <c r="J3" s="142"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="142"/>
+      <c r="M3" s="142"/>
+      <c r="N3" s="142"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
+      <c r="S3" s="142"/>
+      <c r="T3" s="142"/>
+      <c r="U3" s="142"/>
+      <c r="V3" s="142"/>
+      <c r="W3" s="142"/>
+      <c r="X3" s="142"/>
+      <c r="Y3" s="142"/>
+      <c r="Z3" s="142"/>
+      <c r="AA3" s="142"/>
+      <c r="AB3" s="142"/>
+      <c r="AC3" s="143"/>
+      <c r="AD3" s="141"/>
+      <c r="AE3" s="143"/>
+      <c r="AF3" s="141"/>
+      <c r="AG3" s="143"/>
+    </row>
+    <row r="4" spans="1:177" s="3" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="8"/>
+      <c r="AC4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD4" s="7"/>
+      <c r="AE4" s="7"/>
+      <c r="AF4" s="7"/>
+      <c r="AG4" s="8"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="5"/>
+      <c r="AO4" s="5"/>
+      <c r="AP4" s="5"/>
+      <c r="AQ4" s="5"/>
+      <c r="AR4" s="5"/>
+      <c r="AS4" s="5"/>
+      <c r="AT4" s="5"/>
+      <c r="AU4" s="5"/>
+      <c r="AV4" s="5"/>
+      <c r="AW4" s="5"/>
+      <c r="AX4" s="5"/>
+      <c r="AY4" s="5"/>
+      <c r="AZ4" s="5"/>
+      <c r="BA4" s="5"/>
+      <c r="BB4" s="5"/>
+      <c r="BC4" s="5"/>
+      <c r="BD4" s="5"/>
+      <c r="BE4" s="5"/>
+      <c r="BF4" s="5"/>
+      <c r="BG4" s="5"/>
+      <c r="BH4" s="5"/>
+      <c r="BI4" s="5"/>
+      <c r="BJ4" s="5"/>
+      <c r="BK4" s="5"/>
+      <c r="BL4" s="5"/>
+      <c r="BM4" s="5"/>
+      <c r="BN4" s="5"/>
+      <c r="BO4" s="5"/>
+      <c r="BP4" s="5"/>
+      <c r="BQ4" s="5"/>
+      <c r="BR4" s="5"/>
+      <c r="BS4" s="5"/>
+      <c r="BT4" s="5"/>
+      <c r="BU4" s="5"/>
+      <c r="BV4" s="5"/>
+      <c r="BW4" s="5"/>
+      <c r="BX4" s="5"/>
+      <c r="BY4" s="5"/>
+      <c r="BZ4" s="5"/>
+      <c r="CA4" s="5"/>
+      <c r="CB4" s="5"/>
+      <c r="CC4" s="5"/>
+      <c r="CD4" s="5"/>
+      <c r="CE4" s="5"/>
+      <c r="CF4" s="5"/>
+      <c r="CG4" s="5"/>
+      <c r="CH4" s="5"/>
+      <c r="CI4" s="5"/>
+      <c r="CJ4" s="5"/>
+      <c r="CK4" s="5"/>
+      <c r="CL4" s="5"/>
+      <c r="CM4" s="5"/>
+      <c r="CN4" s="5"/>
+      <c r="CO4" s="5"/>
+      <c r="CP4" s="5"/>
+      <c r="CQ4" s="5"/>
+      <c r="CR4" s="5"/>
+      <c r="CS4" s="5"/>
+      <c r="CT4" s="5"/>
+      <c r="CU4" s="5"/>
+      <c r="CV4" s="5"/>
+      <c r="CW4" s="5"/>
+      <c r="CX4" s="5"/>
+      <c r="CY4" s="5"/>
+      <c r="CZ4" s="5"/>
+      <c r="DA4" s="5"/>
+      <c r="DB4" s="5"/>
+      <c r="DC4" s="5"/>
+      <c r="DD4" s="5"/>
+      <c r="DE4" s="5"/>
+      <c r="DF4" s="5"/>
+      <c r="DG4" s="5"/>
+      <c r="DH4" s="5"/>
+      <c r="DI4" s="5"/>
+      <c r="DJ4" s="5"/>
+      <c r="DK4" s="5"/>
+      <c r="DL4" s="5"/>
+      <c r="DM4" s="5"/>
+      <c r="DN4" s="5"/>
+      <c r="DO4" s="5"/>
+      <c r="DP4" s="5"/>
+      <c r="DQ4" s="5"/>
+      <c r="DR4" s="5"/>
+      <c r="DS4" s="5"/>
+      <c r="DT4" s="5"/>
+      <c r="DU4" s="5"/>
+      <c r="DV4" s="5"/>
+      <c r="DW4" s="5"/>
+      <c r="DX4" s="5"/>
+      <c r="DY4" s="5"/>
+      <c r="DZ4" s="5"/>
+      <c r="EA4" s="5"/>
+      <c r="EB4" s="5"/>
+      <c r="EC4" s="5"/>
+      <c r="ED4" s="5"/>
+      <c r="EE4" s="5"/>
+      <c r="EF4" s="5"/>
+      <c r="EG4" s="5"/>
+      <c r="EH4" s="5"/>
+      <c r="EI4" s="5"/>
+      <c r="EJ4" s="5"/>
+      <c r="EK4" s="5"/>
+      <c r="EL4" s="5"/>
+      <c r="EM4" s="5"/>
+      <c r="EN4" s="5"/>
+      <c r="EO4" s="5"/>
+      <c r="EP4" s="5"/>
+      <c r="EQ4" s="5"/>
+      <c r="ER4" s="5"/>
+      <c r="ES4" s="5"/>
+      <c r="ET4" s="5"/>
+      <c r="EU4" s="5"/>
+      <c r="EV4" s="5"/>
+      <c r="EW4" s="5"/>
+      <c r="EX4" s="5"/>
+      <c r="EY4" s="5"/>
+      <c r="EZ4" s="5"/>
+      <c r="FA4" s="5"/>
+      <c r="FB4" s="5"/>
+      <c r="FC4" s="5"/>
+      <c r="FD4" s="5"/>
+      <c r="FE4" s="5"/>
+      <c r="FF4" s="5"/>
+      <c r="FG4" s="5"/>
+      <c r="FH4" s="5"/>
+      <c r="FI4" s="5"/>
+      <c r="FJ4" s="5"/>
+      <c r="FK4" s="5"/>
+      <c r="FL4" s="5"/>
+      <c r="FM4" s="5"/>
+      <c r="FN4" s="5"/>
+      <c r="FO4" s="5"/>
+      <c r="FP4" s="5"/>
+      <c r="FQ4" s="5"/>
+      <c r="FR4" s="5"/>
+      <c r="FS4" s="5"/>
+      <c r="FT4" s="5"/>
+      <c r="FU4" s="5"/>
+    </row>
+    <row r="5" spans="1:177" s="3" customFormat="1" ht="14" customHeight="1">
+      <c r="A5" s="122" t="s">
+        <v>388</v>
+      </c>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="135"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
+      <c r="M5" s="136"/>
+      <c r="N5" s="136"/>
+      <c r="O5" s="136"/>
+      <c r="P5" s="136"/>
+      <c r="Q5" s="136"/>
+      <c r="R5" s="136"/>
+      <c r="S5" s="136"/>
+      <c r="T5" s="136"/>
+      <c r="U5" s="136"/>
+      <c r="V5" s="136"/>
+      <c r="W5" s="136"/>
+      <c r="X5" s="136"/>
+      <c r="Y5" s="136"/>
+      <c r="Z5" s="136"/>
+      <c r="AA5" s="136"/>
+      <c r="AB5" s="137"/>
+      <c r="AC5" s="135"/>
+      <c r="AD5" s="136"/>
+      <c r="AE5" s="136"/>
+      <c r="AF5" s="136"/>
+      <c r="AG5" s="137"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="5"/>
+      <c r="AJ5" s="5"/>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="5"/>
+      <c r="AN5" s="5"/>
+      <c r="AO5" s="5"/>
+      <c r="AP5" s="5"/>
+      <c r="AQ5" s="5"/>
+      <c r="AR5" s="5"/>
+      <c r="AS5" s="5"/>
+      <c r="AT5" s="5"/>
+      <c r="AU5" s="5"/>
+      <c r="AV5" s="5"/>
+      <c r="AW5" s="5"/>
+      <c r="AX5" s="5"/>
+      <c r="AY5" s="5"/>
+      <c r="AZ5" s="5"/>
+      <c r="BA5" s="5"/>
+      <c r="BB5" s="5"/>
+      <c r="BC5" s="5"/>
+      <c r="BD5" s="5"/>
+      <c r="BE5" s="5"/>
+      <c r="BF5" s="5"/>
+      <c r="BG5" s="5"/>
+      <c r="BH5" s="5"/>
+      <c r="BI5" s="5"/>
+      <c r="BJ5" s="5"/>
+      <c r="BK5" s="5"/>
+      <c r="BL5" s="5"/>
+      <c r="BM5" s="5"/>
+      <c r="BN5" s="5"/>
+      <c r="BO5" s="5"/>
+      <c r="BP5" s="5"/>
+      <c r="BQ5" s="5"/>
+      <c r="BR5" s="5"/>
+      <c r="BS5" s="5"/>
+      <c r="BT5" s="5"/>
+      <c r="BU5" s="5"/>
+      <c r="BV5" s="5"/>
+      <c r="BW5" s="5"/>
+      <c r="BX5" s="5"/>
+      <c r="BY5" s="5"/>
+      <c r="BZ5" s="5"/>
+      <c r="CA5" s="5"/>
+      <c r="CB5" s="5"/>
+      <c r="CC5" s="5"/>
+      <c r="CD5" s="5"/>
+      <c r="CE5" s="5"/>
+      <c r="CF5" s="5"/>
+      <c r="CG5" s="5"/>
+      <c r="CH5" s="5"/>
+      <c r="CI5" s="5"/>
+      <c r="CJ5" s="5"/>
+      <c r="CK5" s="5"/>
+      <c r="CL5" s="5"/>
+      <c r="CM5" s="5"/>
+      <c r="CN5" s="5"/>
+      <c r="CO5" s="5"/>
+      <c r="CP5" s="5"/>
+      <c r="CQ5" s="5"/>
+      <c r="CR5" s="5"/>
+      <c r="CS5" s="5"/>
+      <c r="CT5" s="5"/>
+      <c r="CU5" s="5"/>
+      <c r="CV5" s="5"/>
+      <c r="CW5" s="5"/>
+      <c r="CX5" s="5"/>
+      <c r="CY5" s="5"/>
+      <c r="CZ5" s="5"/>
+      <c r="DA5" s="5"/>
+      <c r="DB5" s="5"/>
+      <c r="DC5" s="5"/>
+      <c r="DD5" s="5"/>
+      <c r="DE5" s="5"/>
+      <c r="DF5" s="5"/>
+      <c r="DG5" s="5"/>
+      <c r="DH5" s="5"/>
+      <c r="DI5" s="5"/>
+      <c r="DJ5" s="5"/>
+      <c r="DK5" s="5"/>
+      <c r="DL5" s="5"/>
+      <c r="DM5" s="5"/>
+      <c r="DN5" s="5"/>
+      <c r="DO5" s="5"/>
+      <c r="DP5" s="5"/>
+      <c r="DQ5" s="5"/>
+      <c r="DR5" s="5"/>
+      <c r="DS5" s="5"/>
+      <c r="DT5" s="5"/>
+      <c r="DU5" s="5"/>
+      <c r="DV5" s="5"/>
+      <c r="DW5" s="5"/>
+      <c r="DX5" s="5"/>
+      <c r="DY5" s="5"/>
+      <c r="DZ5" s="5"/>
+      <c r="EA5" s="5"/>
+      <c r="EB5" s="5"/>
+      <c r="EC5" s="5"/>
+      <c r="ED5" s="5"/>
+      <c r="EE5" s="5"/>
+      <c r="EF5" s="5"/>
+      <c r="EG5" s="5"/>
+      <c r="EH5" s="5"/>
+      <c r="EI5" s="5"/>
+      <c r="EJ5" s="5"/>
+      <c r="EK5" s="5"/>
+      <c r="EL5" s="5"/>
+      <c r="EM5" s="5"/>
+      <c r="EN5" s="5"/>
+      <c r="EO5" s="5"/>
+      <c r="EP5" s="5"/>
+      <c r="EQ5" s="5"/>
+      <c r="ER5" s="5"/>
+      <c r="ES5" s="5"/>
+      <c r="ET5" s="5"/>
+      <c r="EU5" s="5"/>
+      <c r="EV5" s="5"/>
+      <c r="EW5" s="5"/>
+      <c r="EX5" s="5"/>
+      <c r="EY5" s="5"/>
+      <c r="EZ5" s="5"/>
+      <c r="FA5" s="5"/>
+      <c r="FB5" s="5"/>
+      <c r="FC5" s="5"/>
+      <c r="FD5" s="5"/>
+      <c r="FE5" s="5"/>
+      <c r="FF5" s="5"/>
+      <c r="FG5" s="5"/>
+      <c r="FH5" s="5"/>
+      <c r="FI5" s="5"/>
+      <c r="FJ5" s="5"/>
+      <c r="FK5" s="5"/>
+      <c r="FL5" s="5"/>
+      <c r="FM5" s="5"/>
+      <c r="FN5" s="5"/>
+      <c r="FO5" s="5"/>
+      <c r="FP5" s="5"/>
+      <c r="FQ5" s="5"/>
+      <c r="FR5" s="5"/>
+      <c r="FS5" s="5"/>
+      <c r="FT5" s="5"/>
+      <c r="FU5" s="5"/>
+    </row>
+    <row r="6" spans="1:177" ht="23" customHeight="1">
+      <c r="A6" s="119" t="s">
+        <v>296</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="132" t="s">
+        <v>356</v>
+      </c>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
+      <c r="N6" s="133"/>
+      <c r="O6" s="133"/>
+      <c r="P6" s="133"/>
+      <c r="Q6" s="133"/>
+      <c r="R6" s="133"/>
+      <c r="S6" s="133"/>
+      <c r="T6" s="133"/>
+      <c r="U6" s="133"/>
+      <c r="V6" s="133"/>
+      <c r="W6" s="133"/>
+      <c r="X6" s="133"/>
+      <c r="Y6" s="133"/>
+      <c r="Z6" s="133"/>
+      <c r="AA6" s="133"/>
+      <c r="AB6" s="134"/>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="30"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="30"/>
+      <c r="AG6" s="31"/>
+    </row>
+    <row r="7" spans="1:177" ht="23" customHeight="1">
+      <c r="A7" s="119" t="s">
+        <v>297</v>
+      </c>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="132" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="133"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="133"/>
+      <c r="X7" s="133"/>
+      <c r="Y7" s="133"/>
+      <c r="Z7" s="133"/>
+      <c r="AA7" s="133"/>
+      <c r="AB7" s="134"/>
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="31"/>
+    </row>
+    <row r="8" spans="1:177" ht="23" customHeight="1">
+      <c r="A8" s="119" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="132" t="s">
+        <v>359</v>
+      </c>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="133"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
+      <c r="N8" s="133"/>
+      <c r="O8" s="133"/>
+      <c r="P8" s="133"/>
+      <c r="Q8" s="133"/>
+      <c r="R8" s="133"/>
+      <c r="S8" s="133"/>
+      <c r="T8" s="133"/>
+      <c r="U8" s="133"/>
+      <c r="V8" s="133"/>
+      <c r="W8" s="133"/>
+      <c r="X8" s="133"/>
+      <c r="Y8" s="133"/>
+      <c r="Z8" s="133"/>
+      <c r="AA8" s="133"/>
+      <c r="AB8" s="134"/>
+      <c r="AC8" s="29"/>
+      <c r="AD8" s="30"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="31"/>
+    </row>
+    <row r="9" spans="1:177" ht="23" customHeight="1">
+      <c r="A9" s="119" t="s">
+        <v>300</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="132" t="s">
+        <v>360</v>
+      </c>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="133"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="133"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="133"/>
+      <c r="T9" s="133"/>
+      <c r="U9" s="133"/>
+      <c r="V9" s="133"/>
+      <c r="W9" s="133"/>
+      <c r="X9" s="133"/>
+      <c r="Y9" s="133"/>
+      <c r="Z9" s="133"/>
+      <c r="AA9" s="133"/>
+      <c r="AB9" s="134"/>
+      <c r="AC9" s="29"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="31"/>
+    </row>
+    <row r="10" spans="1:177" ht="23" customHeight="1">
+      <c r="A10" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="132" t="s">
+        <v>361</v>
+      </c>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="133"/>
+      <c r="N10" s="133"/>
+      <c r="O10" s="133"/>
+      <c r="P10" s="133"/>
+      <c r="Q10" s="133"/>
+      <c r="R10" s="133"/>
+      <c r="S10" s="133"/>
+      <c r="T10" s="133"/>
+      <c r="U10" s="133"/>
+      <c r="V10" s="133"/>
+      <c r="W10" s="133"/>
+      <c r="X10" s="133"/>
+      <c r="Y10" s="133"/>
+      <c r="Z10" s="133"/>
+      <c r="AA10" s="133"/>
+      <c r="AB10" s="134"/>
+      <c r="AC10" s="29"/>
+      <c r="AD10" s="30"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="30"/>
+      <c r="AG10" s="31"/>
+    </row>
+    <row r="11" spans="1:177" ht="23" customHeight="1">
+      <c r="A11" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="132" t="s">
+        <v>375</v>
+      </c>
+      <c r="H11" s="133"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="133"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="133"/>
+      <c r="N11" s="133"/>
+      <c r="O11" s="133"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
+      <c r="R11" s="133"/>
+      <c r="S11" s="133"/>
+      <c r="T11" s="133"/>
+      <c r="U11" s="133"/>
+      <c r="V11" s="133"/>
+      <c r="W11" s="133"/>
+      <c r="X11" s="133"/>
+      <c r="Y11" s="133"/>
+      <c r="Z11" s="133"/>
+      <c r="AA11" s="133"/>
+      <c r="AB11" s="134"/>
+      <c r="AC11" s="29"/>
+      <c r="AD11" s="30"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="31"/>
+    </row>
+    <row r="12" spans="1:177" ht="22.5" customHeight="1">
+      <c r="A12" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="132" t="s">
+        <v>362</v>
+      </c>
+      <c r="H12" s="133"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="133"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="133"/>
+      <c r="M12" s="133"/>
+      <c r="N12" s="133"/>
+      <c r="O12" s="133"/>
+      <c r="P12" s="133"/>
+      <c r="Q12" s="133"/>
+      <c r="R12" s="133"/>
+      <c r="S12" s="133"/>
+      <c r="T12" s="133"/>
+      <c r="U12" s="133"/>
+      <c r="V12" s="133"/>
+      <c r="W12" s="133"/>
+      <c r="X12" s="133"/>
+      <c r="Y12" s="133"/>
+      <c r="Z12" s="133"/>
+      <c r="AA12" s="133"/>
+      <c r="AB12" s="134"/>
+      <c r="AC12" s="132"/>
+      <c r="AD12" s="133"/>
+      <c r="AE12" s="133"/>
+      <c r="AF12" s="133"/>
+      <c r="AG12" s="134"/>
+    </row>
+    <row r="13" spans="1:177" ht="22.5" customHeight="1">
+      <c r="A13" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="132" t="s">
+        <v>363</v>
+      </c>
+      <c r="H13" s="133"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="133"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="133"/>
+      <c r="P13" s="133"/>
+      <c r="Q13" s="133"/>
+      <c r="R13" s="133"/>
+      <c r="S13" s="133"/>
+      <c r="T13" s="133"/>
+      <c r="U13" s="133"/>
+      <c r="V13" s="133"/>
+      <c r="W13" s="133"/>
+      <c r="X13" s="133"/>
+      <c r="Y13" s="133"/>
+      <c r="Z13" s="133"/>
+      <c r="AA13" s="133"/>
+      <c r="AB13" s="134"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="30"/>
+      <c r="AE13" s="30"/>
+      <c r="AF13" s="30"/>
+      <c r="AG13" s="31"/>
+    </row>
+    <row r="14" spans="1:177" ht="22.5" customHeight="1">
+      <c r="A14" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="132" t="s">
+        <v>364</v>
+      </c>
+      <c r="H14" s="133"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="133"/>
+      <c r="N14" s="133"/>
+      <c r="O14" s="133"/>
+      <c r="P14" s="133"/>
+      <c r="Q14" s="133"/>
+      <c r="R14" s="133"/>
+      <c r="S14" s="133"/>
+      <c r="T14" s="133"/>
+      <c r="U14" s="133"/>
+      <c r="V14" s="133"/>
+      <c r="W14" s="133"/>
+      <c r="X14" s="133"/>
+      <c r="Y14" s="133"/>
+      <c r="Z14" s="133"/>
+      <c r="AA14" s="133"/>
+      <c r="AB14" s="134"/>
+      <c r="AC14" s="132"/>
+      <c r="AD14" s="133"/>
+      <c r="AE14" s="133"/>
+      <c r="AF14" s="133"/>
+      <c r="AG14" s="134"/>
+    </row>
+    <row r="15" spans="1:177" ht="22.5" customHeight="1">
+      <c r="A15" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="132" t="s">
+        <v>365</v>
+      </c>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="133"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="133"/>
+      <c r="P15" s="133"/>
+      <c r="Q15" s="133"/>
+      <c r="R15" s="133"/>
+      <c r="S15" s="133"/>
+      <c r="T15" s="133"/>
+      <c r="U15" s="133"/>
+      <c r="V15" s="133"/>
+      <c r="W15" s="133"/>
+      <c r="X15" s="133"/>
+      <c r="Y15" s="133"/>
+      <c r="Z15" s="133"/>
+      <c r="AA15" s="133"/>
+      <c r="AB15" s="134"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="30"/>
+      <c r="AE15" s="30"/>
+      <c r="AF15" s="30"/>
+      <c r="AG15" s="31"/>
+    </row>
+    <row r="16" spans="1:177" ht="22.5" customHeight="1">
+      <c r="A16" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="132" t="s">
+        <v>366</v>
+      </c>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="133"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="133"/>
+      <c r="M16" s="133"/>
+      <c r="N16" s="133"/>
+      <c r="O16" s="133"/>
+      <c r="P16" s="133"/>
+      <c r="Q16" s="133"/>
+      <c r="R16" s="133"/>
+      <c r="S16" s="133"/>
+      <c r="T16" s="133"/>
+      <c r="U16" s="133"/>
+      <c r="V16" s="133"/>
+      <c r="W16" s="133"/>
+      <c r="X16" s="133"/>
+      <c r="Y16" s="133"/>
+      <c r="Z16" s="133"/>
+      <c r="AA16" s="133"/>
+      <c r="AB16" s="134"/>
+      <c r="AC16" s="29"/>
+      <c r="AD16" s="30"/>
+      <c r="AE16" s="30"/>
+      <c r="AF16" s="30"/>
+      <c r="AG16" s="31"/>
+    </row>
+    <row r="17" spans="1:33" ht="22.5" customHeight="1">
+      <c r="A17" s="29" t="s">
+        <v>319</v>
+      </c>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="132" t="s">
+        <v>367</v>
+      </c>
+      <c r="H17" s="133"/>
+      <c r="I17" s="133"/>
+      <c r="J17" s="133"/>
+      <c r="K17" s="133"/>
+      <c r="L17" s="133"/>
+      <c r="M17" s="133"/>
+      <c r="N17" s="133"/>
+      <c r="O17" s="133"/>
+      <c r="P17" s="133"/>
+      <c r="Q17" s="133"/>
+      <c r="R17" s="133"/>
+      <c r="S17" s="133"/>
+      <c r="T17" s="133"/>
+      <c r="U17" s="133"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="133"/>
+      <c r="X17" s="133"/>
+      <c r="Y17" s="133"/>
+      <c r="Z17" s="133"/>
+      <c r="AA17" s="133"/>
+      <c r="AB17" s="134"/>
+      <c r="AC17" s="132"/>
+      <c r="AD17" s="133"/>
+      <c r="AE17" s="133"/>
+      <c r="AF17" s="133"/>
+      <c r="AG17" s="134"/>
+    </row>
+    <row r="18" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A18" s="120" t="s">
+        <v>323</v>
+      </c>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
+      <c r="AA18" s="30"/>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="30"/>
+      <c r="AD18" s="30"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="31"/>
+    </row>
+    <row r="19" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A19" s="29"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="30"/>
+      <c r="X19" s="30"/>
+      <c r="Y19" s="30"/>
+      <c r="Z19" s="30"/>
+      <c r="AA19" s="30"/>
+      <c r="AB19" s="58"/>
+      <c r="AC19" s="30"/>
+      <c r="AD19" s="30"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="31"/>
+    </row>
+    <row r="20" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="58"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
+      <c r="AG20" s="31"/>
+    </row>
+    <row r="21" spans="1:33" ht="14.5" customHeight="1">
+      <c r="A21" s="123" t="s">
+        <v>390</v>
+      </c>
+      <c r="B21" s="124"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="30"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="30"/>
+      <c r="X21" s="30"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="32"/>
+      <c r="AA21" s="30"/>
+      <c r="AB21" s="58"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="30"/>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="30"/>
+      <c r="AG21" s="31"/>
+    </row>
+    <row r="22" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A22" s="120" t="s">
+        <v>328</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="32" t="s">
+        <v>391</v>
+      </c>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="32"/>
+      <c r="AA22" s="30"/>
+      <c r="AB22" s="58"/>
+      <c r="AC22" s="32"/>
+      <c r="AD22" s="30"/>
+      <c r="AE22" s="30"/>
+      <c r="AF22" s="30"/>
+      <c r="AG22" s="31"/>
+    </row>
+    <row r="23" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="58"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="30"/>
+      <c r="AG23" s="31"/>
+    </row>
+    <row r="24" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A24" s="120" t="s">
+        <v>353</v>
+      </c>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="32"/>
+      <c r="AA24" s="30"/>
+      <c r="AB24" s="58"/>
+      <c r="AC24" s="32"/>
+      <c r="AD24" s="30"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="30"/>
+      <c r="AG24" s="31"/>
+    </row>
+    <row r="25" spans="1:33" ht="22.5" customHeight="1">
+      <c r="A25" s="29"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="129" t="s">
+        <v>393</v>
+      </c>
+      <c r="H25" s="130"/>
+      <c r="I25" s="130"/>
+      <c r="J25" s="130"/>
+      <c r="K25" s="130"/>
+      <c r="L25" s="130"/>
+      <c r="M25" s="130"/>
+      <c r="N25" s="130"/>
+      <c r="O25" s="130"/>
+      <c r="P25" s="130"/>
+      <c r="Q25" s="130"/>
+      <c r="R25" s="130"/>
+      <c r="S25" s="130"/>
+      <c r="T25" s="130"/>
+      <c r="U25" s="130"/>
+      <c r="V25" s="130"/>
+      <c r="W25" s="130"/>
+      <c r="X25" s="130"/>
+      <c r="Y25" s="130"/>
+      <c r="Z25" s="130"/>
+      <c r="AA25" s="130"/>
+      <c r="AB25" s="131"/>
+      <c r="AC25" s="32"/>
+      <c r="AD25" s="30"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="30"/>
+      <c r="AG25" s="31"/>
+    </row>
+    <row r="26" spans="1:33" ht="22.5" customHeight="1">
+      <c r="A26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="129" t="s">
+        <v>394</v>
+      </c>
+      <c r="H26" s="130"/>
+      <c r="I26" s="130"/>
+      <c r="J26" s="130"/>
+      <c r="K26" s="130"/>
+      <c r="L26" s="130"/>
+      <c r="M26" s="130"/>
+      <c r="N26" s="130"/>
+      <c r="O26" s="130"/>
+      <c r="P26" s="130"/>
+      <c r="Q26" s="130"/>
+      <c r="R26" s="130"/>
+      <c r="S26" s="130"/>
+      <c r="T26" s="130"/>
+      <c r="U26" s="130"/>
+      <c r="V26" s="130"/>
+      <c r="W26" s="130"/>
+      <c r="X26" s="130"/>
+      <c r="Y26" s="130"/>
+      <c r="Z26" s="130"/>
+      <c r="AA26" s="130"/>
+      <c r="AB26" s="131"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
+      <c r="AG26" s="31"/>
+    </row>
+    <row r="27" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A27" s="29"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="30"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+      <c r="AA27" s="30"/>
+      <c r="AB27" s="31"/>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="30"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="30"/>
+      <c r="AG27" s="31"/>
+    </row>
+    <row r="28" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="31"/>
+    </row>
+    <row r="29" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A29" s="123" t="s">
+        <v>293</v>
+      </c>
+      <c r="B29" s="124"/>
+      <c r="C29" s="124"/>
+      <c r="D29" s="124"/>
+      <c r="E29" s="124"/>
+      <c r="F29" s="125"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="31"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
+      <c r="AG29" s="31"/>
+    </row>
+    <row r="30" spans="1:33" ht="22.5" customHeight="1">
+      <c r="A30" s="126" t="s">
+        <v>337</v>
+      </c>
+      <c r="B30" s="127"/>
+      <c r="C30" s="127"/>
+      <c r="D30" s="127"/>
+      <c r="E30" s="127"/>
+      <c r="F30" s="128"/>
+      <c r="G30" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="30"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="30"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="30"/>
+      <c r="AA30" s="30"/>
+      <c r="AB30" s="31"/>
+      <c r="AC30" s="30"/>
+      <c r="AD30" s="30"/>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="30"/>
+      <c r="AG30" s="31"/>
+    </row>
+    <row r="31" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A31" s="29"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
+      <c r="AA31" s="30"/>
+      <c r="AB31" s="31"/>
+      <c r="AC31" s="30"/>
+      <c r="AD31" s="30"/>
+      <c r="AE31" s="30"/>
+      <c r="AF31" s="30"/>
+      <c r="AG31" s="31"/>
+    </row>
+    <row r="32" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="31"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
+      <c r="AG32" s="31"/>
+    </row>
+    <row r="33" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="30"/>
+      <c r="R33" s="30"/>
+      <c r="S33" s="30"/>
+      <c r="T33" s="30"/>
+      <c r="U33" s="30"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="30"/>
+      <c r="X33" s="30"/>
+      <c r="Y33" s="30"/>
+      <c r="Z33" s="30"/>
+      <c r="AA33" s="30"/>
+      <c r="AB33" s="31"/>
+      <c r="AC33" s="30"/>
+      <c r="AD33" s="30"/>
+      <c r="AE33" s="30"/>
+      <c r="AF33" s="30"/>
+      <c r="AG33" s="31"/>
+    </row>
+    <row r="34" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A34" s="29"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="30"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="30"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="30"/>
+      <c r="X34" s="30"/>
+      <c r="Y34" s="30"/>
+      <c r="Z34" s="30"/>
+      <c r="AA34" s="30"/>
+      <c r="AB34" s="31"/>
+      <c r="AC34" s="30"/>
+      <c r="AD34" s="30"/>
+      <c r="AE34" s="30"/>
+      <c r="AF34" s="30"/>
+      <c r="AG34" s="31"/>
+    </row>
+    <row r="35" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="30"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+      <c r="AA35" s="30"/>
+      <c r="AB35" s="31"/>
+      <c r="AC35" s="30"/>
+      <c r="AD35" s="30"/>
+      <c r="AE35" s="30"/>
+      <c r="AF35" s="30"/>
+      <c r="AG35" s="31"/>
+    </row>
+    <row r="36" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A36" s="29"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
+      <c r="S36" s="30"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="30"/>
+      <c r="X36" s="30"/>
+      <c r="Y36" s="30"/>
+      <c r="Z36" s="30"/>
+      <c r="AA36" s="30"/>
+      <c r="AB36" s="31"/>
+      <c r="AC36" s="30"/>
+      <c r="AD36" s="30"/>
+      <c r="AE36" s="30"/>
+      <c r="AF36" s="30"/>
+      <c r="AG36" s="31"/>
+    </row>
+    <row r="37" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="31"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
+      <c r="AE37" s="30"/>
+      <c r="AF37" s="30"/>
+      <c r="AG37" s="31"/>
+    </row>
+    <row r="38" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A38" s="29"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="30"/>
+      <c r="S38" s="30"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="30"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="30"/>
+      <c r="X38" s="30"/>
+      <c r="Y38" s="30"/>
+      <c r="Z38" s="30"/>
+      <c r="AA38" s="30"/>
+      <c r="AB38" s="31"/>
+      <c r="AC38" s="30"/>
+      <c r="AD38" s="30"/>
+      <c r="AE38" s="30"/>
+      <c r="AF38" s="30"/>
+      <c r="AG38" s="31"/>
+    </row>
+    <row r="39" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A39" s="29"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="30"/>
+      <c r="R39" s="30"/>
+      <c r="S39" s="30"/>
+      <c r="T39" s="30"/>
+      <c r="U39" s="30"/>
+      <c r="V39" s="30"/>
+      <c r="W39" s="30"/>
+      <c r="X39" s="30"/>
+      <c r="Y39" s="30"/>
+      <c r="Z39" s="30"/>
+      <c r="AA39" s="30"/>
+      <c r="AB39" s="31"/>
+      <c r="AC39" s="30"/>
+      <c r="AD39" s="30"/>
+      <c r="AE39" s="30"/>
+      <c r="AF39" s="30"/>
+      <c r="AG39" s="31"/>
+    </row>
+    <row r="40" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+      <c r="AA40" s="30"/>
+      <c r="AB40" s="31"/>
+      <c r="AC40" s="30"/>
+      <c r="AD40" s="30"/>
+      <c r="AE40" s="30"/>
+      <c r="AF40" s="30"/>
+      <c r="AG40" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="G9:AB9"/>
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:AC3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="G5:AB5"/>
+    <mergeCell ref="AC5:AG5"/>
+    <mergeCell ref="G6:AB6"/>
+    <mergeCell ref="G7:AB7"/>
+    <mergeCell ref="G8:AB8"/>
+    <mergeCell ref="AC17:AG17"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="G26:AB26"/>
+    <mergeCell ref="G10:AB10"/>
+    <mergeCell ref="G11:AB11"/>
+    <mergeCell ref="G12:AB12"/>
+    <mergeCell ref="AC12:AG12"/>
+    <mergeCell ref="G13:AB13"/>
+    <mergeCell ref="G14:AB14"/>
+    <mergeCell ref="AC14:AG14"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="G25:AB25"/>
+    <mergeCell ref="G15:AB15"/>
+    <mergeCell ref="G16:AB16"/>
+    <mergeCell ref="G17:AB17"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="91" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0">
+    <oddFooter>&amp;LCopyright© 2005 System Integrator Corp.&amp;C&amp;P</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="31" max="32" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:FU42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
@@ -45501,7 +47569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:FU43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
@@ -56839,31 +58907,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:167" ht="12.75" customHeight="1">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="195" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="196"/>
-      <c r="M1" s="196"/>
-      <c r="N1" s="196"/>
-      <c r="O1" s="196"/>
-      <c r="P1" s="196"/>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="196"/>
-      <c r="T1" s="196"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="196"/>
-      <c r="W1" s="196"/>
+      <c r="B1" s="195"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
+      <c r="V1" s="195"/>
+      <c r="W1" s="195"/>
     </row>
     <row r="2" spans="1:167" ht="13" customHeight="1">
       <c r="A2" s="141" t="s">
@@ -56922,10 +58990,10 @@
       <c r="Q3" s="142"/>
       <c r="R3" s="142"/>
       <c r="S3" s="142"/>
-      <c r="T3" s="195"/>
-      <c r="U3" s="195"/>
-      <c r="V3" s="195"/>
-      <c r="W3" s="195"/>
+      <c r="T3" s="192"/>
+      <c r="U3" s="192"/>
+      <c r="V3" s="192"/>
+      <c r="W3" s="192"/>
       <c r="X3" s="19"/>
       <c r="Y3" s="20"/>
       <c r="Z3" s="20"/>
@@ -59363,17 +61431,17 @@
       <c r="E92" s="80"/>
       <c r="F92" s="80"/>
       <c r="G92" s="80"/>
-      <c r="H92" s="192" t="s">
+      <c r="H92" s="196" t="s">
         <v>227</v>
       </c>
-      <c r="I92" s="192"/>
-      <c r="J92" s="192"/>
-      <c r="K92" s="192"/>
-      <c r="L92" s="192"/>
-      <c r="M92" s="192"/>
-      <c r="N92" s="192"/>
-      <c r="O92" s="192"/>
-      <c r="P92" s="192"/>
+      <c r="I92" s="196"/>
+      <c r="J92" s="196"/>
+      <c r="K92" s="196"/>
+      <c r="L92" s="196"/>
+      <c r="M92" s="196"/>
+      <c r="N92" s="196"/>
+      <c r="O92" s="196"/>
+      <c r="P92" s="196"/>
       <c r="Q92" s="50"/>
       <c r="R92" s="50"/>
       <c r="S92" s="52"/>
@@ -59390,15 +61458,15 @@
       <c r="E93" s="80"/>
       <c r="F93" s="80"/>
       <c r="G93" s="80"/>
-      <c r="H93" s="192"/>
-      <c r="I93" s="192"/>
-      <c r="J93" s="192"/>
-      <c r="K93" s="192"/>
-      <c r="L93" s="192"/>
-      <c r="M93" s="192"/>
-      <c r="N93" s="192"/>
-      <c r="O93" s="192"/>
-      <c r="P93" s="192"/>
+      <c r="H93" s="196"/>
+      <c r="I93" s="196"/>
+      <c r="J93" s="196"/>
+      <c r="K93" s="196"/>
+      <c r="L93" s="196"/>
+      <c r="M93" s="196"/>
+      <c r="N93" s="196"/>
+      <c r="O93" s="196"/>
+      <c r="P93" s="196"/>
       <c r="Q93" s="50"/>
       <c r="R93" s="50"/>
       <c r="S93" s="52"/>
@@ -59415,15 +61483,15 @@
       <c r="E94" s="80"/>
       <c r="F94" s="80"/>
       <c r="G94" s="80"/>
-      <c r="H94" s="192"/>
-      <c r="I94" s="192"/>
-      <c r="J94" s="192"/>
-      <c r="K94" s="192"/>
-      <c r="L94" s="192"/>
-      <c r="M94" s="192"/>
-      <c r="N94" s="192"/>
-      <c r="O94" s="192"/>
-      <c r="P94" s="192"/>
+      <c r="H94" s="196"/>
+      <c r="I94" s="196"/>
+      <c r="J94" s="196"/>
+      <c r="K94" s="196"/>
+      <c r="L94" s="196"/>
+      <c r="M94" s="196"/>
+      <c r="N94" s="196"/>
+      <c r="O94" s="196"/>
+      <c r="P94" s="196"/>
       <c r="Q94" s="50"/>
       <c r="R94" s="50"/>
       <c r="S94" s="52"/>
@@ -59933,6 +62001,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="H92:P94"/>
+    <mergeCell ref="K98:N98"/>
+    <mergeCell ref="K104:M104"/>
+    <mergeCell ref="G3:S3"/>
+    <mergeCell ref="T3:U3"/>
     <mergeCell ref="V3:W3"/>
     <mergeCell ref="K61:N61"/>
     <mergeCell ref="K67:M67"/>
@@ -59941,11 +62014,6 @@
     <mergeCell ref="G2:S2"/>
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="V2:W2"/>
-    <mergeCell ref="H92:P94"/>
-    <mergeCell ref="K98:N98"/>
-    <mergeCell ref="K104:M104"/>
-    <mergeCell ref="G3:S3"/>
-    <mergeCell ref="T3:U3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
